--- a/Formatos/Visita 2 GFPI-F023.xlsx
+++ b/Formatos/Visita 2 GFPI-F023.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SEANT\OneDrive\Documents\Seto 2026\sena\Manual SENA Etapa Productiva\manual-aprendiz-sena\Formatos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SEANT\3D Objects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4BE35C2C-3029-4648-A112-A4612DCF5005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7179BC44-DB9A-4672-9AED-D1649F53DE5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{BC3553EE-4E49-4F2A-B03E-CFAC4EB3009B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{BC3553EE-4E49-4F2A-B03E-CFAC4EB3009B}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja2" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$A:$M</definedName>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="91">
   <si>
     <t>Información general</t>
   </si>
@@ -367,12 +368,39 @@
   <si>
     <t>Pública Reservada</t>
   </si>
+  <si>
+    <t>El aprendiz demuestra un desempeño positivo en su etapa productiva, evidenciando apropiación de conocimientos técnicos, responsabilidad en sus funciones, actitud colaborativa y buena disposición para el aprendizaje.</t>
+  </si>
+  <si>
+    <t>Presenta un avance favorable tanto en lo técnico como en lo actitudinal, con cumplimiento adecuado de sus actividades, comunicación asertiva y trabajo en equipo.</t>
+  </si>
+  <si>
+    <t>El aprendiz mantiene un desempeño satisfactorio, aplicando sus competencias técnicas con compromiso, respeto, adaptabilidad y disposición para integrarse al entorno laboral.</t>
+  </si>
+  <si>
+    <t>Se destaca por su buen manejo de las actividades asignadas, sumado a una actitud proactiva, colaborativa y abierta al aprendizaje continuo.</t>
+  </si>
+  <si>
+    <t>El aprendiz presenta algunas dificultades leves en la aplicación de sus competencias técnicas y en la adaptación a ciertas dinámicas del entorno productivo; no obstante, muestra disposición para corregirlas y mejorar de manera progresiva.</t>
+  </si>
+  <si>
+    <t>Se evidencian aspectos por fortalecer en lo técnico y en habilidades como la comunicación y la organización, aunque las dificultades observadas son manejables y el aprendiz responde positivamente a las orientaciones recibidas.</t>
+  </si>
+  <si>
+    <t>El desempeño del aprendiz refleja avances, aunque aún presenta dificultades puntuales en la ejecución de algunas actividades y en el manejo de situaciones del entorno laboral; estas pueden ser superadas con acompañamiento y seguimiento continuo.</t>
+  </si>
+  <si>
+    <t>El aprendiz presenta dificultades en la aplicación de algunas competencias técnicas y evidencia una disposición irregular frente a las actividades asignadas, por lo que requiere acompañamiento y seguimiento constante para fortalecer su desempeño.</t>
+  </si>
+  <si>
+    <t>Se observan debilidades en el manejo de aspectos técnicos y en su actitud frente a las orientaciones recibidas, situación que exige mayor compromiso, disposición al aprendizaje y apoyo continuo para mejorar su proceso formativo.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -479,6 +507,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF27251E"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -500,7 +534,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -792,15 +826,6 @@
     </border>
     <border>
       <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -875,7 +900,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="168">
+  <cellXfs count="169">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
@@ -925,517 +950,209 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1">
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
           <xfpb:xfComplement i="0"/>
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1">
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
           <xfpb:xfComplement i="0"/>
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="justify" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="justify" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="justify" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="justify" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="justify" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="justify" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="15" fontId="1" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -1443,6 +1160,317 @@
     </xf>
     <xf numFmtId="15" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -1842,7 +1870,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O82"/>
+  <dimension ref="A1:O81"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.5703125" customWidth="1"/>
@@ -1859,1098 +1887,1098 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B1" s="144" t="s">
+      <c r="B1" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="C1" s="145"/>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
-      <c r="F1" s="145"/>
-      <c r="G1" s="145"/>
-      <c r="H1" s="145"/>
-      <c r="I1" s="145"/>
-      <c r="J1" s="145"/>
-      <c r="K1" s="146"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="21"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B2" s="147" t="s">
+      <c r="B2" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="148"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="24"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B3" s="149" t="s">
+      <c r="B3" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="C3" s="150"/>
-      <c r="D3" s="150"/>
-      <c r="E3" s="150"/>
-      <c r="F3" s="150"/>
-      <c r="G3" s="150"/>
-      <c r="H3" s="150"/>
-      <c r="I3" s="150"/>
-      <c r="J3" s="150"/>
-      <c r="K3" s="151"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="27"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B4" s="147" t="s">
+      <c r="B4" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="148"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="24"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B5" s="149" t="s">
+      <c r="B5" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="C5" s="150"/>
-      <c r="D5" s="150"/>
-      <c r="E5" s="150"/>
-      <c r="F5" s="150"/>
-      <c r="G5" s="150"/>
-      <c r="H5" s="150"/>
-      <c r="I5" s="150"/>
-      <c r="J5" s="150"/>
-      <c r="K5" s="151"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="26"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="26"/>
+      <c r="K5" s="27"/>
     </row>
     <row r="6" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="152" t="s">
+      <c r="B6" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="C6" s="153"/>
-      <c r="D6" s="154" t="b">
+      <c r="C6" s="29"/>
+      <c r="D6" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="E6" s="155" t="s">
+      <c r="E6" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="F6" s="153"/>
-      <c r="G6" s="153"/>
-      <c r="H6" s="154" t="b">
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="I6" s="155" t="s">
+      <c r="I6" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="J6" s="153"/>
-      <c r="K6" s="156" t="b">
+      <c r="J6" s="29"/>
+      <c r="K6" s="18" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25"/>
     <row r="8" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="51" t="s">
+      <c r="A8" s="126" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="52"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="52"/>
-      <c r="K8" s="52"/>
-      <c r="L8" s="52"/>
-      <c r="M8" s="52"/>
+      <c r="B8" s="127"/>
+      <c r="C8" s="127"/>
+      <c r="D8" s="127"/>
+      <c r="E8" s="127"/>
+      <c r="F8" s="127"/>
+      <c r="G8" s="127"/>
+      <c r="H8" s="127"/>
+      <c r="I8" s="127"/>
+      <c r="J8" s="127"/>
+      <c r="K8" s="127"/>
+      <c r="L8" s="127"/>
+      <c r="M8" s="127"/>
     </row>
     <row r="9" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="30" t="s">
+      <c r="A9" s="95" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="31"/>
-      <c r="C9" s="48" t="s">
+      <c r="B9" s="96"/>
+      <c r="C9" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="49"/>
-      <c r="E9" s="49"/>
-      <c r="F9" s="49"/>
-      <c r="G9" s="49"/>
-      <c r="H9" s="49"/>
-      <c r="I9" s="49"/>
-      <c r="J9" s="49"/>
-      <c r="K9" s="49"/>
-      <c r="L9" s="49"/>
-      <c r="M9" s="50"/>
+      <c r="D9" s="125"/>
+      <c r="E9" s="125"/>
+      <c r="F9" s="125"/>
+      <c r="G9" s="125"/>
+      <c r="H9" s="125"/>
+      <c r="I9" s="125"/>
+      <c r="J9" s="125"/>
+      <c r="K9" s="125"/>
+      <c r="L9" s="125"/>
+      <c r="M9" s="114"/>
     </row>
     <row r="10" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="30" t="s">
+      <c r="A10" s="95" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="82" t="s">
+      <c r="B10" s="96"/>
+      <c r="C10" s="97" t="s">
         <v>4</v>
       </c>
-      <c r="D10" s="83"/>
-      <c r="E10" s="83"/>
-      <c r="F10" s="83"/>
-      <c r="G10" s="84"/>
+      <c r="D10" s="98"/>
+      <c r="E10" s="98"/>
+      <c r="F10" s="98"/>
+      <c r="G10" s="99"/>
       <c r="H10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I10" s="20"/>
-      <c r="J10" s="21"/>
-      <c r="K10" s="21"/>
-      <c r="L10" s="21"/>
-      <c r="M10" s="22"/>
+      <c r="I10" s="145"/>
+      <c r="J10" s="146"/>
+      <c r="K10" s="146"/>
+      <c r="L10" s="146"/>
+      <c r="M10" s="147"/>
     </row>
     <row r="11" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="30" t="s">
+      <c r="A11" s="95" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="31"/>
-      <c r="C11" s="92"/>
-      <c r="D11" s="93"/>
-      <c r="E11" s="93"/>
-      <c r="F11" s="93"/>
-      <c r="G11" s="93"/>
-      <c r="H11" s="94"/>
-      <c r="I11" s="95" t="s">
+      <c r="B11" s="96"/>
+      <c r="C11" s="110"/>
+      <c r="D11" s="111"/>
+      <c r="E11" s="111"/>
+      <c r="F11" s="111"/>
+      <c r="G11" s="111"/>
+      <c r="H11" s="112"/>
+      <c r="I11" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="J11" s="96"/>
-      <c r="K11" s="56"/>
-      <c r="L11" s="57"/>
-      <c r="M11" s="58"/>
+      <c r="J11" s="53"/>
+      <c r="K11" s="128"/>
+      <c r="L11" s="129"/>
+      <c r="M11" s="130"/>
     </row>
     <row r="12" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="30" t="s">
+      <c r="A12" s="95" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="31"/>
+      <c r="B12" s="96"/>
       <c r="C12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="48" t="s">
+      <c r="D12" s="113" t="s">
         <v>10</v>
       </c>
-      <c r="E12" s="50"/>
-      <c r="F12" s="97" t="s">
+      <c r="E12" s="114"/>
+      <c r="F12" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="98"/>
+      <c r="G12" s="56"/>
       <c r="H12" s="1"/>
-      <c r="I12" s="97" t="s">
+      <c r="I12" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="J12" s="98"/>
-      <c r="K12" s="59"/>
-      <c r="L12" s="60"/>
-      <c r="M12" s="61"/>
+      <c r="J12" s="56"/>
+      <c r="K12" s="131"/>
+      <c r="L12" s="132"/>
+      <c r="M12" s="133"/>
     </row>
     <row r="13" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="30" t="s">
+      <c r="A13" s="95" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="31"/>
-      <c r="C13" s="85"/>
-      <c r="D13" s="86"/>
-      <c r="E13" s="86"/>
-      <c r="F13" s="87"/>
-      <c r="G13" s="85" t="s">
+      <c r="B13" s="96"/>
+      <c r="C13" s="100"/>
+      <c r="D13" s="101"/>
+      <c r="E13" s="101"/>
+      <c r="F13" s="102"/>
+      <c r="G13" s="100" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="86"/>
-      <c r="I13" s="87"/>
-      <c r="J13" s="157"/>
-      <c r="K13" s="158"/>
-      <c r="L13" s="158"/>
-      <c r="M13" s="159"/>
+      <c r="H13" s="101"/>
+      <c r="I13" s="102"/>
+      <c r="J13" s="134"/>
+      <c r="K13" s="135"/>
+      <c r="L13" s="135"/>
+      <c r="M13" s="136"/>
     </row>
     <row r="14" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="88" t="s">
+      <c r="A14" s="103" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="30" t="s">
+      <c r="B14" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="47"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="53"/>
-      <c r="F14" s="54"/>
-      <c r="G14" s="54"/>
-      <c r="H14" s="54"/>
-      <c r="I14" s="54"/>
-      <c r="J14" s="54"/>
-      <c r="K14" s="54"/>
-      <c r="L14" s="54"/>
-      <c r="M14" s="55"/>
+      <c r="C14" s="106"/>
+      <c r="D14" s="96"/>
+      <c r="E14" s="118"/>
+      <c r="F14" s="119"/>
+      <c r="G14" s="119"/>
+      <c r="H14" s="119"/>
+      <c r="I14" s="119"/>
+      <c r="J14" s="119"/>
+      <c r="K14" s="119"/>
+      <c r="L14" s="119"/>
+      <c r="M14" s="120"/>
     </row>
     <row r="15" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="67"/>
-      <c r="B15" s="89" t="s">
+      <c r="A15" s="104"/>
+      <c r="B15" s="107" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="90"/>
-      <c r="D15" s="91"/>
-      <c r="E15" s="62"/>
-      <c r="F15" s="63"/>
-      <c r="G15" s="63"/>
-      <c r="H15" s="63"/>
-      <c r="I15" s="63"/>
-      <c r="J15" s="63"/>
-      <c r="K15" s="63"/>
-      <c r="L15" s="63"/>
-      <c r="M15" s="64"/>
+      <c r="C15" s="108"/>
+      <c r="D15" s="109"/>
+      <c r="E15" s="137"/>
+      <c r="F15" s="138"/>
+      <c r="G15" s="138"/>
+      <c r="H15" s="138"/>
+      <c r="I15" s="138"/>
+      <c r="J15" s="138"/>
+      <c r="K15" s="138"/>
+      <c r="L15" s="138"/>
+      <c r="M15" s="139"/>
     </row>
     <row r="16" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="67"/>
-      <c r="B16" s="30" t="s">
+      <c r="A16" s="104"/>
+      <c r="B16" s="95" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="47"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="53"/>
-      <c r="F16" s="54"/>
-      <c r="G16" s="54"/>
-      <c r="H16" s="54"/>
-      <c r="I16" s="54"/>
-      <c r="J16" s="54"/>
-      <c r="K16" s="54"/>
-      <c r="L16" s="54"/>
-      <c r="M16" s="55"/>
+      <c r="C16" s="106"/>
+      <c r="D16" s="96"/>
+      <c r="E16" s="118"/>
+      <c r="F16" s="119"/>
+      <c r="G16" s="119"/>
+      <c r="H16" s="119"/>
+      <c r="I16" s="119"/>
+      <c r="J16" s="119"/>
+      <c r="K16" s="119"/>
+      <c r="L16" s="119"/>
+      <c r="M16" s="120"/>
     </row>
     <row r="17" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="67"/>
-      <c r="B17" s="30" t="s">
+      <c r="A17" s="104"/>
+      <c r="B17" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="47"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="53"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="54"/>
-      <c r="H17" s="54"/>
-      <c r="I17" s="54"/>
-      <c r="J17" s="54"/>
-      <c r="K17" s="54"/>
-      <c r="L17" s="54"/>
-      <c r="M17" s="55"/>
+      <c r="C17" s="106"/>
+      <c r="D17" s="96"/>
+      <c r="E17" s="118"/>
+      <c r="F17" s="119"/>
+      <c r="G17" s="119"/>
+      <c r="H17" s="119"/>
+      <c r="I17" s="119"/>
+      <c r="J17" s="119"/>
+      <c r="K17" s="119"/>
+      <c r="L17" s="119"/>
+      <c r="M17" s="120"/>
     </row>
     <row r="18" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="67"/>
-      <c r="B18" s="30" t="s">
+      <c r="A18" s="104"/>
+      <c r="B18" s="95" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="47"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="53"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="54"/>
-      <c r="H18" s="54"/>
-      <c r="I18" s="54"/>
-      <c r="J18" s="54"/>
-      <c r="K18" s="54"/>
-      <c r="L18" s="54"/>
-      <c r="M18" s="55"/>
+      <c r="C18" s="106"/>
+      <c r="D18" s="96"/>
+      <c r="E18" s="118"/>
+      <c r="F18" s="119"/>
+      <c r="G18" s="119"/>
+      <c r="H18" s="119"/>
+      <c r="I18" s="119"/>
+      <c r="J18" s="119"/>
+      <c r="K18" s="119"/>
+      <c r="L18" s="119"/>
+      <c r="M18" s="120"/>
     </row>
     <row r="19" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="67"/>
-      <c r="B19" s="30" t="s">
+      <c r="A19" s="104"/>
+      <c r="B19" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="47"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="53"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="54"/>
-      <c r="H19" s="54"/>
-      <c r="I19" s="54"/>
-      <c r="J19" s="54"/>
-      <c r="K19" s="54"/>
-      <c r="L19" s="54"/>
-      <c r="M19" s="55"/>
+      <c r="C19" s="106"/>
+      <c r="D19" s="96"/>
+      <c r="E19" s="118"/>
+      <c r="F19" s="119"/>
+      <c r="G19" s="119"/>
+      <c r="H19" s="119"/>
+      <c r="I19" s="119"/>
+      <c r="J19" s="119"/>
+      <c r="K19" s="119"/>
+      <c r="L19" s="119"/>
+      <c r="M19" s="120"/>
     </row>
     <row r="20" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="67"/>
-      <c r="B20" s="30" t="s">
+      <c r="A20" s="104"/>
+      <c r="B20" s="95" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="47"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="35"/>
-      <c r="H20" s="35"/>
-      <c r="I20" s="35"/>
-      <c r="J20" s="35"/>
-      <c r="K20" s="35"/>
-      <c r="L20" s="35"/>
-      <c r="M20" s="36"/>
+      <c r="C20" s="106"/>
+      <c r="D20" s="96"/>
+      <c r="E20" s="115"/>
+      <c r="F20" s="116"/>
+      <c r="G20" s="116"/>
+      <c r="H20" s="116"/>
+      <c r="I20" s="116"/>
+      <c r="J20" s="116"/>
+      <c r="K20" s="116"/>
+      <c r="L20" s="116"/>
+      <c r="M20" s="117"/>
     </row>
     <row r="21" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="67"/>
-      <c r="B21" s="30" t="s">
+      <c r="A21" s="104"/>
+      <c r="B21" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="47"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="35"/>
-      <c r="H21" s="35"/>
-      <c r="I21" s="35"/>
-      <c r="J21" s="35"/>
-      <c r="K21" s="35"/>
-      <c r="L21" s="35"/>
-      <c r="M21" s="36"/>
+      <c r="C21" s="106"/>
+      <c r="D21" s="96"/>
+      <c r="E21" s="115"/>
+      <c r="F21" s="116"/>
+      <c r="G21" s="116"/>
+      <c r="H21" s="116"/>
+      <c r="I21" s="116"/>
+      <c r="J21" s="116"/>
+      <c r="K21" s="116"/>
+      <c r="L21" s="116"/>
+      <c r="M21" s="117"/>
     </row>
     <row r="22" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="68"/>
-      <c r="B22" s="30" t="s">
+      <c r="A22" s="105"/>
+      <c r="B22" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="47"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="35"/>
-      <c r="J22" s="35"/>
-      <c r="K22" s="35"/>
-      <c r="L22" s="35"/>
-      <c r="M22" s="36"/>
+      <c r="C22" s="106"/>
+      <c r="D22" s="96"/>
+      <c r="E22" s="115"/>
+      <c r="F22" s="116"/>
+      <c r="G22" s="116"/>
+      <c r="H22" s="116"/>
+      <c r="I22" s="116"/>
+      <c r="J22" s="116"/>
+      <c r="K22" s="116"/>
+      <c r="L22" s="116"/>
+      <c r="M22" s="117"/>
     </row>
     <row r="23" spans="1:13" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="66" t="s">
+      <c r="A23" s="121" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="30" t="s">
+      <c r="B23" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="C23" s="47"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="69" t="s">
+      <c r="C23" s="106"/>
+      <c r="D23" s="96"/>
+      <c r="E23" s="122" t="s">
         <v>27</v>
       </c>
-      <c r="F23" s="70"/>
-      <c r="G23" s="70"/>
-      <c r="H23" s="70"/>
-      <c r="I23" s="70"/>
-      <c r="J23" s="70"/>
-      <c r="K23" s="70"/>
-      <c r="L23" s="70"/>
-      <c r="M23" s="71"/>
+      <c r="F23" s="123"/>
+      <c r="G23" s="123"/>
+      <c r="H23" s="123"/>
+      <c r="I23" s="123"/>
+      <c r="J23" s="123"/>
+      <c r="K23" s="123"/>
+      <c r="L23" s="123"/>
+      <c r="M23" s="124"/>
     </row>
     <row r="24" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="67"/>
-      <c r="B24" s="30" t="s">
+      <c r="A24" s="104"/>
+      <c r="B24" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="C24" s="47"/>
-      <c r="D24" s="31"/>
-      <c r="E24" s="72"/>
-      <c r="F24" s="73"/>
-      <c r="G24" s="73"/>
-      <c r="H24" s="73"/>
-      <c r="I24" s="73"/>
-      <c r="J24" s="73"/>
-      <c r="K24" s="73"/>
-      <c r="L24" s="73"/>
-      <c r="M24" s="74"/>
+      <c r="C24" s="106"/>
+      <c r="D24" s="96"/>
+      <c r="E24" s="83"/>
+      <c r="F24" s="84"/>
+      <c r="G24" s="84"/>
+      <c r="H24" s="84"/>
+      <c r="I24" s="84"/>
+      <c r="J24" s="84"/>
+      <c r="K24" s="84"/>
+      <c r="L24" s="84"/>
+      <c r="M24" s="85"/>
     </row>
     <row r="25" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="68"/>
-      <c r="B25" s="30" t="s">
+      <c r="A25" s="105"/>
+      <c r="B25" s="95" t="s">
         <v>22</v>
       </c>
-      <c r="C25" s="47"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="69" t="s">
+      <c r="C25" s="106"/>
+      <c r="D25" s="96"/>
+      <c r="E25" s="122" t="s">
         <v>28</v>
       </c>
-      <c r="F25" s="70"/>
-      <c r="G25" s="70"/>
-      <c r="H25" s="70"/>
-      <c r="I25" s="70"/>
-      <c r="J25" s="70"/>
-      <c r="K25" s="70"/>
-      <c r="L25" s="70"/>
-      <c r="M25" s="71"/>
+      <c r="F25" s="123"/>
+      <c r="G25" s="123"/>
+      <c r="H25" s="123"/>
+      <c r="I25" s="123"/>
+      <c r="J25" s="123"/>
+      <c r="K25" s="123"/>
+      <c r="L25" s="123"/>
+      <c r="M25" s="124"/>
     </row>
     <row r="26" spans="1:13" ht="25.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="30" t="s">
+      <c r="B26" s="95" t="s">
         <v>32</v>
       </c>
-      <c r="C26" s="47"/>
-      <c r="D26" s="31"/>
-      <c r="E26" s="53"/>
-      <c r="F26" s="54"/>
-      <c r="G26" s="54"/>
-      <c r="H26" s="54"/>
-      <c r="I26" s="54"/>
-      <c r="J26" s="54"/>
-      <c r="K26" s="54"/>
-      <c r="L26" s="54"/>
-      <c r="M26" s="55"/>
+      <c r="C26" s="106"/>
+      <c r="D26" s="96"/>
+      <c r="E26" s="118"/>
+      <c r="F26" s="119"/>
+      <c r="G26" s="119"/>
+      <c r="H26" s="119"/>
+      <c r="I26" s="119"/>
+      <c r="J26" s="119"/>
+      <c r="K26" s="119"/>
+      <c r="L26" s="119"/>
+      <c r="M26" s="120"/>
     </row>
     <row r="27" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="30" t="s">
+      <c r="B27" s="95" t="s">
         <v>20</v>
       </c>
-      <c r="C27" s="47"/>
-      <c r="D27" s="31"/>
-      <c r="E27" s="53"/>
-      <c r="F27" s="54"/>
-      <c r="G27" s="54"/>
-      <c r="H27" s="54"/>
-      <c r="I27" s="54"/>
-      <c r="J27" s="54"/>
-      <c r="K27" s="54"/>
-      <c r="L27" s="54"/>
-      <c r="M27" s="55"/>
+      <c r="C27" s="106"/>
+      <c r="D27" s="96"/>
+      <c r="E27" s="118"/>
+      <c r="F27" s="119"/>
+      <c r="G27" s="119"/>
+      <c r="H27" s="119"/>
+      <c r="I27" s="119"/>
+      <c r="J27" s="119"/>
+      <c r="K27" s="119"/>
+      <c r="L27" s="119"/>
+      <c r="M27" s="120"/>
     </row>
     <row r="28" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
-      <c r="B28" s="30" t="s">
+      <c r="B28" s="95" t="s">
         <v>33</v>
       </c>
-      <c r="C28" s="47"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="53"/>
-      <c r="F28" s="54"/>
-      <c r="G28" s="54"/>
-      <c r="H28" s="54"/>
-      <c r="I28" s="54"/>
-      <c r="J28" s="54"/>
-      <c r="K28" s="54"/>
-      <c r="L28" s="54"/>
-      <c r="M28" s="55"/>
+      <c r="C28" s="106"/>
+      <c r="D28" s="96"/>
+      <c r="E28" s="118"/>
+      <c r="F28" s="119"/>
+      <c r="G28" s="119"/>
+      <c r="H28" s="119"/>
+      <c r="I28" s="119"/>
+      <c r="J28" s="119"/>
+      <c r="K28" s="119"/>
+      <c r="L28" s="119"/>
+      <c r="M28" s="120"/>
     </row>
     <row r="29" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3"/>
-      <c r="B29" s="30" t="s">
+      <c r="B29" s="95" t="s">
         <v>34</v>
       </c>
-      <c r="C29" s="47"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="53"/>
-      <c r="F29" s="54"/>
-      <c r="G29" s="54"/>
-      <c r="H29" s="54"/>
-      <c r="I29" s="54"/>
-      <c r="J29" s="54"/>
-      <c r="K29" s="54"/>
-      <c r="L29" s="54"/>
-      <c r="M29" s="55"/>
+      <c r="C29" s="106"/>
+      <c r="D29" s="96"/>
+      <c r="E29" s="118"/>
+      <c r="F29" s="119"/>
+      <c r="G29" s="119"/>
+      <c r="H29" s="119"/>
+      <c r="I29" s="119"/>
+      <c r="J29" s="119"/>
+      <c r="K29" s="119"/>
+      <c r="L29" s="119"/>
+      <c r="M29" s="120"/>
     </row>
     <row r="30" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B30" s="30" t="s">
+      <c r="B30" s="95" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="47"/>
-      <c r="D30" s="31"/>
-      <c r="E30" s="53"/>
-      <c r="F30" s="54"/>
-      <c r="G30" s="54"/>
-      <c r="H30" s="54"/>
-      <c r="I30" s="54"/>
-      <c r="J30" s="54"/>
-      <c r="K30" s="54"/>
-      <c r="L30" s="54"/>
-      <c r="M30" s="55"/>
+      <c r="C30" s="106"/>
+      <c r="D30" s="96"/>
+      <c r="E30" s="118"/>
+      <c r="F30" s="119"/>
+      <c r="G30" s="119"/>
+      <c r="H30" s="119"/>
+      <c r="I30" s="119"/>
+      <c r="J30" s="119"/>
+      <c r="K30" s="119"/>
+      <c r="L30" s="119"/>
+      <c r="M30" s="120"/>
     </row>
     <row r="31" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6"/>
-      <c r="B31" s="30" t="s">
+      <c r="B31" s="95" t="s">
         <v>36</v>
       </c>
-      <c r="C31" s="47"/>
-      <c r="D31" s="31"/>
-      <c r="E31" s="53"/>
-      <c r="F31" s="54"/>
-      <c r="G31" s="54"/>
-      <c r="H31" s="54"/>
-      <c r="I31" s="54"/>
-      <c r="J31" s="54"/>
-      <c r="K31" s="54"/>
-      <c r="L31" s="54"/>
-      <c r="M31" s="55"/>
+      <c r="C31" s="106"/>
+      <c r="D31" s="96"/>
+      <c r="E31" s="118"/>
+      <c r="F31" s="119"/>
+      <c r="G31" s="119"/>
+      <c r="H31" s="119"/>
+      <c r="I31" s="119"/>
+      <c r="J31" s="119"/>
+      <c r="K31" s="119"/>
+      <c r="L31" s="119"/>
+      <c r="M31" s="120"/>
     </row>
     <row r="32" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6"/>
-      <c r="B32" s="30" t="s">
+      <c r="B32" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="C32" s="47"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="34"/>
-      <c r="F32" s="35"/>
-      <c r="G32" s="35"/>
-      <c r="H32" s="35"/>
-      <c r="I32" s="35"/>
-      <c r="J32" s="35"/>
-      <c r="K32" s="35"/>
-      <c r="L32" s="35"/>
-      <c r="M32" s="36"/>
+      <c r="C32" s="106"/>
+      <c r="D32" s="96"/>
+      <c r="E32" s="115"/>
+      <c r="F32" s="116"/>
+      <c r="G32" s="116"/>
+      <c r="H32" s="116"/>
+      <c r="I32" s="116"/>
+      <c r="J32" s="116"/>
+      <c r="K32" s="116"/>
+      <c r="L32" s="116"/>
+      <c r="M32" s="117"/>
     </row>
     <row r="33" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="6"/>
-      <c r="B33" s="30" t="s">
+      <c r="B33" s="95" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="47"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="53"/>
-      <c r="F33" s="54"/>
-      <c r="G33" s="54"/>
-      <c r="H33" s="54"/>
-      <c r="I33" s="54"/>
-      <c r="J33" s="54"/>
-      <c r="K33" s="54"/>
-      <c r="L33" s="54"/>
-      <c r="M33" s="55"/>
+      <c r="C33" s="106"/>
+      <c r="D33" s="96"/>
+      <c r="E33" s="118"/>
+      <c r="F33" s="119"/>
+      <c r="G33" s="119"/>
+      <c r="H33" s="119"/>
+      <c r="I33" s="119"/>
+      <c r="J33" s="119"/>
+      <c r="K33" s="119"/>
+      <c r="L33" s="119"/>
+      <c r="M33" s="120"/>
     </row>
     <row r="34" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7"/>
-      <c r="B34" s="32" t="s">
+      <c r="B34" s="140" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="33"/>
-      <c r="D34" s="65"/>
-      <c r="E34" s="34"/>
-      <c r="F34" s="35"/>
-      <c r="G34" s="35"/>
-      <c r="H34" s="35"/>
-      <c r="I34" s="35"/>
-      <c r="J34" s="35"/>
-      <c r="K34" s="35"/>
-      <c r="L34" s="35"/>
-      <c r="M34" s="36"/>
+      <c r="C34" s="141"/>
+      <c r="D34" s="142"/>
+      <c r="E34" s="115"/>
+      <c r="F34" s="116"/>
+      <c r="G34" s="116"/>
+      <c r="H34" s="116"/>
+      <c r="I34" s="116"/>
+      <c r="J34" s="116"/>
+      <c r="K34" s="116"/>
+      <c r="L34" s="116"/>
+      <c r="M34" s="117"/>
     </row>
     <row r="35" spans="1:13" ht="25.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B35" s="44" t="s">
+      <c r="B35" s="164" t="s">
         <v>41</v>
       </c>
-      <c r="C35" s="45"/>
-      <c r="D35" s="46"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="35"/>
-      <c r="G35" s="35"/>
-      <c r="H35" s="35"/>
-      <c r="I35" s="35"/>
-      <c r="J35" s="35"/>
-      <c r="K35" s="35"/>
-      <c r="L35" s="35"/>
-      <c r="M35" s="36"/>
+      <c r="C35" s="165"/>
+      <c r="D35" s="166"/>
+      <c r="E35" s="115"/>
+      <c r="F35" s="116"/>
+      <c r="G35" s="116"/>
+      <c r="H35" s="116"/>
+      <c r="I35" s="116"/>
+      <c r="J35" s="116"/>
+      <c r="K35" s="116"/>
+      <c r="L35" s="116"/>
+      <c r="M35" s="117"/>
     </row>
     <row r="36" spans="1:13" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B36" s="30" t="s">
+      <c r="B36" s="95" t="s">
         <v>42</v>
       </c>
-      <c r="C36" s="47"/>
-      <c r="D36" s="31"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="35"/>
-      <c r="G36" s="35"/>
-      <c r="H36" s="35"/>
-      <c r="I36" s="35"/>
-      <c r="J36" s="35"/>
-      <c r="K36" s="35"/>
-      <c r="L36" s="35"/>
-      <c r="M36" s="36"/>
+      <c r="C36" s="106"/>
+      <c r="D36" s="96"/>
+      <c r="E36" s="115"/>
+      <c r="F36" s="116"/>
+      <c r="G36" s="116"/>
+      <c r="H36" s="116"/>
+      <c r="I36" s="116"/>
+      <c r="J36" s="116"/>
+      <c r="K36" s="116"/>
+      <c r="L36" s="116"/>
+      <c r="M36" s="117"/>
     </row>
     <row r="37" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="10"/>
-      <c r="B37" s="30" t="s">
+      <c r="B37" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="47"/>
-      <c r="D37" s="31"/>
-      <c r="E37" s="34"/>
-      <c r="F37" s="35"/>
-      <c r="G37" s="35"/>
-      <c r="H37" s="35"/>
-      <c r="I37" s="35"/>
-      <c r="J37" s="35"/>
-      <c r="K37" s="35"/>
-      <c r="L37" s="35"/>
-      <c r="M37" s="36"/>
+      <c r="C37" s="106"/>
+      <c r="D37" s="96"/>
+      <c r="E37" s="115"/>
+      <c r="F37" s="116"/>
+      <c r="G37" s="116"/>
+      <c r="H37" s="116"/>
+      <c r="I37" s="116"/>
+      <c r="J37" s="116"/>
+      <c r="K37" s="116"/>
+      <c r="L37" s="116"/>
+      <c r="M37" s="117"/>
     </row>
     <row r="38" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="18" t="s">
+      <c r="A38" s="143" t="s">
         <v>43</v>
       </c>
-      <c r="B38" s="18"/>
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
-      <c r="F38" s="18"/>
-      <c r="G38" s="18"/>
-      <c r="H38" s="18"/>
-      <c r="I38" s="18"/>
-      <c r="J38" s="18"/>
-      <c r="K38" s="18"/>
-      <c r="L38" s="18"/>
-      <c r="M38" s="18"/>
+      <c r="B38" s="143"/>
+      <c r="C38" s="143"/>
+      <c r="D38" s="143"/>
+      <c r="E38" s="143"/>
+      <c r="F38" s="143"/>
+      <c r="G38" s="143"/>
+      <c r="H38" s="143"/>
+      <c r="I38" s="143"/>
+      <c r="J38" s="143"/>
+      <c r="K38" s="143"/>
+      <c r="L38" s="143"/>
+      <c r="M38" s="143"/>
     </row>
     <row r="39" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="18"/>
-      <c r="B39" s="18"/>
-      <c r="C39" s="18"/>
-      <c r="D39" s="18"/>
-      <c r="E39" s="18"/>
-      <c r="F39" s="18"/>
-      <c r="G39" s="18"/>
-      <c r="H39" s="18"/>
-      <c r="I39" s="18"/>
-      <c r="J39" s="18"/>
-      <c r="K39" s="18"/>
-      <c r="L39" s="18"/>
-      <c r="M39" s="18"/>
+      <c r="A39" s="143"/>
+      <c r="B39" s="143"/>
+      <c r="C39" s="143"/>
+      <c r="D39" s="143"/>
+      <c r="E39" s="143"/>
+      <c r="F39" s="143"/>
+      <c r="G39" s="143"/>
+      <c r="H39" s="143"/>
+      <c r="I39" s="143"/>
+      <c r="J39" s="143"/>
+      <c r="K39" s="143"/>
+      <c r="L39" s="143"/>
+      <c r="M39" s="143"/>
     </row>
     <row r="40" spans="1:13" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="18"/>
-      <c r="B40" s="18"/>
-      <c r="C40" s="18"/>
-      <c r="D40" s="18"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="18"/>
-      <c r="G40" s="18"/>
-      <c r="H40" s="18"/>
-      <c r="I40" s="18"/>
-      <c r="J40" s="18"/>
-      <c r="K40" s="18"/>
-      <c r="L40" s="18"/>
-      <c r="M40" s="18"/>
+      <c r="A40" s="143"/>
+      <c r="B40" s="143"/>
+      <c r="C40" s="143"/>
+      <c r="D40" s="143"/>
+      <c r="E40" s="143"/>
+      <c r="F40" s="143"/>
+      <c r="G40" s="143"/>
+      <c r="H40" s="143"/>
+      <c r="I40" s="143"/>
+      <c r="J40" s="143"/>
+      <c r="K40" s="143"/>
+      <c r="L40" s="143"/>
+      <c r="M40" s="143"/>
     </row>
     <row r="41" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="11"/>
-      <c r="B41" s="126" t="s">
+      <c r="B41" s="68" t="s">
         <v>73</v>
       </c>
-      <c r="C41" s="127"/>
-      <c r="D41" s="127"/>
-      <c r="E41" s="127"/>
-      <c r="F41" s="127"/>
-      <c r="G41" s="127"/>
-      <c r="H41" s="127"/>
-      <c r="I41" s="127"/>
-      <c r="J41" s="128"/>
+      <c r="C41" s="69"/>
+      <c r="D41" s="69"/>
+      <c r="E41" s="69"/>
+      <c r="F41" s="69"/>
+      <c r="G41" s="69"/>
+      <c r="H41" s="69"/>
+      <c r="I41" s="69"/>
+      <c r="J41" s="70"/>
       <c r="K41" s="11"/>
       <c r="L41" s="11"/>
       <c r="M41" s="11"/>
     </row>
     <row r="42" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="11"/>
-      <c r="B42" s="26" t="s">
+      <c r="B42" s="71" t="s">
         <v>72</v>
       </c>
-      <c r="C42" s="27"/>
-      <c r="D42" s="160"/>
-      <c r="E42" s="161"/>
-      <c r="F42" s="162"/>
-      <c r="G42" s="26" t="s">
+      <c r="C42" s="150"/>
+      <c r="D42" s="151"/>
+      <c r="E42" s="152"/>
+      <c r="F42" s="153"/>
+      <c r="G42" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="H42" s="129"/>
-      <c r="I42" s="130"/>
-      <c r="J42" s="166"/>
+      <c r="H42" s="72"/>
+      <c r="I42" s="73"/>
+      <c r="J42" s="77"/>
       <c r="K42" s="11"/>
       <c r="L42" s="11"/>
       <c r="M42" s="11"/>
     </row>
     <row r="43" spans="1:13" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="11"/>
-      <c r="B43" s="28"/>
-      <c r="C43" s="29"/>
-      <c r="D43" s="163"/>
-      <c r="E43" s="164"/>
-      <c r="F43" s="165"/>
-      <c r="G43" s="131" t="s">
+      <c r="B43" s="38"/>
+      <c r="C43" s="39"/>
+      <c r="D43" s="154"/>
+      <c r="E43" s="155"/>
+      <c r="F43" s="156"/>
+      <c r="G43" s="74" t="s">
         <v>44</v>
       </c>
-      <c r="H43" s="132"/>
-      <c r="I43" s="133"/>
-      <c r="J43" s="167"/>
+      <c r="H43" s="75"/>
+      <c r="I43" s="76"/>
+      <c r="J43" s="78"/>
       <c r="K43" s="11"/>
       <c r="L43" s="11"/>
       <c r="M43" s="11"/>
     </row>
     <row r="44" spans="1:13" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="11"/>
-      <c r="B44" s="30" t="s">
+      <c r="B44" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="C44" s="31"/>
+      <c r="C44" s="96"/>
       <c r="D44" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="E44" s="32" t="s">
+      <c r="E44" s="140" t="s">
         <v>48</v>
       </c>
-      <c r="F44" s="33"/>
-      <c r="G44" s="33"/>
-      <c r="H44" s="34"/>
-      <c r="I44" s="35"/>
-      <c r="J44" s="36"/>
+      <c r="F44" s="141"/>
+      <c r="G44" s="141"/>
+      <c r="H44" s="115"/>
+      <c r="I44" s="116"/>
+      <c r="J44" s="117"/>
       <c r="K44" s="11"/>
       <c r="L44" s="11"/>
       <c r="M44" s="11"/>
     </row>
     <row r="45" spans="1:13" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="11"/>
-      <c r="B45" s="134" t="s">
+      <c r="B45" s="79" t="s">
         <v>49</v>
       </c>
-      <c r="C45" s="135"/>
-      <c r="D45" s="111"/>
-      <c r="E45" s="111"/>
-      <c r="F45" s="111"/>
-      <c r="G45" s="111"/>
-      <c r="H45" s="135"/>
-      <c r="I45" s="135"/>
-      <c r="J45" s="136"/>
+      <c r="C45" s="80"/>
+      <c r="D45" s="81"/>
+      <c r="E45" s="81"/>
+      <c r="F45" s="81"/>
+      <c r="G45" s="81"/>
+      <c r="H45" s="80"/>
+      <c r="I45" s="80"/>
+      <c r="J45" s="82"/>
       <c r="K45" s="11"/>
       <c r="L45" s="11"/>
       <c r="M45" s="11"/>
     </row>
     <row r="46" spans="1:13" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="11"/>
-      <c r="B46" s="118" t="s">
+      <c r="B46" s="50" t="s">
         <v>50</v>
       </c>
-      <c r="C46" s="119"/>
-      <c r="D46" s="97" t="s">
+      <c r="C46" s="51"/>
+      <c r="D46" s="54" t="s">
         <v>51</v>
       </c>
-      <c r="E46" s="120"/>
-      <c r="F46" s="120"/>
-      <c r="G46" s="98"/>
-      <c r="H46" s="102" t="s">
+      <c r="E46" s="55"/>
+      <c r="F46" s="55"/>
+      <c r="G46" s="56"/>
+      <c r="H46" s="57" t="s">
         <v>52</v>
       </c>
-      <c r="I46" s="106"/>
-      <c r="J46" s="103"/>
+      <c r="I46" s="58"/>
+      <c r="J46" s="59"/>
       <c r="K46" s="11"/>
       <c r="L46" s="11"/>
       <c r="M46" s="11"/>
     </row>
     <row r="47" spans="1:13" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="11"/>
-      <c r="B47" s="95"/>
-      <c r="C47" s="96"/>
-      <c r="D47" s="121" t="s">
+      <c r="B47" s="52"/>
+      <c r="C47" s="53"/>
+      <c r="D47" s="63" t="s">
         <v>53</v>
       </c>
-      <c r="E47" s="122"/>
-      <c r="F47" s="121" t="s">
+      <c r="E47" s="64"/>
+      <c r="F47" s="63" t="s">
         <v>54</v>
       </c>
-      <c r="G47" s="122"/>
-      <c r="H47" s="104"/>
-      <c r="I47" s="107"/>
-      <c r="J47" s="105"/>
+      <c r="G47" s="64"/>
+      <c r="H47" s="60"/>
+      <c r="I47" s="61"/>
+      <c r="J47" s="62"/>
       <c r="K47" s="11"/>
       <c r="L47" s="11"/>
       <c r="M47" s="11"/>
     </row>
     <row r="48" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="15"/>
-      <c r="B48" s="78" t="s">
+      <c r="B48" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="C48" s="79"/>
-      <c r="D48" s="80"/>
-      <c r="E48" s="81"/>
-      <c r="F48" s="80"/>
-      <c r="G48" s="81"/>
-      <c r="H48" s="123"/>
-      <c r="I48" s="124"/>
-      <c r="J48" s="125"/>
+      <c r="C48" s="32"/>
+      <c r="D48" s="33"/>
+      <c r="E48" s="34"/>
+      <c r="F48" s="33"/>
+      <c r="G48" s="34"/>
+      <c r="H48" s="65"/>
+      <c r="I48" s="66"/>
+      <c r="J48" s="67"/>
       <c r="K48" s="15"/>
       <c r="L48" s="15"/>
       <c r="M48" s="15"/>
     </row>
     <row r="49" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="15"/>
-      <c r="B49" s="78" t="s">
+      <c r="B49" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="C49" s="79"/>
-      <c r="D49" s="80"/>
-      <c r="E49" s="81"/>
-      <c r="F49" s="37"/>
-      <c r="G49" s="38"/>
-      <c r="H49" s="75"/>
-      <c r="I49" s="76"/>
-      <c r="J49" s="77"/>
+      <c r="C49" s="32"/>
+      <c r="D49" s="33"/>
+      <c r="E49" s="34"/>
+      <c r="F49" s="157"/>
+      <c r="G49" s="158"/>
+      <c r="H49" s="40"/>
+      <c r="I49" s="41"/>
+      <c r="J49" s="42"/>
       <c r="K49" s="15"/>
       <c r="L49" s="15"/>
       <c r="M49" s="15"/>
     </row>
     <row r="50" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="15"/>
-      <c r="B50" s="78" t="s">
+      <c r="B50" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="C50" s="79"/>
-      <c r="D50" s="80"/>
-      <c r="E50" s="81"/>
-      <c r="F50" s="80"/>
-      <c r="G50" s="81"/>
-      <c r="H50" s="75"/>
-      <c r="I50" s="76"/>
-      <c r="J50" s="77"/>
+      <c r="C50" s="32"/>
+      <c r="D50" s="33"/>
+      <c r="E50" s="34"/>
+      <c r="F50" s="33"/>
+      <c r="G50" s="34"/>
+      <c r="H50" s="40"/>
+      <c r="I50" s="41"/>
+      <c r="J50" s="42"/>
       <c r="K50" s="15"/>
       <c r="L50" s="15"/>
       <c r="M50" s="15"/>
     </row>
     <row r="51" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="15"/>
-      <c r="B51" s="28" t="s">
+      <c r="B51" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="C51" s="29"/>
-      <c r="D51" s="113"/>
-      <c r="E51" s="114"/>
-      <c r="F51" s="113"/>
-      <c r="G51" s="114"/>
-      <c r="H51" s="115"/>
-      <c r="I51" s="116"/>
-      <c r="J51" s="117"/>
+      <c r="C51" s="39"/>
+      <c r="D51" s="90"/>
+      <c r="E51" s="91"/>
+      <c r="F51" s="90"/>
+      <c r="G51" s="91"/>
+      <c r="H51" s="92"/>
+      <c r="I51" s="93"/>
+      <c r="J51" s="94"/>
       <c r="K51" s="15"/>
       <c r="L51" s="15"/>
       <c r="M51" s="15"/>
     </row>
     <row r="52" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="15"/>
-      <c r="B52" s="78" t="s">
+      <c r="B52" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="C52" s="79"/>
-      <c r="D52" s="80"/>
-      <c r="E52" s="81"/>
-      <c r="F52" s="80"/>
-      <c r="G52" s="81"/>
-      <c r="H52" s="99"/>
-      <c r="I52" s="100"/>
-      <c r="J52" s="101"/>
+      <c r="C52" s="32"/>
+      <c r="D52" s="33"/>
+      <c r="E52" s="34"/>
+      <c r="F52" s="33"/>
+      <c r="G52" s="34"/>
+      <c r="H52" s="35"/>
+      <c r="I52" s="36"/>
+      <c r="J52" s="37"/>
       <c r="K52" s="15"/>
       <c r="L52" s="15"/>
       <c r="M52" s="15"/>
     </row>
     <row r="53" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="15"/>
-      <c r="B53" s="78" t="s">
+      <c r="B53" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="C53" s="79"/>
-      <c r="D53" s="80"/>
-      <c r="E53" s="81"/>
-      <c r="F53" s="80"/>
-      <c r="G53" s="81"/>
-      <c r="H53" s="75"/>
-      <c r="I53" s="76"/>
-      <c r="J53" s="77"/>
+      <c r="C53" s="32"/>
+      <c r="D53" s="33"/>
+      <c r="E53" s="34"/>
+      <c r="F53" s="33"/>
+      <c r="G53" s="34"/>
+      <c r="H53" s="40"/>
+      <c r="I53" s="41"/>
+      <c r="J53" s="42"/>
       <c r="K53" s="15"/>
       <c r="L53" s="15"/>
       <c r="M53" s="15"/>
     </row>
     <row r="54" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="15"/>
-      <c r="B54" s="78" t="s">
+      <c r="B54" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="C54" s="79"/>
-      <c r="D54" s="80"/>
-      <c r="E54" s="81"/>
-      <c r="F54" s="80"/>
-      <c r="G54" s="81"/>
-      <c r="H54" s="75"/>
-      <c r="I54" s="76"/>
-      <c r="J54" s="77"/>
+      <c r="C54" s="32"/>
+      <c r="D54" s="33"/>
+      <c r="E54" s="34"/>
+      <c r="F54" s="33"/>
+      <c r="G54" s="34"/>
+      <c r="H54" s="40"/>
+      <c r="I54" s="41"/>
+      <c r="J54" s="42"/>
       <c r="K54" s="15"/>
       <c r="L54" s="15"/>
       <c r="M54" s="15"/>
     </row>
     <row r="55" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="15"/>
-      <c r="B55" s="137" t="s">
+      <c r="B55" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="C55" s="138"/>
-      <c r="D55" s="139"/>
-      <c r="E55" s="140"/>
-      <c r="F55" s="139"/>
-      <c r="G55" s="140"/>
-      <c r="H55" s="141"/>
-      <c r="I55" s="142"/>
-      <c r="J55" s="143"/>
+      <c r="C55" s="44"/>
+      <c r="D55" s="45"/>
+      <c r="E55" s="46"/>
+      <c r="F55" s="45"/>
+      <c r="G55" s="46"/>
+      <c r="H55" s="47"/>
+      <c r="I55" s="48"/>
+      <c r="J55" s="49"/>
       <c r="K55" s="15"/>
       <c r="L55" s="15"/>
       <c r="M55" s="15"/>
     </row>
     <row r="56" spans="1:13" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="15"/>
-      <c r="B56" s="110" t="s">
+      <c r="B56" s="88" t="s">
         <v>62</v>
       </c>
-      <c r="C56" s="111"/>
-      <c r="D56" s="111"/>
-      <c r="E56" s="111"/>
-      <c r="F56" s="111"/>
-      <c r="G56" s="111"/>
-      <c r="H56" s="111"/>
-      <c r="I56" s="111"/>
-      <c r="J56" s="112"/>
+      <c r="C56" s="81"/>
+      <c r="D56" s="81"/>
+      <c r="E56" s="81"/>
+      <c r="F56" s="81"/>
+      <c r="G56" s="81"/>
+      <c r="H56" s="81"/>
+      <c r="I56" s="81"/>
+      <c r="J56" s="89"/>
       <c r="K56" s="15"/>
       <c r="L56" s="15"/>
       <c r="M56" s="15"/>
     </row>
     <row r="57" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="15"/>
-      <c r="B57" s="102" t="s">
+      <c r="B57" s="57" t="s">
         <v>50</v>
       </c>
-      <c r="C57" s="103"/>
-      <c r="D57" s="72" t="s">
+      <c r="C57" s="59"/>
+      <c r="D57" s="83" t="s">
         <v>51</v>
       </c>
-      <c r="E57" s="73"/>
-      <c r="F57" s="73"/>
-      <c r="G57" s="74"/>
-      <c r="H57" s="102" t="s">
+      <c r="E57" s="84"/>
+      <c r="F57" s="84"/>
+      <c r="G57" s="85"/>
+      <c r="H57" s="57" t="s">
         <v>52</v>
       </c>
-      <c r="I57" s="106"/>
-      <c r="J57" s="103"/>
+      <c r="I57" s="58"/>
+      <c r="J57" s="59"/>
       <c r="K57" s="15"/>
       <c r="L57" s="15"/>
       <c r="M57" s="15"/>
     </row>
     <row r="58" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="15"/>
-      <c r="B58" s="104"/>
-      <c r="C58" s="105"/>
-      <c r="D58" s="108" t="s">
+      <c r="B58" s="60"/>
+      <c r="C58" s="62"/>
+      <c r="D58" s="86" t="s">
         <v>53</v>
       </c>
-      <c r="E58" s="109"/>
-      <c r="F58" s="108" t="s">
+      <c r="E58" s="87"/>
+      <c r="F58" s="86" t="s">
         <v>54</v>
       </c>
-      <c r="G58" s="109"/>
-      <c r="H58" s="104"/>
-      <c r="I58" s="107"/>
-      <c r="J58" s="105"/>
+      <c r="G58" s="87"/>
+      <c r="H58" s="60"/>
+      <c r="I58" s="61"/>
+      <c r="J58" s="62"/>
       <c r="K58" s="15"/>
       <c r="L58" s="15"/>
       <c r="M58" s="15"/>
     </row>
     <row r="59" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="15"/>
-      <c r="B59" s="78" t="s">
+      <c r="B59" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="C59" s="79"/>
-      <c r="D59" s="80"/>
-      <c r="E59" s="81"/>
-      <c r="F59" s="80"/>
-      <c r="G59" s="81"/>
-      <c r="H59" s="99"/>
-      <c r="I59" s="100"/>
-      <c r="J59" s="101"/>
+      <c r="C59" s="32"/>
+      <c r="D59" s="33"/>
+      <c r="E59" s="34"/>
+      <c r="F59" s="33"/>
+      <c r="G59" s="34"/>
+      <c r="H59" s="35"/>
+      <c r="I59" s="36"/>
+      <c r="J59" s="37"/>
       <c r="K59" s="15"/>
       <c r="L59" s="15"/>
       <c r="M59" s="15"/>
     </row>
     <row r="60" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="15"/>
-      <c r="B60" s="78" t="s">
+      <c r="B60" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="C60" s="79"/>
-      <c r="D60" s="80"/>
-      <c r="E60" s="81"/>
-      <c r="F60" s="80"/>
-      <c r="G60" s="81"/>
-      <c r="H60" s="99"/>
-      <c r="I60" s="100"/>
-      <c r="J60" s="101"/>
+      <c r="C60" s="32"/>
+      <c r="D60" s="33"/>
+      <c r="E60" s="34"/>
+      <c r="F60" s="33"/>
+      <c r="G60" s="34"/>
+      <c r="H60" s="35"/>
+      <c r="I60" s="36"/>
+      <c r="J60" s="37"/>
       <c r="K60" s="15"/>
       <c r="L60" s="15"/>
       <c r="M60" s="15"/>
     </row>
     <row r="61" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="15"/>
-      <c r="B61" s="78" t="s">
+      <c r="B61" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="C61" s="79"/>
-      <c r="D61" s="80"/>
-      <c r="E61" s="81"/>
-      <c r="F61" s="80"/>
-      <c r="G61" s="81"/>
-      <c r="H61" s="99"/>
-      <c r="I61" s="100"/>
-      <c r="J61" s="101"/>
+      <c r="C61" s="32"/>
+      <c r="D61" s="33"/>
+      <c r="E61" s="34"/>
+      <c r="F61" s="33"/>
+      <c r="G61" s="34"/>
+      <c r="H61" s="35"/>
+      <c r="I61" s="36"/>
+      <c r="J61" s="37"/>
       <c r="K61" s="15"/>
       <c r="L61" s="15"/>
       <c r="M61" s="15"/>
     </row>
     <row r="62" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="15"/>
-      <c r="B62" s="78" t="s">
+      <c r="B62" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="C62" s="79"/>
-      <c r="D62" s="80"/>
-      <c r="E62" s="81"/>
-      <c r="F62" s="80"/>
-      <c r="G62" s="81"/>
-      <c r="H62" s="99"/>
-      <c r="I62" s="100"/>
-      <c r="J62" s="101"/>
+      <c r="C62" s="32"/>
+      <c r="D62" s="33"/>
+      <c r="E62" s="34"/>
+      <c r="F62" s="33"/>
+      <c r="G62" s="34"/>
+      <c r="H62" s="35"/>
+      <c r="I62" s="36"/>
+      <c r="J62" s="37"/>
       <c r="K62" s="15"/>
       <c r="L62" s="15"/>
       <c r="M62" s="15"/>
     </row>
     <row r="63" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="15"/>
-      <c r="B63" s="78" t="s">
+      <c r="B63" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="C63" s="79"/>
-      <c r="D63" s="80"/>
-      <c r="E63" s="81"/>
-      <c r="F63" s="80"/>
-      <c r="G63" s="81"/>
-      <c r="H63" s="99"/>
-      <c r="I63" s="100"/>
-      <c r="J63" s="101"/>
+      <c r="C63" s="32"/>
+      <c r="D63" s="33"/>
+      <c r="E63" s="34"/>
+      <c r="F63" s="33"/>
+      <c r="G63" s="34"/>
+      <c r="H63" s="35"/>
+      <c r="I63" s="36"/>
+      <c r="J63" s="37"/>
       <c r="K63" s="15"/>
       <c r="L63" s="15"/>
       <c r="M63" s="15"/>
@@ -2979,226 +3007,353 @@
       <c r="L65" s="11"/>
       <c r="M65" s="11"/>
     </row>
-    <row r="66" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="11"/>
-      <c r="B66" s="23"/>
-      <c r="C66" s="23"/>
-      <c r="D66" s="23"/>
-      <c r="E66" s="23"/>
-      <c r="F66" s="23"/>
-      <c r="G66" s="23"/>
-      <c r="H66" s="23"/>
-      <c r="I66" s="23"/>
-      <c r="J66" s="23"/>
+      <c r="B66" s="168"/>
+      <c r="C66" s="168"/>
+      <c r="D66" s="168"/>
+      <c r="E66" s="168"/>
+      <c r="F66" s="168"/>
+      <c r="G66" s="168"/>
+      <c r="H66" s="168"/>
+      <c r="I66" s="168"/>
+      <c r="J66" s="168"/>
       <c r="K66" s="11"/>
       <c r="L66" s="11"/>
       <c r="M66" s="11"/>
     </row>
     <row r="67" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="11"/>
-      <c r="B67" s="24"/>
-      <c r="C67" s="24"/>
-      <c r="D67" s="24"/>
-      <c r="E67" s="24"/>
-      <c r="F67" s="24"/>
-      <c r="G67" s="24"/>
-      <c r="H67" s="24"/>
-      <c r="I67" s="24"/>
-      <c r="J67" s="24"/>
+      <c r="B67" s="14" t="s">
+        <v>69</v>
+      </c>
       <c r="K67" s="11"/>
       <c r="L67" s="11"/>
       <c r="M67" s="11"/>
     </row>
-    <row r="68" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="11"/>
-      <c r="B68" s="14" t="s">
-        <v>69</v>
-      </c>
+      <c r="B68" s="149"/>
+      <c r="C68" s="149"/>
+      <c r="D68" s="149"/>
+      <c r="E68" s="149"/>
+      <c r="F68" s="149"/>
+      <c r="G68" s="149"/>
+      <c r="H68" s="149"/>
+      <c r="I68" s="149"/>
+      <c r="J68" s="149"/>
       <c r="K68" s="11"/>
       <c r="L68" s="11"/>
       <c r="M68" s="11"/>
     </row>
-    <row r="69" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="11"/>
-      <c r="B69" s="25"/>
-      <c r="C69" s="25"/>
-      <c r="D69" s="25"/>
-      <c r="E69" s="25"/>
-      <c r="F69" s="25"/>
-      <c r="G69" s="25"/>
-      <c r="H69" s="25"/>
-      <c r="I69" s="25"/>
-      <c r="J69" s="25"/>
+      <c r="B69" s="14" t="s">
+        <v>70</v>
+      </c>
       <c r="K69" s="11"/>
       <c r="L69" s="11"/>
       <c r="M69" s="11"/>
     </row>
-    <row r="70" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="11"/>
-      <c r="B70" s="14" t="s">
-        <v>70</v>
-      </c>
+      <c r="B70" s="148"/>
+      <c r="C70" s="148"/>
+      <c r="D70" s="148"/>
+      <c r="E70" s="148"/>
+      <c r="F70" s="148"/>
+      <c r="G70" s="148"/>
+      <c r="H70" s="148"/>
+      <c r="I70" s="148"/>
+      <c r="J70" s="148"/>
       <c r="K70" s="11"/>
       <c r="L70" s="11"/>
       <c r="M70" s="11"/>
     </row>
-    <row r="71" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="11"/>
-      <c r="B71" s="23"/>
-      <c r="C71" s="23"/>
-      <c r="D71" s="23"/>
-      <c r="E71" s="23"/>
-      <c r="F71" s="23"/>
-      <c r="G71" s="23"/>
-      <c r="H71" s="23"/>
-      <c r="I71" s="23"/>
-      <c r="J71" s="23"/>
+      <c r="B71" s="11"/>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="11"/>
+      <c r="F71" s="11"/>
+      <c r="G71" s="11"/>
+      <c r="H71" s="11"/>
+      <c r="I71" s="11"/>
+      <c r="J71" s="11"/>
       <c r="K71" s="11"/>
       <c r="L71" s="11"/>
       <c r="M71" s="11"/>
     </row>
-    <row r="72" spans="1:13" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="11"/>
-      <c r="B72" s="11"/>
-      <c r="C72" s="11"/>
-      <c r="D72" s="11"/>
-      <c r="E72" s="11"/>
-      <c r="F72" s="11"/>
-      <c r="G72" s="11"/>
-      <c r="H72" s="11"/>
-      <c r="I72" s="11"/>
-      <c r="J72" s="11"/>
-      <c r="K72" s="11"/>
-      <c r="L72" s="11"/>
-      <c r="M72" s="11"/>
-    </row>
-    <row r="73" spans="1:13" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="42"/>
-      <c r="B73" s="42"/>
-      <c r="C73" s="42"/>
-      <c r="D73" s="42"/>
-      <c r="E73" s="40"/>
-      <c r="F73" s="40"/>
-      <c r="G73" s="42"/>
-      <c r="H73" s="42"/>
-      <c r="I73" s="40"/>
-      <c r="J73" s="40"/>
-      <c r="K73" s="42"/>
-      <c r="L73" s="42"/>
-      <c r="M73" s="42"/>
+    <row r="72" spans="1:13" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="162"/>
+      <c r="B72" s="162"/>
+      <c r="C72" s="162"/>
+      <c r="D72" s="162"/>
+      <c r="E72" s="160"/>
+      <c r="F72" s="160"/>
+      <c r="G72" s="162"/>
+      <c r="H72" s="162"/>
+      <c r="I72" s="160"/>
+      <c r="J72" s="160"/>
+      <c r="K72" s="162"/>
+      <c r="L72" s="162"/>
+      <c r="M72" s="162"/>
+    </row>
+    <row r="73" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="162"/>
+      <c r="B73" s="162"/>
+      <c r="C73" s="162"/>
+      <c r="D73" s="162"/>
+      <c r="E73" s="160"/>
+      <c r="F73" s="160"/>
+      <c r="G73" s="162"/>
+      <c r="H73" s="162"/>
+      <c r="I73" s="160"/>
+      <c r="J73" s="160"/>
+      <c r="K73" s="162"/>
+      <c r="L73" s="162"/>
+      <c r="M73" s="162"/>
     </row>
     <row r="74" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="42"/>
-      <c r="B74" s="42"/>
-      <c r="C74" s="42"/>
-      <c r="D74" s="42"/>
-      <c r="E74" s="40"/>
-      <c r="F74" s="40"/>
-      <c r="G74" s="42"/>
-      <c r="H74" s="42"/>
-      <c r="I74" s="40"/>
-      <c r="J74" s="40"/>
-      <c r="K74" s="42"/>
-      <c r="L74" s="42"/>
-      <c r="M74" s="42"/>
+      <c r="A74" s="162"/>
+      <c r="B74" s="162"/>
+      <c r="C74" s="162"/>
+      <c r="D74" s="162"/>
+      <c r="E74" s="160"/>
+      <c r="F74" s="160"/>
+      <c r="G74" s="162"/>
+      <c r="H74" s="162"/>
+      <c r="I74" s="160"/>
+      <c r="J74" s="160"/>
+      <c r="K74" s="162"/>
+      <c r="L74" s="162"/>
+      <c r="M74" s="162"/>
     </row>
     <row r="75" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="42"/>
-      <c r="B75" s="42"/>
-      <c r="C75" s="42"/>
-      <c r="D75" s="42"/>
-      <c r="E75" s="40"/>
-      <c r="F75" s="40"/>
-      <c r="G75" s="42"/>
-      <c r="H75" s="42"/>
-      <c r="I75" s="40"/>
-      <c r="J75" s="40"/>
-      <c r="K75" s="42"/>
-      <c r="L75" s="42"/>
-      <c r="M75" s="42"/>
+      <c r="A75" s="162"/>
+      <c r="B75" s="162"/>
+      <c r="C75" s="162"/>
+      <c r="D75" s="162"/>
+      <c r="E75" s="160"/>
+      <c r="F75" s="160"/>
+      <c r="G75" s="162"/>
+      <c r="H75" s="162"/>
+      <c r="I75" s="160"/>
+      <c r="J75" s="160"/>
+      <c r="K75" s="162"/>
+      <c r="L75" s="162"/>
+      <c r="M75" s="162"/>
     </row>
     <row r="76" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="42"/>
-      <c r="B76" s="42"/>
-      <c r="C76" s="42"/>
-      <c r="D76" s="42"/>
-      <c r="E76" s="40"/>
-      <c r="F76" s="40"/>
-      <c r="G76" s="42"/>
-      <c r="H76" s="42"/>
-      <c r="I76" s="40"/>
-      <c r="J76" s="40"/>
-      <c r="K76" s="42"/>
-      <c r="L76" s="42"/>
-      <c r="M76" s="42"/>
-    </row>
-    <row r="77" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="43"/>
-      <c r="B77" s="43"/>
-      <c r="C77" s="43"/>
-      <c r="D77" s="43"/>
-      <c r="E77" s="40"/>
-      <c r="F77" s="40"/>
-      <c r="G77" s="43"/>
-      <c r="H77" s="43"/>
-      <c r="I77" s="40"/>
-      <c r="J77" s="40"/>
-      <c r="K77" s="43"/>
-      <c r="L77" s="43"/>
-      <c r="M77" s="43"/>
-    </row>
-    <row r="78" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="39"/>
-      <c r="B78" s="39"/>
-      <c r="C78" s="39"/>
-      <c r="D78" s="39"/>
-      <c r="E78" s="40"/>
-      <c r="F78" s="40"/>
-      <c r="G78" s="41" t="s">
+      <c r="A76" s="163"/>
+      <c r="B76" s="163"/>
+      <c r="C76" s="163"/>
+      <c r="D76" s="163"/>
+      <c r="E76" s="160"/>
+      <c r="F76" s="160"/>
+      <c r="G76" s="163"/>
+      <c r="H76" s="163"/>
+      <c r="I76" s="160"/>
+      <c r="J76" s="160"/>
+      <c r="K76" s="163"/>
+      <c r="L76" s="163"/>
+      <c r="M76" s="163"/>
+    </row>
+    <row r="77" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="159"/>
+      <c r="B77" s="159"/>
+      <c r="C77" s="159"/>
+      <c r="D77" s="159"/>
+      <c r="E77" s="160"/>
+      <c r="F77" s="160"/>
+      <c r="G77" s="161" t="s">
         <v>27</v>
       </c>
-      <c r="H78" s="41"/>
-      <c r="I78" s="40"/>
-      <c r="J78" s="40"/>
-      <c r="K78" s="39"/>
-      <c r="L78" s="39"/>
-      <c r="M78" s="39"/>
+      <c r="H77" s="161"/>
+      <c r="I77" s="160"/>
+      <c r="J77" s="160"/>
+      <c r="K77" s="159"/>
+      <c r="L77" s="159"/>
+      <c r="M77" s="159"/>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A78" s="12"/>
+      <c r="B78" s="12"/>
+      <c r="C78" s="12"/>
+      <c r="D78" s="12"/>
+      <c r="E78" s="12"/>
+      <c r="F78" s="12"/>
+      <c r="G78" s="12"/>
+      <c r="H78" s="12"/>
+      <c r="I78" s="12"/>
+      <c r="J78" s="12"/>
+      <c r="K78" s="12"/>
+      <c r="L78" s="12"/>
+      <c r="M78" s="12"/>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A79" s="12"/>
-      <c r="B79" s="12"/>
-      <c r="C79" s="12"/>
-      <c r="D79" s="12"/>
-      <c r="E79" s="12"/>
-      <c r="F79" s="12"/>
-      <c r="G79" s="12"/>
-      <c r="H79" s="12"/>
-      <c r="I79" s="12"/>
-      <c r="J79" s="12"/>
-      <c r="K79" s="12"/>
-      <c r="L79" s="12"/>
-      <c r="M79" s="12"/>
+      <c r="A79" s="13"/>
+      <c r="C79" s="144"/>
+      <c r="D79" s="144"/>
+      <c r="E79" s="144"/>
+      <c r="F79" s="144"/>
+      <c r="G79" s="144"/>
+      <c r="H79" s="144"/>
+      <c r="I79" s="144"/>
+      <c r="J79" s="144"/>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A80" s="13"/>
-      <c r="C80" s="19"/>
-      <c r="D80" s="19"/>
-      <c r="E80" s="19"/>
-      <c r="F80" s="19"/>
-      <c r="G80" s="19"/>
-      <c r="H80" s="19"/>
-      <c r="I80" s="19"/>
-      <c r="J80" s="19"/>
-    </row>
-    <row r="81" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F81" s="17" t="s">
+      <c r="F80" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G81" s="17"/>
-    </row>
-    <row r="82" spans="6:7" x14ac:dyDescent="0.25"/>
+      <c r="G80" s="23"/>
+    </row>
+    <row r="81" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="166">
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="A38:M40"/>
+    <mergeCell ref="C79:J79"/>
+    <mergeCell ref="I10:M10"/>
+    <mergeCell ref="B66:J66"/>
+    <mergeCell ref="B68:J68"/>
+    <mergeCell ref="B70:J70"/>
+    <mergeCell ref="B42:C43"/>
+    <mergeCell ref="D42:F43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="E44:G44"/>
+    <mergeCell ref="H44:J44"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="A77:D77"/>
+    <mergeCell ref="E77:F77"/>
+    <mergeCell ref="G77:H77"/>
+    <mergeCell ref="I77:J77"/>
+    <mergeCell ref="K77:M77"/>
+    <mergeCell ref="A72:D76"/>
+    <mergeCell ref="E72:F76"/>
+    <mergeCell ref="G72:H76"/>
+    <mergeCell ref="I72:J76"/>
+    <mergeCell ref="K72:M76"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="C9:M9"/>
+    <mergeCell ref="A8:M8"/>
+    <mergeCell ref="E14:M14"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="J13:M13"/>
+    <mergeCell ref="E15:M15"/>
+    <mergeCell ref="E16:M16"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="E32:M32"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="E29:M29"/>
+    <mergeCell ref="E30:M30"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E23:M23"/>
+    <mergeCell ref="E24:M24"/>
+    <mergeCell ref="E25:M25"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="E35:M35"/>
+    <mergeCell ref="E36:M36"/>
+    <mergeCell ref="E37:M37"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="E33:M33"/>
+    <mergeCell ref="E34:M34"/>
+    <mergeCell ref="E21:M21"/>
+    <mergeCell ref="E22:M22"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E17:M17"/>
+    <mergeCell ref="E18:M18"/>
+    <mergeCell ref="E19:M19"/>
+    <mergeCell ref="E31:M31"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E26:M26"/>
+    <mergeCell ref="E27:M27"/>
+    <mergeCell ref="E28:M28"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="H50:J50"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="A14:A22"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E20:M20"/>
+    <mergeCell ref="B41:J41"/>
+    <mergeCell ref="G42:I42"/>
+    <mergeCell ref="G43:I43"/>
+    <mergeCell ref="J42:J43"/>
+    <mergeCell ref="B45:J45"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="H60:J60"/>
+    <mergeCell ref="B57:C58"/>
+    <mergeCell ref="D57:G57"/>
+    <mergeCell ref="H57:J58"/>
+    <mergeCell ref="D58:E58"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="D59:E59"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="H59:J59"/>
+    <mergeCell ref="B56:J56"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="F62:G62"/>
+    <mergeCell ref="H62:J62"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="H52:J52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="B46:C47"/>
+    <mergeCell ref="D46:G46"/>
+    <mergeCell ref="H46:J47"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="H48:J48"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="D61:E61"/>
+    <mergeCell ref="F61:G61"/>
+    <mergeCell ref="H61:J61"/>
+    <mergeCell ref="H51:J51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="H49:J49"/>
+    <mergeCell ref="B50:C50"/>
     <mergeCell ref="B1:K1"/>
     <mergeCell ref="B2:K2"/>
     <mergeCell ref="B3:K3"/>
@@ -3223,165 +3378,23 @@
     <mergeCell ref="H55:J55"/>
     <mergeCell ref="B62:C62"/>
     <mergeCell ref="D62:E62"/>
-    <mergeCell ref="F62:G62"/>
-    <mergeCell ref="H62:J62"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="H52:J52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="B46:C47"/>
-    <mergeCell ref="D46:G46"/>
-    <mergeCell ref="H46:J47"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="H48:J48"/>
-    <mergeCell ref="B41:J41"/>
-    <mergeCell ref="G42:I42"/>
-    <mergeCell ref="G43:I43"/>
-    <mergeCell ref="J42:J43"/>
-    <mergeCell ref="B45:J45"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="F60:G60"/>
-    <mergeCell ref="H60:J60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="D61:E61"/>
-    <mergeCell ref="F61:G61"/>
-    <mergeCell ref="H61:J61"/>
-    <mergeCell ref="B57:C58"/>
-    <mergeCell ref="D57:G57"/>
-    <mergeCell ref="H57:J58"/>
-    <mergeCell ref="D58:E58"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="D59:E59"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="H59:J59"/>
-    <mergeCell ref="B56:J56"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="H51:J51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="H49:J49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="H50:J50"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="A14:A22"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E20:M20"/>
-    <mergeCell ref="E21:M21"/>
-    <mergeCell ref="E22:M22"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E17:M17"/>
-    <mergeCell ref="E18:M18"/>
-    <mergeCell ref="E19:M19"/>
-    <mergeCell ref="E31:M31"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="E26:M26"/>
-    <mergeCell ref="E27:M27"/>
-    <mergeCell ref="E28:M28"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E23:M23"/>
-    <mergeCell ref="E24:M24"/>
-    <mergeCell ref="E25:M25"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="E35:M35"/>
-    <mergeCell ref="E36:M36"/>
-    <mergeCell ref="E37:M37"/>
-    <mergeCell ref="C9:M9"/>
-    <mergeCell ref="A8:M8"/>
-    <mergeCell ref="E14:M14"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="J13:M13"/>
-    <mergeCell ref="E15:M15"/>
-    <mergeCell ref="E16:M16"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="E32:M32"/>
-    <mergeCell ref="E33:M33"/>
-    <mergeCell ref="E34:M34"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="E29:M29"/>
-    <mergeCell ref="E30:M30"/>
-    <mergeCell ref="F81:G81"/>
-    <mergeCell ref="A38:M40"/>
-    <mergeCell ref="C80:J80"/>
-    <mergeCell ref="I10:M10"/>
-    <mergeCell ref="B66:J67"/>
-    <mergeCell ref="B69:J69"/>
-    <mergeCell ref="B71:J71"/>
-    <mergeCell ref="B42:C43"/>
-    <mergeCell ref="D42:F43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="E44:G44"/>
-    <mergeCell ref="H44:J44"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="A78:D78"/>
-    <mergeCell ref="E78:F78"/>
-    <mergeCell ref="G78:H78"/>
-    <mergeCell ref="I78:J78"/>
-    <mergeCell ref="K78:M78"/>
-    <mergeCell ref="A73:D77"/>
-    <mergeCell ref="E73:F77"/>
-    <mergeCell ref="G73:H77"/>
-    <mergeCell ref="I73:J77"/>
-    <mergeCell ref="K73:M77"/>
-    <mergeCell ref="B35:D35"/>
   </mergeCells>
-  <conditionalFormatting sqref="A78:D78 K78:M78 C80:J80">
+  <conditionalFormatting sqref="A77:D77 K77:M77 C79:J79">
     <cfRule type="containsBlanks" dxfId="5" priority="2">
-      <formula>LEN(TRIM(A78))=0</formula>
+      <formula>LEN(TRIM(A77))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A78:D78">
+  <conditionalFormatting sqref="A77:D77">
     <cfRule type="containsBlanks" dxfId="4" priority="4">
-      <formula>LEN(TRIM(A78))=0</formula>
+      <formula>LEN(TRIM(A77))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C80">
+  <conditionalFormatting sqref="C79">
     <cfRule type="containsBlanks" dxfId="3" priority="5">
-      <formula>LEN(TRIM(C80))=0</formula>
+      <formula>LEN(TRIM(C79))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D42:F43 J42:J43 D48:J55 D59:J63 B69:J69 B71:J71">
+  <conditionalFormatting sqref="D42:F43 J42:J43 D48:J55 D59:J63 B68:J68 B70:J70">
     <cfRule type="containsBlanks" dxfId="2" priority="1">
       <formula>LEN(TRIM(B42))=0</formula>
     </cfRule>
@@ -3391,12 +3404,12 @@
       <formula>LEN(TRIM(C10))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K78:M78">
+  <conditionalFormatting sqref="K77:M77">
     <cfRule type="containsBlanks" dxfId="0" priority="3">
-      <formula>LEN(TRIM(K78))=0</formula>
+      <formula>LEN(TRIM(K77))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="47">
+  <dataValidations count="48">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Indicar el nivel formativo en el cual se encuentra el aprendiz. Técnio o Tecnólogo" sqref="I10:M10" xr:uid="{FDFD4240-B4E4-40FA-8880-3E4E045C5084}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Registrar el nombre del programa" prompt="Registrar el nombre del programa" sqref="C11:H11" xr:uid="{34EF5BAD-650F-4FA7-AB25-B4A5694BB4C0}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Número Ficha" prompt="Registre el número de ficha en el que se encuentra matriculado según el programa de formación." sqref="K11:M11" xr:uid="{C295E52F-E427-4103-89DB-18FF195E95C6}"/>
@@ -3419,16 +3432,15 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el número del celular del jefe inmediato o supervisor y el número fijo de la empresa con extensión" sqref="E32:M32" xr:uid="{D17896B5-5299-404D-BF06-0A7409E6BB11}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="En caso de que aplique, registrar el nombre de otro contacto en la empresa. De no tener digitar N/A" sqref="E33:M33" xr:uid="{A6F4976B-257F-4E38-96A4-122163F2BCDA}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el teléfono institucional al cual contactarse en caso que el ente coformador no responda" sqref="E34:M34" xr:uid="{A593241B-15E7-4EA6-B9DE-E0DF01ED6DB9}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="En caso de que el aprendiz sea una persona en situación de discapacidad, diligencie este espacio con el nombre de la persona que le asiste." sqref="E35:M35" xr:uid="{C19946D2-B571-4104-A1EA-FEF5A7253596}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Aquí se especifica el tipo de asistencia brindada al aprendiz para que desempeñe la totalidad de sus tareas asegurando un ambiente laboral inclusivo adecuado a sus necesidades. Puede incluir asistencias como lenguaje de señas, soporte visual etc" sqref="E36:M36" xr:uid="{B635F5F5-108B-409C-BCAD-0AA5A654CF02}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el número del celular de la persona que asiste al aprendiz " sqref="E37:M37" xr:uid="{77AEF51E-4966-4ADA-B94D-7E72C6BE4FFA}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el nombre completo del aprendiz y en la parte superior la Firma manuscrita o digital." sqref="A78:D78" xr:uid="{A7FEFB2B-7370-4FA2-8820-7EB89B730FD1}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el nombre completo del co-formador y en la parte superior de esta la Firma manuscrita o digital." sqref="K78:M78" xr:uid="{DAE2A968-2309-42D5-952C-BC599D7BE50F}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Diligenciar fecha de la sesión en este espacio. Ejemplo: Bogotá dia/mes/año Virtual" sqref="C80:J80" xr:uid="{201095D8-80DA-45BB-84F9-D066E44DB3C5}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Si no aplica colocar N/A" prompt="En caso de que el aprendiz sea una persona en situación de discapacidad, diligencie este espacio con el nombre de la persona que le asiste." sqref="E35:M35" xr:uid="{C19946D2-B571-4104-A1EA-FEF5A7253596}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Si no aplica colocar N/A" prompt="Aquí se especifica el tipo de asistencia brindada al aprendiz para que desempeñe la totalidad de sus tareas asegurando un ambiente laboral inclusivo adecuado a sus necesidades. Puede incluir asistencias como lenguaje de señas, soporte visual etc" sqref="E36:M36" xr:uid="{B635F5F5-108B-409C-BCAD-0AA5A654CF02}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Si no aplica colocar N/A" prompt="Registrar el número del celular de la persona que asiste al aprendiz " sqref="E37:M37" xr:uid="{77AEF51E-4966-4ADA-B94D-7E72C6BE4FFA}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="OBLIGATORIO" prompt="Registrar el nombre completo del aprendiz y en la parte superior la Firma manuscrita o digital." sqref="A77:D77" xr:uid="{A7FEFB2B-7370-4FA2-8820-7EB89B730FD1}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="OBLIGATORIO" prompt="Registrar el nombre completo del co-formador y en la parte superior de esta la Firma manuscrita o digital." sqref="K77:M77" xr:uid="{DAE2A968-2309-42D5-952C-BC599D7BE50F}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Bogotá dd/mm/aaaa Virtual" prompt="Diligenciar fecha de la sesión en este espacio. Ejemplo: Bogotá dia/mes/año Virtual" sqref="C79:J79" xr:uid="{201095D8-80DA-45BB-84F9-D066E44DB3C5}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registre la fecha en que el aprendiz dio inicio a su etapa productiva." sqref="D42:F43" xr:uid="{91ABAF52-821D-4DE8-B0C2-245C3EFA4EAC}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registre la fecha en que se realizó el momento de planeación de la etapa productiva. FCHA DE LA SESION" sqref="J42:J43" xr:uid="{54F15547-5AB5-4314-88CB-73760EC82315}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Adjuntar enlace de la video llamada" sqref="H44:J44" xr:uid="{B1F72570-FBB0-43D7-BC61-1C17B377356B}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Indique las razones por las que se brinda dicha valoración (indispensable en las valoradas por mejorar)." sqref="H48:J48" xr:uid="{2775CE5B-7882-46E3-9B64-A1DCACE5C767}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Aporta activamente al mejoramiento de sus habilidades técnicas y métodos de trabajo." sqref="D49:F49" xr:uid="{A8FCB973-8FC0-4BDD-BF0E-CC9BB61BE366}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Marcar con una X según correspon" prompt="Demuestra las competencias específicas del programa de formación en situaciones reales de trabajo. " sqref="D48:G48" xr:uid="{948FA747-4CF8-48C4-8768-F9CADBC3F362}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Realiza acciones que fortalezcan su perfil ocupacional potenciando sus competencias en el marco de su proyecto de vida." sqref="D50:G50" xr:uid="{379961D4-6BD4-47A0-B009-E49C8B35A883}"/>
@@ -3442,10 +3454,83 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Propone alternativas de solución a situaciones problemáticas, en el contexto del desarrollo de su etapa productiva. " sqref="D61:G61" xr:uid="{8CFCA47A-7FFB-4C81-B160-32FC56FE753D}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Es comprometido con las actividades asignadas y con la empresa, demostrando puntualidad, proactividad y buena presentación personal en el desarrollo de su etapa productiva" sqref="D62:G62" xr:uid="{C5D9BB00-F014-4DE5-B59C-090440CDA5FD}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Demuestra capacidad para ordenar y disponer los elementos necesarios e información que facilite la ejecución del trabajo y el logro de los objetivos." sqref="D63:G63" xr:uid="{B8588CD4-9B9C-4123-8FA4-B0191CFB9CEA}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar las correspondientes observaciones para cada variable sea del co-formador, instructor de seguimiento y del aprendiz, si es del caso" sqref="B66:J67" xr:uid="{8831A1A9-AB8B-443F-901C-833E895B3B1F}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar de manera objetiva y concisa la información adicional que complemente el proceso de acompañamiento al aprendiz en su etapa productiva." sqref="B69:J69 B71:J71" xr:uid="{D7E55FAF-6FC8-4AC1-A902-F35811C9DD3B}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="OBLIGATORIO" prompt="Registrar de manera objetiva y concisa la información adicional que complemente el proceso de acompañamiento al aprendiz en su etapa productiva." sqref="B70:J70" xr:uid="{D7E55FAF-6FC8-4AC1-A902-F35811C9DD3B}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="OBLIGATORIO" prompt="Registrar de manera objetiva y concisa la información adicional que complemente el proceso de acompañamiento al aprendiz en su etapa productiva." sqref="B68:J68" xr:uid="{B24B5D0A-E15D-45FB-8DD6-CE569B75705D}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="DILIGENCIAR SI HAY POR MEJORAR" prompt="Si hay factores por mejorar favor escribir las observaciones o los compromisos de mejora" sqref="H48:J55" xr:uid="{70C7BBAF-F2BE-4776-BA55-57FE0807C14D}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Diligenciar si hay por mejorar" prompt="Si hay factores por mejorar favor escribir las observaciones o los compromisos de mejora" sqref="H59:J63" xr:uid="{56231F2E-9BAE-4742-84BB-A6BBFCFB029F}"/>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="5" scale="68" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar las correspondientes observaciones para cada variable sea del co-formador, instructor de seguimiento y del aprendiz, si es del caso" xr:uid="{8831A1A9-AB8B-443F-901C-833E895B3B1F}">
+          <x14:formula1>
+            <xm:f>Hoja2!$A$1:$A$9</xm:f>
+          </x14:formula1>
+          <xm:sqref>B66:J66</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B116DD3D-17ED-40B5-9E6B-227A66CA4F49}">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="85.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A1" s="167" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A2" s="167" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="167" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="167" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A5" s="167" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="167" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A7" s="167" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A8" s="167" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="167" t="s">
+        <v>90</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Formatos/Visita 2 GFPI-F023.xlsx
+++ b/Formatos/Visita 2 GFPI-F023.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SEANT\3D Objects\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SEANT\OneDrive\Documents\Seto 2026\sena\Manual SENA Etapa Productiva\manual-aprendiz-sena\Formatos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7179BC44-DB9A-4672-9AED-D1649F53DE5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0630D33E-B5D0-4F12-A43A-9112395366C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{BC3553EE-4E49-4F2A-B03E-CFAC4EB3009B}"/>
   </bookViews>
@@ -900,7 +900,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="169">
+  <cellXfs count="167">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
@@ -964,6 +964,9 @@
         </ext>
       </extLst>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1127,6 +1130,18 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1203,18 +1218,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1302,6 +1305,69 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1314,69 +1380,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1397,13 +1400,17 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1431,14 +1438,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -1465,13 +1464,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1887,95 +1879,95 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="22"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="23"/>
-      <c r="K2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="25"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27"/>
+      <c r="K3" s="28"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="25"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="26" t="s">
         <v>78</v>
       </c>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
-      <c r="K5" s="27"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="27"/>
+      <c r="K5" s="28"/>
     </row>
     <row r="6" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="29" t="s">
         <v>79</v>
       </c>
-      <c r="C6" s="29"/>
+      <c r="C6" s="30"/>
       <c r="D6" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="E6" s="30" t="s">
+      <c r="E6" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="30"/>
       <c r="H6" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="I6" s="30" t="s">
+      <c r="I6" s="31" t="s">
         <v>81</v>
       </c>
-      <c r="J6" s="29"/>
+      <c r="J6" s="30"/>
       <c r="K6" s="18" t="b">
         <v>0</v>
       </c>
@@ -1999,11 +1991,11 @@
       <c r="M8" s="127"/>
     </row>
     <row r="9" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="95" t="s">
+      <c r="A9" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="96"/>
-      <c r="C9" s="113" t="s">
+      <c r="B9" s="97"/>
+      <c r="C9" s="114" t="s">
         <v>2</v>
       </c>
       <c r="D9" s="125"/>
@@ -2015,118 +2007,118 @@
       <c r="J9" s="125"/>
       <c r="K9" s="125"/>
       <c r="L9" s="125"/>
-      <c r="M9" s="114"/>
+      <c r="M9" s="115"/>
     </row>
     <row r="10" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="95" t="s">
+      <c r="A10" s="96" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="96"/>
-      <c r="C10" s="97" t="s">
+      <c r="B10" s="97"/>
+      <c r="C10" s="98" t="s">
         <v>4</v>
       </c>
-      <c r="D10" s="98"/>
-      <c r="E10" s="98"/>
-      <c r="F10" s="98"/>
-      <c r="G10" s="99"/>
+      <c r="D10" s="99"/>
+      <c r="E10" s="99"/>
+      <c r="F10" s="99"/>
+      <c r="G10" s="100"/>
       <c r="H10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I10" s="145"/>
-      <c r="J10" s="146"/>
-      <c r="K10" s="146"/>
-      <c r="L10" s="146"/>
-      <c r="M10" s="147"/>
+      <c r="I10" s="146"/>
+      <c r="J10" s="147"/>
+      <c r="K10" s="147"/>
+      <c r="L10" s="147"/>
+      <c r="M10" s="148"/>
     </row>
     <row r="11" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="95" t="s">
+      <c r="A11" s="96" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="96"/>
-      <c r="C11" s="110"/>
-      <c r="D11" s="111"/>
-      <c r="E11" s="111"/>
-      <c r="F11" s="111"/>
-      <c r="G11" s="111"/>
-      <c r="H11" s="112"/>
-      <c r="I11" s="52" t="s">
+      <c r="B11" s="97"/>
+      <c r="C11" s="111"/>
+      <c r="D11" s="112"/>
+      <c r="E11" s="112"/>
+      <c r="F11" s="112"/>
+      <c r="G11" s="112"/>
+      <c r="H11" s="113"/>
+      <c r="I11" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="J11" s="53"/>
+      <c r="J11" s="54"/>
       <c r="K11" s="128"/>
       <c r="L11" s="129"/>
       <c r="M11" s="130"/>
     </row>
     <row r="12" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="95" t="s">
+      <c r="A12" s="96" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="96"/>
+      <c r="B12" s="97"/>
       <c r="C12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="113" t="s">
+      <c r="D12" s="114" t="s">
         <v>10</v>
       </c>
-      <c r="E12" s="114"/>
-      <c r="F12" s="54" t="s">
+      <c r="E12" s="115"/>
+      <c r="F12" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="56"/>
+      <c r="G12" s="57"/>
       <c r="H12" s="1"/>
-      <c r="I12" s="54" t="s">
+      <c r="I12" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="J12" s="56"/>
+      <c r="J12" s="57"/>
       <c r="K12" s="131"/>
       <c r="L12" s="132"/>
       <c r="M12" s="133"/>
     </row>
     <row r="13" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="95" t="s">
+      <c r="A13" s="96" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="96"/>
-      <c r="C13" s="100"/>
-      <c r="D13" s="101"/>
-      <c r="E13" s="101"/>
-      <c r="F13" s="102"/>
-      <c r="G13" s="100" t="s">
+      <c r="B13" s="97"/>
+      <c r="C13" s="101"/>
+      <c r="D13" s="102"/>
+      <c r="E13" s="102"/>
+      <c r="F13" s="103"/>
+      <c r="G13" s="101" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="101"/>
-      <c r="I13" s="102"/>
+      <c r="H13" s="102"/>
+      <c r="I13" s="103"/>
       <c r="J13" s="134"/>
       <c r="K13" s="135"/>
       <c r="L13" s="135"/>
       <c r="M13" s="136"/>
     </row>
     <row r="14" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="103" t="s">
+      <c r="A14" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="95" t="s">
+      <c r="B14" s="96" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="106"/>
-      <c r="D14" s="96"/>
-      <c r="E14" s="118"/>
-      <c r="F14" s="119"/>
-      <c r="G14" s="119"/>
-      <c r="H14" s="119"/>
-      <c r="I14" s="119"/>
-      <c r="J14" s="119"/>
-      <c r="K14" s="119"/>
-      <c r="L14" s="119"/>
-      <c r="M14" s="120"/>
+      <c r="C14" s="107"/>
+      <c r="D14" s="97"/>
+      <c r="E14" s="119"/>
+      <c r="F14" s="120"/>
+      <c r="G14" s="120"/>
+      <c r="H14" s="120"/>
+      <c r="I14" s="120"/>
+      <c r="J14" s="120"/>
+      <c r="K14" s="120"/>
+      <c r="L14" s="120"/>
+      <c r="M14" s="121"/>
     </row>
     <row r="15" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="104"/>
-      <c r="B15" s="107" t="s">
+      <c r="A15" s="105"/>
+      <c r="B15" s="108" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="108"/>
-      <c r="D15" s="109"/>
+      <c r="C15" s="109"/>
+      <c r="D15" s="110"/>
       <c r="E15" s="137"/>
       <c r="F15" s="138"/>
       <c r="G15" s="138"/>
@@ -2138,339 +2130,339 @@
       <c r="M15" s="139"/>
     </row>
     <row r="16" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="104"/>
-      <c r="B16" s="95" t="s">
+      <c r="A16" s="105"/>
+      <c r="B16" s="96" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="106"/>
-      <c r="D16" s="96"/>
-      <c r="E16" s="118"/>
-      <c r="F16" s="119"/>
-      <c r="G16" s="119"/>
-      <c r="H16" s="119"/>
-      <c r="I16" s="119"/>
-      <c r="J16" s="119"/>
-      <c r="K16" s="119"/>
-      <c r="L16" s="119"/>
-      <c r="M16" s="120"/>
+      <c r="C16" s="107"/>
+      <c r="D16" s="97"/>
+      <c r="E16" s="119"/>
+      <c r="F16" s="120"/>
+      <c r="G16" s="120"/>
+      <c r="H16" s="120"/>
+      <c r="I16" s="120"/>
+      <c r="J16" s="120"/>
+      <c r="K16" s="120"/>
+      <c r="L16" s="120"/>
+      <c r="M16" s="121"/>
     </row>
     <row r="17" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="104"/>
-      <c r="B17" s="95" t="s">
+      <c r="A17" s="105"/>
+      <c r="B17" s="96" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="106"/>
-      <c r="D17" s="96"/>
-      <c r="E17" s="118"/>
-      <c r="F17" s="119"/>
-      <c r="G17" s="119"/>
-      <c r="H17" s="119"/>
-      <c r="I17" s="119"/>
-      <c r="J17" s="119"/>
-      <c r="K17" s="119"/>
-      <c r="L17" s="119"/>
-      <c r="M17" s="120"/>
+      <c r="C17" s="107"/>
+      <c r="D17" s="97"/>
+      <c r="E17" s="119"/>
+      <c r="F17" s="120"/>
+      <c r="G17" s="120"/>
+      <c r="H17" s="120"/>
+      <c r="I17" s="120"/>
+      <c r="J17" s="120"/>
+      <c r="K17" s="120"/>
+      <c r="L17" s="120"/>
+      <c r="M17" s="121"/>
     </row>
     <row r="18" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="104"/>
-      <c r="B18" s="95" t="s">
+      <c r="A18" s="105"/>
+      <c r="B18" s="96" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="106"/>
-      <c r="D18" s="96"/>
-      <c r="E18" s="118"/>
-      <c r="F18" s="119"/>
-      <c r="G18" s="119"/>
-      <c r="H18" s="119"/>
-      <c r="I18" s="119"/>
-      <c r="J18" s="119"/>
-      <c r="K18" s="119"/>
-      <c r="L18" s="119"/>
-      <c r="M18" s="120"/>
+      <c r="C18" s="107"/>
+      <c r="D18" s="97"/>
+      <c r="E18" s="119"/>
+      <c r="F18" s="120"/>
+      <c r="G18" s="120"/>
+      <c r="H18" s="120"/>
+      <c r="I18" s="120"/>
+      <c r="J18" s="120"/>
+      <c r="K18" s="120"/>
+      <c r="L18" s="120"/>
+      <c r="M18" s="121"/>
     </row>
     <row r="19" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="104"/>
-      <c r="B19" s="95" t="s">
+      <c r="A19" s="105"/>
+      <c r="B19" s="96" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="106"/>
-      <c r="D19" s="96"/>
-      <c r="E19" s="118"/>
-      <c r="F19" s="119"/>
-      <c r="G19" s="119"/>
-      <c r="H19" s="119"/>
-      <c r="I19" s="119"/>
-      <c r="J19" s="119"/>
-      <c r="K19" s="119"/>
-      <c r="L19" s="119"/>
-      <c r="M19" s="120"/>
+      <c r="C19" s="107"/>
+      <c r="D19" s="97"/>
+      <c r="E19" s="119"/>
+      <c r="F19" s="120"/>
+      <c r="G19" s="120"/>
+      <c r="H19" s="120"/>
+      <c r="I19" s="120"/>
+      <c r="J19" s="120"/>
+      <c r="K19" s="120"/>
+      <c r="L19" s="120"/>
+      <c r="M19" s="121"/>
     </row>
     <row r="20" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="104"/>
-      <c r="B20" s="95" t="s">
+      <c r="A20" s="105"/>
+      <c r="B20" s="96" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="106"/>
-      <c r="D20" s="96"/>
-      <c r="E20" s="115"/>
-      <c r="F20" s="116"/>
-      <c r="G20" s="116"/>
-      <c r="H20" s="116"/>
-      <c r="I20" s="116"/>
-      <c r="J20" s="116"/>
-      <c r="K20" s="116"/>
-      <c r="L20" s="116"/>
-      <c r="M20" s="117"/>
+      <c r="C20" s="107"/>
+      <c r="D20" s="97"/>
+      <c r="E20" s="116"/>
+      <c r="F20" s="117"/>
+      <c r="G20" s="117"/>
+      <c r="H20" s="117"/>
+      <c r="I20" s="117"/>
+      <c r="J20" s="117"/>
+      <c r="K20" s="117"/>
+      <c r="L20" s="117"/>
+      <c r="M20" s="118"/>
     </row>
     <row r="21" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="104"/>
-      <c r="B21" s="95" t="s">
+      <c r="A21" s="105"/>
+      <c r="B21" s="96" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="106"/>
-      <c r="D21" s="96"/>
-      <c r="E21" s="115"/>
-      <c r="F21" s="116"/>
-      <c r="G21" s="116"/>
-      <c r="H21" s="116"/>
-      <c r="I21" s="116"/>
-      <c r="J21" s="116"/>
-      <c r="K21" s="116"/>
-      <c r="L21" s="116"/>
-      <c r="M21" s="117"/>
+      <c r="C21" s="107"/>
+      <c r="D21" s="97"/>
+      <c r="E21" s="116"/>
+      <c r="F21" s="117"/>
+      <c r="G21" s="117"/>
+      <c r="H21" s="117"/>
+      <c r="I21" s="117"/>
+      <c r="J21" s="117"/>
+      <c r="K21" s="117"/>
+      <c r="L21" s="117"/>
+      <c r="M21" s="118"/>
     </row>
     <row r="22" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="105"/>
-      <c r="B22" s="95" t="s">
+      <c r="A22" s="106"/>
+      <c r="B22" s="96" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="106"/>
-      <c r="D22" s="96"/>
-      <c r="E22" s="115"/>
-      <c r="F22" s="116"/>
-      <c r="G22" s="116"/>
-      <c r="H22" s="116"/>
-      <c r="I22" s="116"/>
-      <c r="J22" s="116"/>
-      <c r="K22" s="116"/>
-      <c r="L22" s="116"/>
-      <c r="M22" s="117"/>
+      <c r="C22" s="107"/>
+      <c r="D22" s="97"/>
+      <c r="E22" s="116"/>
+      <c r="F22" s="117"/>
+      <c r="G22" s="117"/>
+      <c r="H22" s="117"/>
+      <c r="I22" s="117"/>
+      <c r="J22" s="117"/>
+      <c r="K22" s="117"/>
+      <c r="L22" s="117"/>
+      <c r="M22" s="118"/>
     </row>
     <row r="23" spans="1:13" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="121" t="s">
+      <c r="A23" s="140" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="95" t="s">
+      <c r="B23" s="96" t="s">
         <v>26</v>
       </c>
-      <c r="C23" s="106"/>
-      <c r="D23" s="96"/>
-      <c r="E23" s="122" t="s">
+      <c r="C23" s="107"/>
+      <c r="D23" s="97"/>
+      <c r="E23" s="141" t="s">
         <v>27</v>
       </c>
-      <c r="F23" s="123"/>
-      <c r="G23" s="123"/>
-      <c r="H23" s="123"/>
-      <c r="I23" s="123"/>
-      <c r="J23" s="123"/>
-      <c r="K23" s="123"/>
-      <c r="L23" s="123"/>
-      <c r="M23" s="124"/>
+      <c r="F23" s="142"/>
+      <c r="G23" s="142"/>
+      <c r="H23" s="142"/>
+      <c r="I23" s="142"/>
+      <c r="J23" s="142"/>
+      <c r="K23" s="142"/>
+      <c r="L23" s="142"/>
+      <c r="M23" s="143"/>
     </row>
     <row r="24" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="104"/>
-      <c r="B24" s="95" t="s">
+      <c r="A24" s="105"/>
+      <c r="B24" s="96" t="s">
         <v>19</v>
       </c>
-      <c r="C24" s="106"/>
-      <c r="D24" s="96"/>
-      <c r="E24" s="83"/>
-      <c r="F24" s="84"/>
-      <c r="G24" s="84"/>
-      <c r="H24" s="84"/>
-      <c r="I24" s="84"/>
-      <c r="J24" s="84"/>
-      <c r="K24" s="84"/>
-      <c r="L24" s="84"/>
-      <c r="M24" s="85"/>
+      <c r="C24" s="107"/>
+      <c r="D24" s="97"/>
+      <c r="E24" s="87"/>
+      <c r="F24" s="88"/>
+      <c r="G24" s="88"/>
+      <c r="H24" s="88"/>
+      <c r="I24" s="88"/>
+      <c r="J24" s="88"/>
+      <c r="K24" s="88"/>
+      <c r="L24" s="88"/>
+      <c r="M24" s="89"/>
     </row>
     <row r="25" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="105"/>
-      <c r="B25" s="95" t="s">
+      <c r="A25" s="106"/>
+      <c r="B25" s="96" t="s">
         <v>22</v>
       </c>
-      <c r="C25" s="106"/>
-      <c r="D25" s="96"/>
-      <c r="E25" s="122" t="s">
+      <c r="C25" s="107"/>
+      <c r="D25" s="97"/>
+      <c r="E25" s="141" t="s">
         <v>28</v>
       </c>
-      <c r="F25" s="123"/>
-      <c r="G25" s="123"/>
-      <c r="H25" s="123"/>
-      <c r="I25" s="123"/>
-      <c r="J25" s="123"/>
-      <c r="K25" s="123"/>
-      <c r="L25" s="123"/>
-      <c r="M25" s="124"/>
+      <c r="F25" s="142"/>
+      <c r="G25" s="142"/>
+      <c r="H25" s="142"/>
+      <c r="I25" s="142"/>
+      <c r="J25" s="142"/>
+      <c r="K25" s="142"/>
+      <c r="L25" s="142"/>
+      <c r="M25" s="143"/>
     </row>
     <row r="26" spans="1:13" ht="25.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="95" t="s">
+      <c r="B26" s="96" t="s">
         <v>32</v>
       </c>
-      <c r="C26" s="106"/>
-      <c r="D26" s="96"/>
-      <c r="E26" s="118"/>
-      <c r="F26" s="119"/>
-      <c r="G26" s="119"/>
-      <c r="H26" s="119"/>
-      <c r="I26" s="119"/>
-      <c r="J26" s="119"/>
-      <c r="K26" s="119"/>
-      <c r="L26" s="119"/>
-      <c r="M26" s="120"/>
+      <c r="C26" s="107"/>
+      <c r="D26" s="97"/>
+      <c r="E26" s="119"/>
+      <c r="F26" s="120"/>
+      <c r="G26" s="120"/>
+      <c r="H26" s="120"/>
+      <c r="I26" s="120"/>
+      <c r="J26" s="120"/>
+      <c r="K26" s="120"/>
+      <c r="L26" s="120"/>
+      <c r="M26" s="121"/>
     </row>
     <row r="27" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="95" t="s">
+      <c r="B27" s="96" t="s">
         <v>20</v>
       </c>
-      <c r="C27" s="106"/>
-      <c r="D27" s="96"/>
-      <c r="E27" s="118"/>
-      <c r="F27" s="119"/>
-      <c r="G27" s="119"/>
-      <c r="H27" s="119"/>
-      <c r="I27" s="119"/>
-      <c r="J27" s="119"/>
-      <c r="K27" s="119"/>
-      <c r="L27" s="119"/>
-      <c r="M27" s="120"/>
+      <c r="C27" s="107"/>
+      <c r="D27" s="97"/>
+      <c r="E27" s="119"/>
+      <c r="F27" s="120"/>
+      <c r="G27" s="120"/>
+      <c r="H27" s="120"/>
+      <c r="I27" s="120"/>
+      <c r="J27" s="120"/>
+      <c r="K27" s="120"/>
+      <c r="L27" s="120"/>
+      <c r="M27" s="121"/>
     </row>
     <row r="28" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
-      <c r="B28" s="95" t="s">
+      <c r="B28" s="96" t="s">
         <v>33</v>
       </c>
-      <c r="C28" s="106"/>
-      <c r="D28" s="96"/>
-      <c r="E28" s="118"/>
-      <c r="F28" s="119"/>
-      <c r="G28" s="119"/>
-      <c r="H28" s="119"/>
-      <c r="I28" s="119"/>
-      <c r="J28" s="119"/>
-      <c r="K28" s="119"/>
-      <c r="L28" s="119"/>
-      <c r="M28" s="120"/>
+      <c r="C28" s="107"/>
+      <c r="D28" s="97"/>
+      <c r="E28" s="119"/>
+      <c r="F28" s="120"/>
+      <c r="G28" s="120"/>
+      <c r="H28" s="120"/>
+      <c r="I28" s="120"/>
+      <c r="J28" s="120"/>
+      <c r="K28" s="120"/>
+      <c r="L28" s="120"/>
+      <c r="M28" s="121"/>
     </row>
     <row r="29" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3"/>
-      <c r="B29" s="95" t="s">
+      <c r="B29" s="96" t="s">
         <v>34</v>
       </c>
-      <c r="C29" s="106"/>
-      <c r="D29" s="96"/>
-      <c r="E29" s="118"/>
-      <c r="F29" s="119"/>
-      <c r="G29" s="119"/>
-      <c r="H29" s="119"/>
-      <c r="I29" s="119"/>
-      <c r="J29" s="119"/>
-      <c r="K29" s="119"/>
-      <c r="L29" s="119"/>
-      <c r="M29" s="120"/>
+      <c r="C29" s="107"/>
+      <c r="D29" s="97"/>
+      <c r="E29" s="119"/>
+      <c r="F29" s="120"/>
+      <c r="G29" s="120"/>
+      <c r="H29" s="120"/>
+      <c r="I29" s="120"/>
+      <c r="J29" s="120"/>
+      <c r="K29" s="120"/>
+      <c r="L29" s="120"/>
+      <c r="M29" s="121"/>
     </row>
     <row r="30" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B30" s="95" t="s">
+      <c r="B30" s="96" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="106"/>
-      <c r="D30" s="96"/>
-      <c r="E30" s="118"/>
-      <c r="F30" s="119"/>
-      <c r="G30" s="119"/>
-      <c r="H30" s="119"/>
-      <c r="I30" s="119"/>
-      <c r="J30" s="119"/>
-      <c r="K30" s="119"/>
-      <c r="L30" s="119"/>
-      <c r="M30" s="120"/>
+      <c r="C30" s="107"/>
+      <c r="D30" s="97"/>
+      <c r="E30" s="119"/>
+      <c r="F30" s="120"/>
+      <c r="G30" s="120"/>
+      <c r="H30" s="120"/>
+      <c r="I30" s="120"/>
+      <c r="J30" s="120"/>
+      <c r="K30" s="120"/>
+      <c r="L30" s="120"/>
+      <c r="M30" s="121"/>
     </row>
     <row r="31" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6"/>
-      <c r="B31" s="95" t="s">
+      <c r="B31" s="96" t="s">
         <v>36</v>
       </c>
-      <c r="C31" s="106"/>
-      <c r="D31" s="96"/>
-      <c r="E31" s="118"/>
-      <c r="F31" s="119"/>
-      <c r="G31" s="119"/>
-      <c r="H31" s="119"/>
-      <c r="I31" s="119"/>
-      <c r="J31" s="119"/>
-      <c r="K31" s="119"/>
-      <c r="L31" s="119"/>
-      <c r="M31" s="120"/>
+      <c r="C31" s="107"/>
+      <c r="D31" s="97"/>
+      <c r="E31" s="119"/>
+      <c r="F31" s="120"/>
+      <c r="G31" s="120"/>
+      <c r="H31" s="120"/>
+      <c r="I31" s="120"/>
+      <c r="J31" s="120"/>
+      <c r="K31" s="120"/>
+      <c r="L31" s="120"/>
+      <c r="M31" s="121"/>
     </row>
     <row r="32" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6"/>
-      <c r="B32" s="95" t="s">
+      <c r="B32" s="96" t="s">
         <v>19</v>
       </c>
-      <c r="C32" s="106"/>
-      <c r="D32" s="96"/>
-      <c r="E32" s="115"/>
-      <c r="F32" s="116"/>
-      <c r="G32" s="116"/>
-      <c r="H32" s="116"/>
-      <c r="I32" s="116"/>
-      <c r="J32" s="116"/>
-      <c r="K32" s="116"/>
-      <c r="L32" s="116"/>
-      <c r="M32" s="117"/>
+      <c r="C32" s="107"/>
+      <c r="D32" s="97"/>
+      <c r="E32" s="116"/>
+      <c r="F32" s="117"/>
+      <c r="G32" s="117"/>
+      <c r="H32" s="117"/>
+      <c r="I32" s="117"/>
+      <c r="J32" s="117"/>
+      <c r="K32" s="117"/>
+      <c r="L32" s="117"/>
+      <c r="M32" s="118"/>
     </row>
     <row r="33" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="6"/>
-      <c r="B33" s="95" t="s">
+      <c r="B33" s="96" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="106"/>
-      <c r="D33" s="96"/>
-      <c r="E33" s="118"/>
-      <c r="F33" s="119"/>
-      <c r="G33" s="119"/>
-      <c r="H33" s="119"/>
-      <c r="I33" s="119"/>
-      <c r="J33" s="119"/>
-      <c r="K33" s="119"/>
-      <c r="L33" s="119"/>
-      <c r="M33" s="120"/>
+      <c r="C33" s="107"/>
+      <c r="D33" s="97"/>
+      <c r="E33" s="119"/>
+      <c r="F33" s="120"/>
+      <c r="G33" s="120"/>
+      <c r="H33" s="120"/>
+      <c r="I33" s="120"/>
+      <c r="J33" s="120"/>
+      <c r="K33" s="120"/>
+      <c r="L33" s="120"/>
+      <c r="M33" s="121"/>
     </row>
     <row r="34" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7"/>
-      <c r="B34" s="140" t="s">
+      <c r="B34" s="122" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="141"/>
-      <c r="D34" s="142"/>
-      <c r="E34" s="115"/>
-      <c r="F34" s="116"/>
-      <c r="G34" s="116"/>
-      <c r="H34" s="116"/>
-      <c r="I34" s="116"/>
-      <c r="J34" s="116"/>
-      <c r="K34" s="116"/>
-      <c r="L34" s="116"/>
-      <c r="M34" s="117"/>
+      <c r="C34" s="123"/>
+      <c r="D34" s="124"/>
+      <c r="E34" s="116"/>
+      <c r="F34" s="117"/>
+      <c r="G34" s="117"/>
+      <c r="H34" s="117"/>
+      <c r="I34" s="117"/>
+      <c r="J34" s="117"/>
+      <c r="K34" s="117"/>
+      <c r="L34" s="117"/>
+      <c r="M34" s="118"/>
     </row>
     <row r="35" spans="1:13" ht="25.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
@@ -2481,504 +2473,502 @@
       </c>
       <c r="C35" s="165"/>
       <c r="D35" s="166"/>
-      <c r="E35" s="115"/>
-      <c r="F35" s="116"/>
-      <c r="G35" s="116"/>
-      <c r="H35" s="116"/>
-      <c r="I35" s="116"/>
-      <c r="J35" s="116"/>
-      <c r="K35" s="116"/>
-      <c r="L35" s="116"/>
-      <c r="M35" s="117"/>
+      <c r="E35" s="116"/>
+      <c r="F35" s="117"/>
+      <c r="G35" s="117"/>
+      <c r="H35" s="117"/>
+      <c r="I35" s="117"/>
+      <c r="J35" s="117"/>
+      <c r="K35" s="117"/>
+      <c r="L35" s="117"/>
+      <c r="M35" s="118"/>
     </row>
     <row r="36" spans="1:13" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B36" s="95" t="s">
+      <c r="B36" s="96" t="s">
         <v>42</v>
       </c>
-      <c r="C36" s="106"/>
-      <c r="D36" s="96"/>
-      <c r="E36" s="115"/>
-      <c r="F36" s="116"/>
-      <c r="G36" s="116"/>
-      <c r="H36" s="116"/>
-      <c r="I36" s="116"/>
-      <c r="J36" s="116"/>
-      <c r="K36" s="116"/>
-      <c r="L36" s="116"/>
-      <c r="M36" s="117"/>
+      <c r="C36" s="107"/>
+      <c r="D36" s="97"/>
+      <c r="E36" s="116"/>
+      <c r="F36" s="117"/>
+      <c r="G36" s="117"/>
+      <c r="H36" s="117"/>
+      <c r="I36" s="117"/>
+      <c r="J36" s="117"/>
+      <c r="K36" s="117"/>
+      <c r="L36" s="117"/>
+      <c r="M36" s="118"/>
     </row>
     <row r="37" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="10"/>
-      <c r="B37" s="95" t="s">
+      <c r="B37" s="96" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="106"/>
-      <c r="D37" s="96"/>
-      <c r="E37" s="115"/>
-      <c r="F37" s="116"/>
-      <c r="G37" s="116"/>
-      <c r="H37" s="116"/>
-      <c r="I37" s="116"/>
-      <c r="J37" s="116"/>
-      <c r="K37" s="116"/>
-      <c r="L37" s="116"/>
-      <c r="M37" s="117"/>
+      <c r="C37" s="107"/>
+      <c r="D37" s="97"/>
+      <c r="E37" s="116"/>
+      <c r="F37" s="117"/>
+      <c r="G37" s="117"/>
+      <c r="H37" s="117"/>
+      <c r="I37" s="117"/>
+      <c r="J37" s="117"/>
+      <c r="K37" s="117"/>
+      <c r="L37" s="117"/>
+      <c r="M37" s="118"/>
     </row>
     <row r="38" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="143" t="s">
+      <c r="A38" s="144" t="s">
         <v>43</v>
       </c>
-      <c r="B38" s="143"/>
-      <c r="C38" s="143"/>
-      <c r="D38" s="143"/>
-      <c r="E38" s="143"/>
-      <c r="F38" s="143"/>
-      <c r="G38" s="143"/>
-      <c r="H38" s="143"/>
-      <c r="I38" s="143"/>
-      <c r="J38" s="143"/>
-      <c r="K38" s="143"/>
-      <c r="L38" s="143"/>
-      <c r="M38" s="143"/>
+      <c r="B38" s="144"/>
+      <c r="C38" s="144"/>
+      <c r="D38" s="144"/>
+      <c r="E38" s="144"/>
+      <c r="F38" s="144"/>
+      <c r="G38" s="144"/>
+      <c r="H38" s="144"/>
+      <c r="I38" s="144"/>
+      <c r="J38" s="144"/>
+      <c r="K38" s="144"/>
+      <c r="L38" s="144"/>
+      <c r="M38" s="144"/>
     </row>
     <row r="39" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="143"/>
-      <c r="B39" s="143"/>
-      <c r="C39" s="143"/>
-      <c r="D39" s="143"/>
-      <c r="E39" s="143"/>
-      <c r="F39" s="143"/>
-      <c r="G39" s="143"/>
-      <c r="H39" s="143"/>
-      <c r="I39" s="143"/>
-      <c r="J39" s="143"/>
-      <c r="K39" s="143"/>
-      <c r="L39" s="143"/>
-      <c r="M39" s="143"/>
+      <c r="A39" s="144"/>
+      <c r="B39" s="144"/>
+      <c r="C39" s="144"/>
+      <c r="D39" s="144"/>
+      <c r="E39" s="144"/>
+      <c r="F39" s="144"/>
+      <c r="G39" s="144"/>
+      <c r="H39" s="144"/>
+      <c r="I39" s="144"/>
+      <c r="J39" s="144"/>
+      <c r="K39" s="144"/>
+      <c r="L39" s="144"/>
+      <c r="M39" s="144"/>
     </row>
     <row r="40" spans="1:13" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="143"/>
-      <c r="B40" s="143"/>
-      <c r="C40" s="143"/>
-      <c r="D40" s="143"/>
-      <c r="E40" s="143"/>
-      <c r="F40" s="143"/>
-      <c r="G40" s="143"/>
-      <c r="H40" s="143"/>
-      <c r="I40" s="143"/>
-      <c r="J40" s="143"/>
-      <c r="K40" s="143"/>
-      <c r="L40" s="143"/>
-      <c r="M40" s="143"/>
+      <c r="A40" s="144"/>
+      <c r="B40" s="144"/>
+      <c r="C40" s="144"/>
+      <c r="D40" s="144"/>
+      <c r="E40" s="144"/>
+      <c r="F40" s="144"/>
+      <c r="G40" s="144"/>
+      <c r="H40" s="144"/>
+      <c r="I40" s="144"/>
+      <c r="J40" s="144"/>
+      <c r="K40" s="144"/>
+      <c r="L40" s="144"/>
+      <c r="M40" s="144"/>
     </row>
     <row r="41" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="11"/>
-      <c r="B41" s="68" t="s">
+      <c r="B41" s="72" t="s">
         <v>73</v>
       </c>
-      <c r="C41" s="69"/>
-      <c r="D41" s="69"/>
-      <c r="E41" s="69"/>
-      <c r="F41" s="69"/>
-      <c r="G41" s="69"/>
-      <c r="H41" s="69"/>
-      <c r="I41" s="69"/>
-      <c r="J41" s="70"/>
+      <c r="C41" s="73"/>
+      <c r="D41" s="73"/>
+      <c r="E41" s="73"/>
+      <c r="F41" s="73"/>
+      <c r="G41" s="73"/>
+      <c r="H41" s="73"/>
+      <c r="I41" s="73"/>
+      <c r="J41" s="74"/>
       <c r="K41" s="11"/>
       <c r="L41" s="11"/>
       <c r="M41" s="11"/>
     </row>
     <row r="42" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="11"/>
-      <c r="B42" s="71" t="s">
+      <c r="B42" s="75" t="s">
         <v>72</v>
       </c>
-      <c r="C42" s="150"/>
-      <c r="D42" s="151"/>
-      <c r="E42" s="152"/>
-      <c r="F42" s="153"/>
-      <c r="G42" s="71" t="s">
+      <c r="C42" s="152"/>
+      <c r="D42" s="153"/>
+      <c r="E42" s="154"/>
+      <c r="F42" s="155"/>
+      <c r="G42" s="75" t="s">
         <v>46</v>
       </c>
-      <c r="H42" s="72"/>
-      <c r="I42" s="73"/>
-      <c r="J42" s="77"/>
+      <c r="H42" s="76"/>
+      <c r="I42" s="77"/>
+      <c r="J42" s="81"/>
       <c r="K42" s="11"/>
       <c r="L42" s="11"/>
       <c r="M42" s="11"/>
     </row>
     <row r="43" spans="1:13" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="11"/>
-      <c r="B43" s="38"/>
-      <c r="C43" s="39"/>
-      <c r="D43" s="154"/>
-      <c r="E43" s="155"/>
-      <c r="F43" s="156"/>
-      <c r="G43" s="74" t="s">
+      <c r="B43" s="39"/>
+      <c r="C43" s="40"/>
+      <c r="D43" s="156"/>
+      <c r="E43" s="157"/>
+      <c r="F43" s="158"/>
+      <c r="G43" s="78" t="s">
         <v>44</v>
       </c>
-      <c r="H43" s="75"/>
-      <c r="I43" s="76"/>
-      <c r="J43" s="78"/>
+      <c r="H43" s="79"/>
+      <c r="I43" s="80"/>
+      <c r="J43" s="82"/>
       <c r="K43" s="11"/>
       <c r="L43" s="11"/>
       <c r="M43" s="11"/>
     </row>
     <row r="44" spans="1:13" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="11"/>
-      <c r="B44" s="95" t="s">
+      <c r="B44" s="96" t="s">
         <v>47</v>
       </c>
-      <c r="C44" s="96"/>
+      <c r="C44" s="97"/>
       <c r="D44" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="E44" s="140" t="s">
+      <c r="E44" s="122" t="s">
         <v>48</v>
       </c>
-      <c r="F44" s="141"/>
-      <c r="G44" s="141"/>
-      <c r="H44" s="115"/>
-      <c r="I44" s="116"/>
-      <c r="J44" s="117"/>
+      <c r="F44" s="123"/>
+      <c r="G44" s="123"/>
+      <c r="H44" s="116"/>
+      <c r="I44" s="117"/>
+      <c r="J44" s="118"/>
       <c r="K44" s="11"/>
       <c r="L44" s="11"/>
       <c r="M44" s="11"/>
     </row>
     <row r="45" spans="1:13" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="11"/>
-      <c r="B45" s="79" t="s">
+      <c r="B45" s="83" t="s">
         <v>49</v>
       </c>
-      <c r="C45" s="80"/>
-      <c r="D45" s="81"/>
-      <c r="E45" s="81"/>
-      <c r="F45" s="81"/>
-      <c r="G45" s="81"/>
-      <c r="H45" s="80"/>
-      <c r="I45" s="80"/>
-      <c r="J45" s="82"/>
+      <c r="C45" s="84"/>
+      <c r="D45" s="85"/>
+      <c r="E45" s="85"/>
+      <c r="F45" s="85"/>
+      <c r="G45" s="85"/>
+      <c r="H45" s="84"/>
+      <c r="I45" s="84"/>
+      <c r="J45" s="86"/>
       <c r="K45" s="11"/>
       <c r="L45" s="11"/>
       <c r="M45" s="11"/>
     </row>
     <row r="46" spans="1:13" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="11"/>
-      <c r="B46" s="50" t="s">
+      <c r="B46" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="C46" s="51"/>
-      <c r="D46" s="54" t="s">
+      <c r="C46" s="52"/>
+      <c r="D46" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="E46" s="55"/>
-      <c r="F46" s="55"/>
-      <c r="G46" s="56"/>
-      <c r="H46" s="57" t="s">
+      <c r="E46" s="56"/>
+      <c r="F46" s="56"/>
+      <c r="G46" s="57"/>
+      <c r="H46" s="58" t="s">
         <v>52</v>
       </c>
-      <c r="I46" s="58"/>
-      <c r="J46" s="59"/>
+      <c r="I46" s="59"/>
+      <c r="J46" s="60"/>
       <c r="K46" s="11"/>
       <c r="L46" s="11"/>
       <c r="M46" s="11"/>
     </row>
     <row r="47" spans="1:13" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="11"/>
-      <c r="B47" s="52"/>
-      <c r="C47" s="53"/>
-      <c r="D47" s="63" t="s">
+      <c r="B47" s="53"/>
+      <c r="C47" s="54"/>
+      <c r="D47" s="64" t="s">
         <v>53</v>
       </c>
-      <c r="E47" s="64"/>
-      <c r="F47" s="63" t="s">
+      <c r="E47" s="65"/>
+      <c r="F47" s="64" t="s">
         <v>54</v>
       </c>
-      <c r="G47" s="64"/>
-      <c r="H47" s="60"/>
-      <c r="I47" s="61"/>
-      <c r="J47" s="62"/>
+      <c r="G47" s="65"/>
+      <c r="H47" s="61"/>
+      <c r="I47" s="62"/>
+      <c r="J47" s="63"/>
       <c r="K47" s="11"/>
       <c r="L47" s="11"/>
       <c r="M47" s="11"/>
     </row>
     <row r="48" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="15"/>
-      <c r="B48" s="31" t="s">
+      <c r="B48" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="C48" s="32"/>
-      <c r="D48" s="33"/>
-      <c r="E48" s="34"/>
-      <c r="F48" s="33"/>
-      <c r="G48" s="34"/>
-      <c r="H48" s="65"/>
-      <c r="I48" s="66"/>
-      <c r="J48" s="67"/>
+      <c r="C48" s="33"/>
+      <c r="D48" s="34"/>
+      <c r="E48" s="35"/>
+      <c r="F48" s="34"/>
+      <c r="G48" s="35"/>
+      <c r="H48" s="66"/>
+      <c r="I48" s="67"/>
+      <c r="J48" s="68"/>
       <c r="K48" s="15"/>
       <c r="L48" s="15"/>
       <c r="M48" s="15"/>
     </row>
     <row r="49" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="15"/>
-      <c r="B49" s="31" t="s">
+      <c r="B49" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="C49" s="32"/>
-      <c r="D49" s="33"/>
-      <c r="E49" s="34"/>
-      <c r="F49" s="157"/>
-      <c r="G49" s="158"/>
-      <c r="H49" s="40"/>
-      <c r="I49" s="41"/>
-      <c r="J49" s="42"/>
+      <c r="C49" s="33"/>
+      <c r="D49" s="34"/>
+      <c r="E49" s="35"/>
+      <c r="F49" s="34"/>
+      <c r="G49" s="35"/>
+      <c r="H49" s="41"/>
+      <c r="I49" s="42"/>
+      <c r="J49" s="43"/>
       <c r="K49" s="15"/>
       <c r="L49" s="15"/>
       <c r="M49" s="15"/>
     </row>
     <row r="50" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="15"/>
-      <c r="B50" s="31" t="s">
+      <c r="B50" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="C50" s="32"/>
-      <c r="D50" s="33"/>
-      <c r="E50" s="34"/>
-      <c r="F50" s="33"/>
-      <c r="G50" s="34"/>
-      <c r="H50" s="40"/>
-      <c r="I50" s="41"/>
-      <c r="J50" s="42"/>
+      <c r="C50" s="33"/>
+      <c r="D50" s="34"/>
+      <c r="E50" s="35"/>
+      <c r="H50" s="41"/>
+      <c r="I50" s="42"/>
+      <c r="J50" s="43"/>
       <c r="K50" s="15"/>
       <c r="L50" s="15"/>
       <c r="M50" s="15"/>
     </row>
     <row r="51" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="15"/>
-      <c r="B51" s="38" t="s">
+      <c r="B51" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="C51" s="39"/>
-      <c r="D51" s="90"/>
-      <c r="E51" s="91"/>
-      <c r="F51" s="90"/>
-      <c r="G51" s="91"/>
-      <c r="H51" s="92"/>
-      <c r="I51" s="93"/>
-      <c r="J51" s="94"/>
+      <c r="C51" s="40"/>
+      <c r="D51" s="94"/>
+      <c r="E51" s="95"/>
+      <c r="F51" s="94"/>
+      <c r="G51" s="95"/>
+      <c r="H51" s="69"/>
+      <c r="I51" s="70"/>
+      <c r="J51" s="71"/>
       <c r="K51" s="15"/>
       <c r="L51" s="15"/>
       <c r="M51" s="15"/>
     </row>
     <row r="52" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="15"/>
-      <c r="B52" s="31" t="s">
+      <c r="B52" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="C52" s="32"/>
-      <c r="D52" s="33"/>
-      <c r="E52" s="34"/>
-      <c r="F52" s="33"/>
-      <c r="G52" s="34"/>
-      <c r="H52" s="35"/>
-      <c r="I52" s="36"/>
-      <c r="J52" s="37"/>
+      <c r="C52" s="33"/>
+      <c r="D52" s="34"/>
+      <c r="E52" s="35"/>
+      <c r="F52" s="34"/>
+      <c r="G52" s="35"/>
+      <c r="H52" s="36"/>
+      <c r="I52" s="37"/>
+      <c r="J52" s="38"/>
       <c r="K52" s="15"/>
       <c r="L52" s="15"/>
       <c r="M52" s="15"/>
     </row>
     <row r="53" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="15"/>
-      <c r="B53" s="31" t="s">
+      <c r="B53" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="C53" s="32"/>
-      <c r="D53" s="33"/>
-      <c r="E53" s="34"/>
-      <c r="F53" s="33"/>
-      <c r="G53" s="34"/>
-      <c r="H53" s="40"/>
-      <c r="I53" s="41"/>
-      <c r="J53" s="42"/>
+      <c r="C53" s="33"/>
+      <c r="D53" s="34"/>
+      <c r="E53" s="35"/>
+      <c r="F53" s="34"/>
+      <c r="G53" s="35"/>
+      <c r="H53" s="41"/>
+      <c r="I53" s="42"/>
+      <c r="J53" s="43"/>
       <c r="K53" s="15"/>
       <c r="L53" s="15"/>
       <c r="M53" s="15"/>
     </row>
     <row r="54" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="15"/>
-      <c r="B54" s="31" t="s">
+      <c r="B54" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="C54" s="32"/>
-      <c r="D54" s="33"/>
-      <c r="E54" s="34"/>
-      <c r="F54" s="33"/>
-      <c r="G54" s="34"/>
-      <c r="H54" s="40"/>
-      <c r="I54" s="41"/>
-      <c r="J54" s="42"/>
+      <c r="C54" s="33"/>
+      <c r="D54" s="34"/>
+      <c r="E54" s="35"/>
+      <c r="F54" s="34"/>
+      <c r="G54" s="35"/>
+      <c r="H54" s="41"/>
+      <c r="I54" s="42"/>
+      <c r="J54" s="43"/>
       <c r="K54" s="15"/>
       <c r="L54" s="15"/>
       <c r="M54" s="15"/>
     </row>
     <row r="55" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="15"/>
-      <c r="B55" s="43" t="s">
+      <c r="B55" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="C55" s="44"/>
-      <c r="D55" s="45"/>
-      <c r="E55" s="46"/>
-      <c r="F55" s="45"/>
-      <c r="G55" s="46"/>
-      <c r="H55" s="47"/>
-      <c r="I55" s="48"/>
-      <c r="J55" s="49"/>
+      <c r="C55" s="45"/>
+      <c r="D55" s="46"/>
+      <c r="E55" s="47"/>
+      <c r="F55" s="46"/>
+      <c r="G55" s="47"/>
+      <c r="H55" s="48"/>
+      <c r="I55" s="49"/>
+      <c r="J55" s="50"/>
       <c r="K55" s="15"/>
       <c r="L55" s="15"/>
       <c r="M55" s="15"/>
     </row>
     <row r="56" spans="1:13" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="15"/>
-      <c r="B56" s="88" t="s">
+      <c r="B56" s="92" t="s">
         <v>62</v>
       </c>
-      <c r="C56" s="81"/>
-      <c r="D56" s="81"/>
-      <c r="E56" s="81"/>
-      <c r="F56" s="81"/>
-      <c r="G56" s="81"/>
-      <c r="H56" s="81"/>
-      <c r="I56" s="81"/>
-      <c r="J56" s="89"/>
+      <c r="C56" s="85"/>
+      <c r="D56" s="85"/>
+      <c r="E56" s="85"/>
+      <c r="F56" s="85"/>
+      <c r="G56" s="85"/>
+      <c r="H56" s="85"/>
+      <c r="I56" s="85"/>
+      <c r="J56" s="93"/>
       <c r="K56" s="15"/>
       <c r="L56" s="15"/>
       <c r="M56" s="15"/>
     </row>
     <row r="57" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="15"/>
-      <c r="B57" s="57" t="s">
+      <c r="B57" s="58" t="s">
         <v>50</v>
       </c>
-      <c r="C57" s="59"/>
-      <c r="D57" s="83" t="s">
+      <c r="C57" s="60"/>
+      <c r="D57" s="87" t="s">
         <v>51</v>
       </c>
-      <c r="E57" s="84"/>
-      <c r="F57" s="84"/>
-      <c r="G57" s="85"/>
-      <c r="H57" s="57" t="s">
+      <c r="E57" s="88"/>
+      <c r="F57" s="88"/>
+      <c r="G57" s="89"/>
+      <c r="H57" s="58" t="s">
         <v>52</v>
       </c>
-      <c r="I57" s="58"/>
-      <c r="J57" s="59"/>
+      <c r="I57" s="59"/>
+      <c r="J57" s="60"/>
       <c r="K57" s="15"/>
       <c r="L57" s="15"/>
       <c r="M57" s="15"/>
     </row>
     <row r="58" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="15"/>
-      <c r="B58" s="60"/>
-      <c r="C58" s="62"/>
-      <c r="D58" s="86" t="s">
+      <c r="B58" s="61"/>
+      <c r="C58" s="63"/>
+      <c r="D58" s="90" t="s">
         <v>53</v>
       </c>
-      <c r="E58" s="87"/>
-      <c r="F58" s="86" t="s">
+      <c r="E58" s="91"/>
+      <c r="F58" s="90" t="s">
         <v>54</v>
       </c>
-      <c r="G58" s="87"/>
-      <c r="H58" s="60"/>
-      <c r="I58" s="61"/>
-      <c r="J58" s="62"/>
+      <c r="G58" s="91"/>
+      <c r="H58" s="61"/>
+      <c r="I58" s="62"/>
+      <c r="J58" s="63"/>
       <c r="K58" s="15"/>
       <c r="L58" s="15"/>
       <c r="M58" s="15"/>
     </row>
     <row r="59" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="15"/>
-      <c r="B59" s="31" t="s">
+      <c r="B59" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="C59" s="32"/>
-      <c r="D59" s="33"/>
-      <c r="E59" s="34"/>
-      <c r="F59" s="33"/>
-      <c r="G59" s="34"/>
-      <c r="H59" s="35"/>
-      <c r="I59" s="36"/>
-      <c r="J59" s="37"/>
+      <c r="C59" s="33"/>
+      <c r="D59" s="34"/>
+      <c r="E59" s="35"/>
+      <c r="F59" s="34"/>
+      <c r="G59" s="35"/>
+      <c r="H59" s="36"/>
+      <c r="I59" s="37"/>
+      <c r="J59" s="38"/>
       <c r="K59" s="15"/>
       <c r="L59" s="15"/>
       <c r="M59" s="15"/>
     </row>
     <row r="60" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="15"/>
-      <c r="B60" s="31" t="s">
+      <c r="B60" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="C60" s="32"/>
-      <c r="D60" s="33"/>
-      <c r="E60" s="34"/>
-      <c r="F60" s="33"/>
-      <c r="G60" s="34"/>
-      <c r="H60" s="35"/>
-      <c r="I60" s="36"/>
-      <c r="J60" s="37"/>
+      <c r="C60" s="33"/>
+      <c r="D60" s="34"/>
+      <c r="E60" s="35"/>
+      <c r="F60" s="34"/>
+      <c r="G60" s="35"/>
+      <c r="H60" s="36"/>
+      <c r="I60" s="37"/>
+      <c r="J60" s="38"/>
       <c r="K60" s="15"/>
       <c r="L60" s="15"/>
       <c r="M60" s="15"/>
     </row>
     <row r="61" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="15"/>
-      <c r="B61" s="31" t="s">
+      <c r="B61" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="C61" s="32"/>
-      <c r="D61" s="33"/>
-      <c r="E61" s="34"/>
-      <c r="F61" s="33"/>
-      <c r="G61" s="34"/>
-      <c r="H61" s="35"/>
-      <c r="I61" s="36"/>
-      <c r="J61" s="37"/>
+      <c r="C61" s="33"/>
+      <c r="D61" s="34"/>
+      <c r="E61" s="35"/>
+      <c r="F61" s="34"/>
+      <c r="G61" s="35"/>
+      <c r="H61" s="36"/>
+      <c r="I61" s="37"/>
+      <c r="J61" s="38"/>
       <c r="K61" s="15"/>
       <c r="L61" s="15"/>
       <c r="M61" s="15"/>
     </row>
     <row r="62" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="15"/>
-      <c r="B62" s="31" t="s">
+      <c r="B62" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="C62" s="32"/>
-      <c r="D62" s="33"/>
-      <c r="E62" s="34"/>
-      <c r="F62" s="33"/>
-      <c r="G62" s="34"/>
-      <c r="H62" s="35"/>
-      <c r="I62" s="36"/>
-      <c r="J62" s="37"/>
+      <c r="C62" s="33"/>
+      <c r="D62" s="34"/>
+      <c r="E62" s="35"/>
+      <c r="F62" s="34"/>
+      <c r="G62" s="35"/>
+      <c r="H62" s="36"/>
+      <c r="I62" s="37"/>
+      <c r="J62" s="38"/>
       <c r="K62" s="15"/>
       <c r="L62" s="15"/>
       <c r="M62" s="15"/>
     </row>
     <row r="63" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="15"/>
-      <c r="B63" s="31" t="s">
+      <c r="B63" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="C63" s="32"/>
-      <c r="D63" s="33"/>
-      <c r="E63" s="34"/>
-      <c r="F63" s="33"/>
-      <c r="G63" s="34"/>
-      <c r="H63" s="35"/>
-      <c r="I63" s="36"/>
-      <c r="J63" s="37"/>
+      <c r="C63" s="33"/>
+      <c r="D63" s="34"/>
+      <c r="E63" s="35"/>
+      <c r="F63" s="34"/>
+      <c r="G63" s="35"/>
+      <c r="H63" s="36"/>
+      <c r="I63" s="37"/>
+      <c r="J63" s="38"/>
       <c r="K63" s="15"/>
       <c r="L63" s="15"/>
       <c r="M63" s="15"/>
@@ -3009,15 +2999,15 @@
     </row>
     <row r="66" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="11"/>
-      <c r="B66" s="168"/>
-      <c r="C66" s="168"/>
-      <c r="D66" s="168"/>
-      <c r="E66" s="168"/>
-      <c r="F66" s="168"/>
-      <c r="G66" s="168"/>
-      <c r="H66" s="168"/>
-      <c r="I66" s="168"/>
-      <c r="J66" s="168"/>
+      <c r="B66" s="149"/>
+      <c r="C66" s="149"/>
+      <c r="D66" s="149"/>
+      <c r="E66" s="149"/>
+      <c r="F66" s="149"/>
+      <c r="G66" s="149"/>
+      <c r="H66" s="149"/>
+      <c r="I66" s="149"/>
+      <c r="J66" s="149"/>
       <c r="K66" s="11"/>
       <c r="L66" s="11"/>
       <c r="M66" s="11"/>
@@ -3033,15 +3023,15 @@
     </row>
     <row r="68" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="11"/>
-      <c r="B68" s="149"/>
-      <c r="C68" s="149"/>
-      <c r="D68" s="149"/>
-      <c r="E68" s="149"/>
-      <c r="F68" s="149"/>
-      <c r="G68" s="149"/>
-      <c r="H68" s="149"/>
-      <c r="I68" s="149"/>
-      <c r="J68" s="149"/>
+      <c r="B68" s="150"/>
+      <c r="C68" s="150"/>
+      <c r="D68" s="150"/>
+      <c r="E68" s="150"/>
+      <c r="F68" s="150"/>
+      <c r="G68" s="150"/>
+      <c r="H68" s="150"/>
+      <c r="I68" s="150"/>
+      <c r="J68" s="150"/>
       <c r="K68" s="11"/>
       <c r="L68" s="11"/>
       <c r="M68" s="11"/>
@@ -3057,15 +3047,15 @@
     </row>
     <row r="70" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="11"/>
-      <c r="B70" s="148"/>
-      <c r="C70" s="148"/>
-      <c r="D70" s="148"/>
-      <c r="E70" s="148"/>
-      <c r="F70" s="148"/>
-      <c r="G70" s="148"/>
-      <c r="H70" s="148"/>
-      <c r="I70" s="148"/>
-      <c r="J70" s="148"/>
+      <c r="B70" s="151"/>
+      <c r="C70" s="151"/>
+      <c r="D70" s="151"/>
+      <c r="E70" s="151"/>
+      <c r="F70" s="151"/>
+      <c r="G70" s="151"/>
+      <c r="H70" s="151"/>
+      <c r="I70" s="151"/>
+      <c r="J70" s="151"/>
       <c r="K70" s="11"/>
       <c r="L70" s="11"/>
       <c r="M70" s="11"/>
@@ -3194,24 +3184,24 @@
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" s="13"/>
-      <c r="C79" s="144"/>
-      <c r="D79" s="144"/>
-      <c r="E79" s="144"/>
-      <c r="F79" s="144"/>
-      <c r="G79" s="144"/>
-      <c r="H79" s="144"/>
-      <c r="I79" s="144"/>
-      <c r="J79" s="144"/>
+      <c r="C79" s="145"/>
+      <c r="D79" s="145"/>
+      <c r="E79" s="145"/>
+      <c r="F79" s="145"/>
+      <c r="G79" s="145"/>
+      <c r="H79" s="145"/>
+      <c r="I79" s="145"/>
+      <c r="J79" s="145"/>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="F80" s="23" t="s">
+      <c r="F80" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="G80" s="23"/>
+      <c r="G80" s="24"/>
     </row>
     <row r="81" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="166">
+  <mergeCells count="165">
     <mergeCell ref="F80:G80"/>
     <mergeCell ref="A38:M40"/>
     <mergeCell ref="C79:J79"/>
@@ -3224,7 +3214,6 @@
     <mergeCell ref="B44:C44"/>
     <mergeCell ref="E44:G44"/>
     <mergeCell ref="H44:J44"/>
-    <mergeCell ref="F49:G49"/>
     <mergeCell ref="A77:D77"/>
     <mergeCell ref="E77:F77"/>
     <mergeCell ref="G77:H77"/>
@@ -3258,6 +3247,8 @@
     <mergeCell ref="E23:M23"/>
     <mergeCell ref="E24:M24"/>
     <mergeCell ref="E25:M25"/>
+    <mergeCell ref="E21:M21"/>
+    <mergeCell ref="E22:M22"/>
     <mergeCell ref="B36:D36"/>
     <mergeCell ref="B37:D37"/>
     <mergeCell ref="E35:M35"/>
@@ -3267,8 +3258,6 @@
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="E33:M33"/>
     <mergeCell ref="E34:M34"/>
-    <mergeCell ref="E21:M21"/>
-    <mergeCell ref="E22:M22"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="B19:D19"/>
@@ -3283,7 +3272,7 @@
     <mergeCell ref="E27:M27"/>
     <mergeCell ref="E28:M28"/>
     <mergeCell ref="D50:E50"/>
-    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="F49:G49"/>
     <mergeCell ref="H50:J50"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A10:B10"/>
@@ -3379,9 +3368,9 @@
     <mergeCell ref="B62:C62"/>
     <mergeCell ref="D62:E62"/>
   </mergeCells>
-  <conditionalFormatting sqref="A77:D77 K77:M77 C79:J79">
+  <conditionalFormatting sqref="A77:D77 K77:M77 C79:J79 D51:J55 D50:E50 H50:J50 D48:J49">
     <cfRule type="containsBlanks" dxfId="5" priority="2">
-      <formula>LEN(TRIM(A77))=0</formula>
+      <formula>LEN(TRIM(A48))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A77:D77">
@@ -3394,7 +3383,7 @@
       <formula>LEN(TRIM(C79))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D42:F43 J42:J43 D48:J55 D59:J63 B68:J68 B70:J70">
+  <conditionalFormatting sqref="D42:F43 J42:J43 D59:J63 B68:J68 B70:J70">
     <cfRule type="containsBlanks" dxfId="2" priority="1">
       <formula>LEN(TRIM(B42))=0</formula>
     </cfRule>
@@ -3409,7 +3398,7 @@
       <formula>LEN(TRIM(K77))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="48">
+  <dataValidations count="47">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Indicar el nivel formativo en el cual se encuentra el aprendiz. Técnio o Tecnólogo" sqref="I10:M10" xr:uid="{FDFD4240-B4E4-40FA-8880-3E4E045C5084}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Registrar el nombre del programa" prompt="Registrar el nombre del programa" sqref="C11:H11" xr:uid="{34EF5BAD-650F-4FA7-AB25-B4A5694BB4C0}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Número Ficha" prompt="Registre el número de ficha en el que se encuentra matriculado según el programa de formación." sqref="K11:M11" xr:uid="{C295E52F-E427-4103-89DB-18FF195E95C6}"/>
@@ -3422,7 +3411,7 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el correo electrónico personal del aprendiz" sqref="E19:M19" xr:uid="{CEDF05F3-A498-464C-AF78-C83490E95D67}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el correo electrónico institucional del aprendiz @sena.edu.co , @soysena.edu.co" sqref="E20:M20" xr:uid="{8AC0CC91-D06D-4D82-A06B-CEDFF66185FC}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el nombre de la alternativa de etapa productiva, de acuerdo con las alternativas descritas en el reglamento del aprendiz vigente" sqref="E21:M21" xr:uid="{48CA359C-CBBE-4B45-B681-EA4693D12177}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Indicar la fecha en que quedó registrada la alternativa en el aplicativo SofiaPlus.  Gestione con la coordinación académica el reporte del SVP para obtener la información requerida en este apartado" sqref="E22:M22" xr:uid="{A4B53DE5-4CEE-4C8C-A08B-9C6344C18954}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="OBLIGATORIO" prompt="Indicar la fecha de registro en el aplicativo SofiaPlus. RUTA: INGRESAR A SOFIAPLUS-APRENDIZ-CONSULTAR INSCRIPCIONES A PROGRAMAS...----DETALLE DE INSCRIPCION // PARTE INFWERIOR INDICA LA FECHA DE INSCRIPCION" sqref="E22:M22" xr:uid="{A4B53DE5-4CEE-4C8C-A08B-9C6344C18954}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el nombre completo de la empresa o entidad co-formadora (empresa, entidad o institución gubernamental o no gubernamental)." sqref="E26:M26" xr:uid="{35AC5BC6-659F-4E4C-B567-3C3F16C509BD}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar la dirección de la empresa, entidad o institución gubernamental o no gubernamental." sqref="E27:M27" xr:uid="{18FD205E-10DD-4EB5-8E57-F8B0C00BF5BC}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar el numero NIT de la empresa, entidad o institución gubernamental o no gubernamental." sqref="E28:M28" xr:uid="{0E9499EA-A21D-4209-94F0-6561C0BEA458}"/>
@@ -3435,15 +3424,14 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Si no aplica colocar N/A" prompt="En caso de que el aprendiz sea una persona en situación de discapacidad, diligencie este espacio con el nombre de la persona que le asiste." sqref="E35:M35" xr:uid="{C19946D2-B571-4104-A1EA-FEF5A7253596}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Si no aplica colocar N/A" prompt="Aquí se especifica el tipo de asistencia brindada al aprendiz para que desempeñe la totalidad de sus tareas asegurando un ambiente laboral inclusivo adecuado a sus necesidades. Puede incluir asistencias como lenguaje de señas, soporte visual etc" sqref="E36:M36" xr:uid="{B635F5F5-108B-409C-BCAD-0AA5A654CF02}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Si no aplica colocar N/A" prompt="Registrar el número del celular de la persona que asiste al aprendiz " sqref="E37:M37" xr:uid="{77AEF51E-4966-4ADA-B94D-7E72C6BE4FFA}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="OBLIGATORIO" prompt="Registrar el nombre completo del aprendiz y en la parte superior la Firma manuscrita o digital." sqref="A77:D77" xr:uid="{A7FEFB2B-7370-4FA2-8820-7EB89B730FD1}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="OBLIGATORIO" prompt="Registrar el nombre completo del co-formador y en la parte superior de esta la Firma manuscrita o digital." sqref="K77:M77" xr:uid="{DAE2A968-2309-42D5-952C-BC599D7BE50F}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="OBLIGATORIO NOMBRE Y FIRMA APREN" prompt="Registrar el nombre completo del aprendiz y en la parte superior la Firma manuscrita o digital." sqref="A77:D77" xr:uid="{A7FEFB2B-7370-4FA2-8820-7EB89B730FD1}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="OBLIGATORIO NOMBRE Y FIRMA JEFE" prompt="Registrar el nombre completo del co-formador y en la parte superior de esta la Firma manuscrita o digital." sqref="K77:M77" xr:uid="{DAE2A968-2309-42D5-952C-BC599D7BE50F}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Bogotá dd/mm/aaaa Virtual" prompt="Diligenciar fecha de la sesión en este espacio. Ejemplo: Bogotá dia/mes/año Virtual" sqref="C79:J79" xr:uid="{201095D8-80DA-45BB-84F9-D066E44DB3C5}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registre la fecha en que el aprendiz dio inicio a su etapa productiva." sqref="D42:F43" xr:uid="{91ABAF52-821D-4DE8-B0C2-245C3EFA4EAC}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registre la fecha en que se realizó el momento de planeación de la etapa productiva. FCHA DE LA SESION" sqref="J42:J43" xr:uid="{54F15547-5AB5-4314-88CB-73760EC82315}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Adjuntar enlace de la video llamada" sqref="H44:J44" xr:uid="{B1F72570-FBB0-43D7-BC61-1C17B377356B}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Aporta activamente al mejoramiento de sus habilidades técnicas y métodos de trabajo." sqref="D49:F49" xr:uid="{A8FCB973-8FC0-4BDD-BF0E-CC9BB61BE366}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Aporta activamente al mejoramiento de sus habilidades técnicas y métodos de trabajo." sqref="D49:E49" xr:uid="{A8FCB973-8FC0-4BDD-BF0E-CC9BB61BE366}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Marcar con una X según correspon" prompt="Demuestra las competencias específicas del programa de formación en situaciones reales de trabajo. " sqref="D48:G48" xr:uid="{948FA747-4CF8-48C4-8768-F9CADBC3F362}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Realiza acciones que fortalezcan su perfil ocupacional potenciando sus competencias en el marco de su proyecto de vida." sqref="D50:G50" xr:uid="{379961D4-6BD4-47A0-B009-E49C8B35A883}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Presenta con oportunidad y calidad los productos generados en el desarrollo de sus actividades." sqref="D51:G51" xr:uid="{19539D16-ED2B-4BF9-A64A-1332E00D8693}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Administra los recursos para el desarrollo de sus actividades con criterios de responsabilidad ambiental." sqref="D52:G52" xr:uid="{2B7AA1E4-5959-4E7A-871B-23982F85D610}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Utiliza de manera racional los materiales, equipos y herramientas suministrados para el desempeño de sus actividades." sqref="D53:G53" xr:uid="{3DAD6ADF-7EDC-428E-A36E-3CB7EE1A10E7}"/>
@@ -3454,17 +3442,17 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Propone alternativas de solución a situaciones problemáticas, en el contexto del desarrollo de su etapa productiva. " sqref="D61:G61" xr:uid="{8CFCA47A-7FFB-4C81-B160-32FC56FE753D}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Es comprometido con las actividades asignadas y con la empresa, demostrando puntualidad, proactividad y buena presentación personal en el desarrollo de su etapa productiva" sqref="D62:G62" xr:uid="{C5D9BB00-F014-4DE5-B59C-090440CDA5FD}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Demuestra capacidad para ordenar y disponer los elementos necesarios e información que facilite la ejecución del trabajo y el logro de los objetivos." sqref="D63:G63" xr:uid="{B8588CD4-9B9C-4123-8FA4-B0191CFB9CEA}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="OBLIGATORIO" prompt="Registrar de manera objetiva y concisa la información adicional que complemente el proceso de acompañamiento al aprendiz en su etapa productiva." sqref="B70:J70" xr:uid="{D7E55FAF-6FC8-4AC1-A902-F35811C9DD3B}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="OBLIGATORIO" prompt="Registrar de manera objetiva y concisa la información adicional que complemente el proceso de acompañamiento al aprendiz en su etapa productiva." sqref="B68:J68" xr:uid="{B24B5D0A-E15D-45FB-8DD6-CE569B75705D}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="OBLIGATORIO" prompt="Registrar de manera objetiva y concisa la información adicional que complemente el proceso de acompañamiento al aprendiz en su etapa productiva." sqref="B70:J70 B68:J68" xr:uid="{D7E55FAF-6FC8-4AC1-A902-F35811C9DD3B}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="DILIGENCIAR SI HAY POR MEJORAR" prompt="Si hay factores por mejorar favor escribir las observaciones o los compromisos de mejora" sqref="H48:J55" xr:uid="{70C7BBAF-F2BE-4776-BA55-57FE0807C14D}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Diligenciar si hay por mejorar" prompt="Si hay factores por mejorar favor escribir las observaciones o los compromisos de mejora" sqref="H59:J63" xr:uid="{56231F2E-9BAE-4742-84BB-A6BBFCFB029F}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Realiza acciones que fortalezcan su perfil ocupacional potenciando sus competencias en el marco de su proyecto de vida." sqref="D50:E50 F49:G49" xr:uid="{379961D4-6BD4-47A0-B009-E49C8B35A883}"/>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="5" scale="68" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Registrar las correspondientes observaciones para cada variable sea del co-formador, instructor de seguimiento y del aprendiz, si es del caso" xr:uid="{8831A1A9-AB8B-443F-901C-833E895B3B1F}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8831A1A9-AB8B-443F-901C-833E895B3B1F}">
           <x14:formula1>
             <xm:f>Hoja2!$A$1:$A$9</xm:f>
           </x14:formula1>
@@ -3485,47 +3473,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A1" s="167" t="s">
+      <c r="A1" s="19" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A2" s="167" t="s">
+      <c r="A2" s="19" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A3" s="167" t="s">
+      <c r="A3" s="19" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="167" t="s">
+      <c r="A4" s="19" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A5" s="167" t="s">
+      <c r="A5" s="19" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="167" t="s">
+      <c r="A6" s="19" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A7" s="167" t="s">
+      <c r="A7" s="19" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A8" s="167" t="s">
+      <c r="A8" s="19" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="167" t="s">
+      <c r="A9" s="19" t="s">
         <v>90</v>
       </c>
     </row>

--- a/Formatos/Visita 2 GFPI-F023.xlsx
+++ b/Formatos/Visita 2 GFPI-F023.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SEANT\OneDrive\Documents\Seto 2026\sena\Manual SENA Etapa Productiva\manual-aprendiz-sena\Formatos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0630D33E-B5D0-4F12-A43A-9112395366C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37FB8EBA-F1E6-4458-A15B-89CCBCFED77A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{BC3553EE-4E49-4F2A-B03E-CFAC4EB3009B}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{BC3553EE-4E49-4F2A-B03E-CFAC4EB3009B}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -1293,18 +1293,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1313,6 +1301,18 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1494,7 +1494,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1508,7 +1508,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="8" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2102,15 +2102,15 @@
       </c>
       <c r="C14" s="107"/>
       <c r="D14" s="97"/>
-      <c r="E14" s="119"/>
-      <c r="F14" s="120"/>
-      <c r="G14" s="120"/>
-      <c r="H14" s="120"/>
-      <c r="I14" s="120"/>
-      <c r="J14" s="120"/>
-      <c r="K14" s="120"/>
-      <c r="L14" s="120"/>
-      <c r="M14" s="121"/>
+      <c r="E14" s="122"/>
+      <c r="F14" s="123"/>
+      <c r="G14" s="123"/>
+      <c r="H14" s="123"/>
+      <c r="I14" s="123"/>
+      <c r="J14" s="123"/>
+      <c r="K14" s="123"/>
+      <c r="L14" s="123"/>
+      <c r="M14" s="124"/>
     </row>
     <row r="15" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="105"/>
@@ -2136,15 +2136,15 @@
       </c>
       <c r="C16" s="107"/>
       <c r="D16" s="97"/>
-      <c r="E16" s="119"/>
-      <c r="F16" s="120"/>
-      <c r="G16" s="120"/>
-      <c r="H16" s="120"/>
-      <c r="I16" s="120"/>
-      <c r="J16" s="120"/>
-      <c r="K16" s="120"/>
-      <c r="L16" s="120"/>
-      <c r="M16" s="121"/>
+      <c r="E16" s="122"/>
+      <c r="F16" s="123"/>
+      <c r="G16" s="123"/>
+      <c r="H16" s="123"/>
+      <c r="I16" s="123"/>
+      <c r="J16" s="123"/>
+      <c r="K16" s="123"/>
+      <c r="L16" s="123"/>
+      <c r="M16" s="124"/>
     </row>
     <row r="17" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="105"/>
@@ -2153,15 +2153,15 @@
       </c>
       <c r="C17" s="107"/>
       <c r="D17" s="97"/>
-      <c r="E17" s="119"/>
-      <c r="F17" s="120"/>
-      <c r="G17" s="120"/>
-      <c r="H17" s="120"/>
-      <c r="I17" s="120"/>
-      <c r="J17" s="120"/>
-      <c r="K17" s="120"/>
-      <c r="L17" s="120"/>
-      <c r="M17" s="121"/>
+      <c r="E17" s="122"/>
+      <c r="F17" s="123"/>
+      <c r="G17" s="123"/>
+      <c r="H17" s="123"/>
+      <c r="I17" s="123"/>
+      <c r="J17" s="123"/>
+      <c r="K17" s="123"/>
+      <c r="L17" s="123"/>
+      <c r="M17" s="124"/>
     </row>
     <row r="18" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="105"/>
@@ -2170,15 +2170,15 @@
       </c>
       <c r="C18" s="107"/>
       <c r="D18" s="97"/>
-      <c r="E18" s="119"/>
-      <c r="F18" s="120"/>
-      <c r="G18" s="120"/>
-      <c r="H18" s="120"/>
-      <c r="I18" s="120"/>
-      <c r="J18" s="120"/>
-      <c r="K18" s="120"/>
-      <c r="L18" s="120"/>
-      <c r="M18" s="121"/>
+      <c r="E18" s="122"/>
+      <c r="F18" s="123"/>
+      <c r="G18" s="123"/>
+      <c r="H18" s="123"/>
+      <c r="I18" s="123"/>
+      <c r="J18" s="123"/>
+      <c r="K18" s="123"/>
+      <c r="L18" s="123"/>
+      <c r="M18" s="124"/>
     </row>
     <row r="19" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="105"/>
@@ -2187,15 +2187,15 @@
       </c>
       <c r="C19" s="107"/>
       <c r="D19" s="97"/>
-      <c r="E19" s="119"/>
-      <c r="F19" s="120"/>
-      <c r="G19" s="120"/>
-      <c r="H19" s="120"/>
-      <c r="I19" s="120"/>
-      <c r="J19" s="120"/>
-      <c r="K19" s="120"/>
-      <c r="L19" s="120"/>
-      <c r="M19" s="121"/>
+      <c r="E19" s="122"/>
+      <c r="F19" s="123"/>
+      <c r="G19" s="123"/>
+      <c r="H19" s="123"/>
+      <c r="I19" s="123"/>
+      <c r="J19" s="123"/>
+      <c r="K19" s="123"/>
+      <c r="L19" s="123"/>
+      <c r="M19" s="124"/>
     </row>
     <row r="20" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="105"/>
@@ -2314,15 +2314,15 @@
       </c>
       <c r="C26" s="107"/>
       <c r="D26" s="97"/>
-      <c r="E26" s="119"/>
-      <c r="F26" s="120"/>
-      <c r="G26" s="120"/>
-      <c r="H26" s="120"/>
-      <c r="I26" s="120"/>
-      <c r="J26" s="120"/>
-      <c r="K26" s="120"/>
-      <c r="L26" s="120"/>
-      <c r="M26" s="121"/>
+      <c r="E26" s="122"/>
+      <c r="F26" s="123"/>
+      <c r="G26" s="123"/>
+      <c r="H26" s="123"/>
+      <c r="I26" s="123"/>
+      <c r="J26" s="123"/>
+      <c r="K26" s="123"/>
+      <c r="L26" s="123"/>
+      <c r="M26" s="124"/>
     </row>
     <row r="27" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
@@ -2333,15 +2333,15 @@
       </c>
       <c r="C27" s="107"/>
       <c r="D27" s="97"/>
-      <c r="E27" s="119"/>
-      <c r="F27" s="120"/>
-      <c r="G27" s="120"/>
-      <c r="H27" s="120"/>
-      <c r="I27" s="120"/>
-      <c r="J27" s="120"/>
-      <c r="K27" s="120"/>
-      <c r="L27" s="120"/>
-      <c r="M27" s="121"/>
+      <c r="E27" s="122"/>
+      <c r="F27" s="123"/>
+      <c r="G27" s="123"/>
+      <c r="H27" s="123"/>
+      <c r="I27" s="123"/>
+      <c r="J27" s="123"/>
+      <c r="K27" s="123"/>
+      <c r="L27" s="123"/>
+      <c r="M27" s="124"/>
     </row>
     <row r="28" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
@@ -2350,15 +2350,15 @@
       </c>
       <c r="C28" s="107"/>
       <c r="D28" s="97"/>
-      <c r="E28" s="119"/>
-      <c r="F28" s="120"/>
-      <c r="G28" s="120"/>
-      <c r="H28" s="120"/>
-      <c r="I28" s="120"/>
-      <c r="J28" s="120"/>
-      <c r="K28" s="120"/>
-      <c r="L28" s="120"/>
-      <c r="M28" s="121"/>
+      <c r="E28" s="122"/>
+      <c r="F28" s="123"/>
+      <c r="G28" s="123"/>
+      <c r="H28" s="123"/>
+      <c r="I28" s="123"/>
+      <c r="J28" s="123"/>
+      <c r="K28" s="123"/>
+      <c r="L28" s="123"/>
+      <c r="M28" s="124"/>
     </row>
     <row r="29" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3"/>
@@ -2367,15 +2367,15 @@
       </c>
       <c r="C29" s="107"/>
       <c r="D29" s="97"/>
-      <c r="E29" s="119"/>
-      <c r="F29" s="120"/>
-      <c r="G29" s="120"/>
-      <c r="H29" s="120"/>
-      <c r="I29" s="120"/>
-      <c r="J29" s="120"/>
-      <c r="K29" s="120"/>
-      <c r="L29" s="120"/>
-      <c r="M29" s="121"/>
+      <c r="E29" s="122"/>
+      <c r="F29" s="123"/>
+      <c r="G29" s="123"/>
+      <c r="H29" s="123"/>
+      <c r="I29" s="123"/>
+      <c r="J29" s="123"/>
+      <c r="K29" s="123"/>
+      <c r="L29" s="123"/>
+      <c r="M29" s="124"/>
     </row>
     <row r="30" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
@@ -2386,15 +2386,15 @@
       </c>
       <c r="C30" s="107"/>
       <c r="D30" s="97"/>
-      <c r="E30" s="119"/>
-      <c r="F30" s="120"/>
-      <c r="G30" s="120"/>
-      <c r="H30" s="120"/>
-      <c r="I30" s="120"/>
-      <c r="J30" s="120"/>
-      <c r="K30" s="120"/>
-      <c r="L30" s="120"/>
-      <c r="M30" s="121"/>
+      <c r="E30" s="122"/>
+      <c r="F30" s="123"/>
+      <c r="G30" s="123"/>
+      <c r="H30" s="123"/>
+      <c r="I30" s="123"/>
+      <c r="J30" s="123"/>
+      <c r="K30" s="123"/>
+      <c r="L30" s="123"/>
+      <c r="M30" s="124"/>
     </row>
     <row r="31" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6"/>
@@ -2403,15 +2403,15 @@
       </c>
       <c r="C31" s="107"/>
       <c r="D31" s="97"/>
-      <c r="E31" s="119"/>
-      <c r="F31" s="120"/>
-      <c r="G31" s="120"/>
-      <c r="H31" s="120"/>
-      <c r="I31" s="120"/>
-      <c r="J31" s="120"/>
-      <c r="K31" s="120"/>
-      <c r="L31" s="120"/>
-      <c r="M31" s="121"/>
+      <c r="E31" s="122"/>
+      <c r="F31" s="123"/>
+      <c r="G31" s="123"/>
+      <c r="H31" s="123"/>
+      <c r="I31" s="123"/>
+      <c r="J31" s="123"/>
+      <c r="K31" s="123"/>
+      <c r="L31" s="123"/>
+      <c r="M31" s="124"/>
     </row>
     <row r="32" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6"/>
@@ -2437,23 +2437,23 @@
       </c>
       <c r="C33" s="107"/>
       <c r="D33" s="97"/>
-      <c r="E33" s="119"/>
-      <c r="F33" s="120"/>
-      <c r="G33" s="120"/>
-      <c r="H33" s="120"/>
-      <c r="I33" s="120"/>
-      <c r="J33" s="120"/>
-      <c r="K33" s="120"/>
-      <c r="L33" s="120"/>
-      <c r="M33" s="121"/>
+      <c r="E33" s="122"/>
+      <c r="F33" s="123"/>
+      <c r="G33" s="123"/>
+      <c r="H33" s="123"/>
+      <c r="I33" s="123"/>
+      <c r="J33" s="123"/>
+      <c r="K33" s="123"/>
+      <c r="L33" s="123"/>
+      <c r="M33" s="124"/>
     </row>
     <row r="34" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7"/>
-      <c r="B34" s="122" t="s">
+      <c r="B34" s="119" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="123"/>
-      <c r="D34" s="124"/>
+      <c r="C34" s="120"/>
+      <c r="D34" s="121"/>
       <c r="E34" s="116"/>
       <c r="F34" s="117"/>
       <c r="G34" s="117"/>
@@ -2628,11 +2628,11 @@
       <c r="D44" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="E44" s="122" t="s">
+      <c r="E44" s="119" t="s">
         <v>48</v>
       </c>
-      <c r="F44" s="123"/>
-      <c r="G44" s="123"/>
+      <c r="F44" s="120"/>
+      <c r="G44" s="120"/>
       <c r="H44" s="116"/>
       <c r="I44" s="117"/>
       <c r="J44" s="118"/>
@@ -2739,6 +2739,8 @@
       <c r="C50" s="33"/>
       <c r="D50" s="34"/>
       <c r="E50" s="35"/>
+      <c r="F50" s="34"/>
+      <c r="G50" s="35"/>
       <c r="H50" s="41"/>
       <c r="I50" s="42"/>
       <c r="J50" s="43"/>
@@ -3201,7 +3203,8 @@
     </row>
     <row r="81" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="165">
+  <mergeCells count="166">
+    <mergeCell ref="F50:G50"/>
     <mergeCell ref="F80:G80"/>
     <mergeCell ref="A38:M40"/>
     <mergeCell ref="C79:J79"/>
@@ -3225,6 +3228,7 @@
     <mergeCell ref="I72:J76"/>
     <mergeCell ref="K72:M76"/>
     <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B36:D36"/>
     <mergeCell ref="C9:M9"/>
     <mergeCell ref="A8:M8"/>
     <mergeCell ref="E14:M14"/>
@@ -3249,7 +3253,6 @@
     <mergeCell ref="E25:M25"/>
     <mergeCell ref="E21:M21"/>
     <mergeCell ref="E22:M22"/>
-    <mergeCell ref="B36:D36"/>
     <mergeCell ref="B37:D37"/>
     <mergeCell ref="E35:M35"/>
     <mergeCell ref="E36:M36"/>
@@ -3368,24 +3371,24 @@
     <mergeCell ref="B62:C62"/>
     <mergeCell ref="D62:E62"/>
   </mergeCells>
-  <conditionalFormatting sqref="A77:D77 K77:M77 C79:J79 D51:J55 D50:E50 H50:J50 D48:J49">
-    <cfRule type="containsBlanks" dxfId="5" priority="2">
-      <formula>LEN(TRIM(A48))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A77:D77">
-    <cfRule type="containsBlanks" dxfId="4" priority="4">
+    <cfRule type="containsBlanks" dxfId="5" priority="4">
       <formula>LEN(TRIM(A77))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C79">
-    <cfRule type="containsBlanks" dxfId="3" priority="5">
+    <cfRule type="containsBlanks" dxfId="4" priority="5">
       <formula>LEN(TRIM(C79))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D42:F43 J42:J43 D59:J63 B68:J68 B70:J70">
-    <cfRule type="containsBlanks" dxfId="2" priority="1">
+    <cfRule type="containsBlanks" dxfId="3" priority="1">
       <formula>LEN(TRIM(B42))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A77:D77 K77:M77 C79:J79 D48:J55">
+    <cfRule type="containsBlanks" dxfId="2" priority="2">
+      <formula>LEN(TRIM(A48))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I10:M10 C11:H11 K11:M11 J13:M13 E14:M22 E26:M37">
@@ -3445,7 +3448,7 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="OBLIGATORIO" prompt="Registrar de manera objetiva y concisa la información adicional que complemente el proceso de acompañamiento al aprendiz en su etapa productiva." sqref="B70:J70 B68:J68" xr:uid="{D7E55FAF-6FC8-4AC1-A902-F35811C9DD3B}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="DILIGENCIAR SI HAY POR MEJORAR" prompt="Si hay factores por mejorar favor escribir las observaciones o los compromisos de mejora" sqref="H48:J55" xr:uid="{70C7BBAF-F2BE-4776-BA55-57FE0807C14D}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Diligenciar si hay por mejorar" prompt="Si hay factores por mejorar favor escribir las observaciones o los compromisos de mejora" sqref="H59:J63" xr:uid="{56231F2E-9BAE-4742-84BB-A6BBFCFB029F}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Realiza acciones que fortalezcan su perfil ocupacional potenciando sus competencias en el marco de su proyecto de vida." sqref="D50:E50 F49:G49" xr:uid="{379961D4-6BD4-47A0-B009-E49C8B35A883}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Realiza acciones que fortalezcan su perfil ocupacional potenciando sus competencias en el marco de su proyecto de vida." sqref="D50:G50 F49:G49" xr:uid="{379961D4-6BD4-47A0-B009-E49C8B35A883}"/>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="5" scale="68" fitToHeight="0" orientation="portrait" r:id="rId1"/>

--- a/Formatos/Visita 2 GFPI-F023.xlsx
+++ b/Formatos/Visita 2 GFPI-F023.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SEANT\OneDrive\Documents\Seto 2026\sena\Manual SENA Etapa Productiva\manual-aprendiz-sena\Formatos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniminuto0-my.sharepoint.com/personal/sergio_torres_mar_uniminuto_edu_co/Documents/Documentos/Seto 2026/SETO/sena/Manual SENA Etapa Productiva/manual-aprendiz-sena/Formatos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37FB8EBA-F1E6-4458-A15B-89CCBCFED77A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{37FB8EBA-F1E6-4458-A15B-89CCBCFED77A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D119071-9D0F-4223-9741-A379E1890E12}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{BC3553EE-4E49-4F2A-B03E-CFAC4EB3009B}"/>
+    <workbookView xWindow="28680" yWindow="-105" windowWidth="29040" windowHeight="15720" xr2:uid="{BC3553EE-4E49-4F2A-B03E-CFAC4EB3009B}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -400,7 +400,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -494,13 +494,6 @@
       <family val="2"/>
     </font>
     <font>
-      <u/>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Aptos Narrow"/>
@@ -900,7 +893,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="167">
+  <cellXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
@@ -950,48 +943,410 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1">
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement i="0"/>
-        </ext>
-      </extLst>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1">
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement i="0"/>
-        </ext>
-      </extLst>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="1" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="15" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1003,50 +1358,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1061,415 +1372,75 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="1" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="15" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="12">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1523,23 +1494,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
-<FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
-  <bag type="Checkbox"/>
-  <bag type="XFControls">
-    <bagId k="CellControl">0</bagId>
-  </bag>
-  <bag type="XFComplement">
-    <bagId k="XFControls">1</bagId>
-  </bag>
-  <bag type="XFComplements" extRef="XFComplementsMapperExtRef">
-    <a k="MappedFeaturePropertyBags">
-      <bagId>2</bagId>
-    </a>
-  </bag>
-</FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1862,7 +1816,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O81"/>
+  <dimension ref="A1:XFD81"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.5703125" customWidth="1"/>
@@ -1875,1102 +1829,1097 @@
     <col min="12" max="12" width="3.7109375" customWidth="1"/>
     <col min="13" max="13" width="13.28515625" customWidth="1"/>
     <col min="14" max="15" width="0" hidden="1" customWidth="1"/>
-    <col min="16" max="16384" width="11.42578125" hidden="1"/>
+    <col min="16" max="16383" width="11.42578125" hidden="1"/>
+    <col min="16384" max="16384" width="1.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="132" t="s">
         <v>74</v>
       </c>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="22"/>
+      <c r="C1" s="133"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="133"/>
+      <c r="F1" s="133"/>
+      <c r="G1" s="133"/>
+      <c r="H1" s="133"/>
+      <c r="I1" s="133"/>
+      <c r="J1" s="133"/>
+      <c r="K1" s="134"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="135" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="25"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="136"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="137" t="s">
         <v>76</v>
       </c>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
-      <c r="J3" s="27"/>
-      <c r="K3" s="28"/>
+      <c r="C3" s="138"/>
+      <c r="D3" s="138"/>
+      <c r="E3" s="138"/>
+      <c r="F3" s="138"/>
+      <c r="G3" s="138"/>
+      <c r="H3" s="138"/>
+      <c r="I3" s="138"/>
+      <c r="J3" s="138"/>
+      <c r="K3" s="139"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="135" t="s">
         <v>77</v>
       </c>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="25"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="136"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="137" t="s">
         <v>78</v>
       </c>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
-      <c r="I5" s="27"/>
-      <c r="J5" s="27"/>
-      <c r="K5" s="28"/>
+      <c r="C5" s="138"/>
+      <c r="D5" s="138"/>
+      <c r="E5" s="138"/>
+      <c r="F5" s="138"/>
+      <c r="G5" s="138"/>
+      <c r="H5" s="138"/>
+      <c r="I5" s="138"/>
+      <c r="J5" s="138"/>
+      <c r="K5" s="139"/>
     </row>
     <row r="6" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="29" t="s">
+      <c r="B6" s="140" t="s">
         <v>79</v>
       </c>
-      <c r="C6" s="30"/>
-      <c r="D6" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="E6" s="31" t="s">
+      <c r="C6" s="141"/>
+      <c r="D6" s="147"/>
+      <c r="E6" s="142" t="s">
         <v>80</v>
       </c>
-      <c r="F6" s="30"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" s="31" t="s">
+      <c r="F6" s="141"/>
+      <c r="G6" s="141"/>
+      <c r="H6" s="147"/>
+      <c r="I6" s="142" t="s">
         <v>81</v>
       </c>
-      <c r="J6" s="30"/>
-      <c r="K6" s="18" t="b">
-        <v>0</v>
-      </c>
+      <c r="J6" s="141"/>
+      <c r="K6" s="148"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25"/>
     <row r="8" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="126" t="s">
+      <c r="A8" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="127"/>
-      <c r="C8" s="127"/>
-      <c r="D8" s="127"/>
-      <c r="E8" s="127"/>
-      <c r="F8" s="127"/>
-      <c r="G8" s="127"/>
-      <c r="H8" s="127"/>
-      <c r="I8" s="127"/>
-      <c r="J8" s="127"/>
-      <c r="K8" s="127"/>
-      <c r="L8" s="127"/>
-      <c r="M8" s="127"/>
+      <c r="B8" s="56"/>
+      <c r="C8" s="56"/>
+      <c r="D8" s="56"/>
+      <c r="E8" s="56"/>
+      <c r="F8" s="56"/>
+      <c r="G8" s="56"/>
+      <c r="H8" s="56"/>
+      <c r="I8" s="56"/>
+      <c r="J8" s="56"/>
+      <c r="K8" s="56"/>
+      <c r="L8" s="56"/>
+      <c r="M8" s="56"/>
     </row>
     <row r="9" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="96" t="s">
+      <c r="A9" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="97"/>
-      <c r="C9" s="114" t="s">
+      <c r="B9" s="37"/>
+      <c r="C9" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="125"/>
-      <c r="E9" s="125"/>
-      <c r="F9" s="125"/>
-      <c r="G9" s="125"/>
-      <c r="H9" s="125"/>
-      <c r="I9" s="125"/>
-      <c r="J9" s="125"/>
-      <c r="K9" s="125"/>
-      <c r="L9" s="125"/>
-      <c r="M9" s="115"/>
+      <c r="D9" s="53"/>
+      <c r="E9" s="53"/>
+      <c r="F9" s="53"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="53"/>
+      <c r="I9" s="53"/>
+      <c r="J9" s="53"/>
+      <c r="K9" s="53"/>
+      <c r="L9" s="53"/>
+      <c r="M9" s="54"/>
     </row>
     <row r="10" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="96" t="s">
+      <c r="A10" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="97"/>
-      <c r="C10" s="98" t="s">
+      <c r="B10" s="37"/>
+      <c r="C10" s="82" t="s">
         <v>4</v>
       </c>
-      <c r="D10" s="99"/>
-      <c r="E10" s="99"/>
-      <c r="F10" s="99"/>
-      <c r="G10" s="100"/>
+      <c r="D10" s="83"/>
+      <c r="E10" s="83"/>
+      <c r="F10" s="83"/>
+      <c r="G10" s="84"/>
       <c r="H10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I10" s="146"/>
-      <c r="J10" s="147"/>
-      <c r="K10" s="147"/>
-      <c r="L10" s="147"/>
-      <c r="M10" s="148"/>
+      <c r="I10" s="23"/>
+      <c r="J10" s="24"/>
+      <c r="K10" s="24"/>
+      <c r="L10" s="24"/>
+      <c r="M10" s="25"/>
     </row>
     <row r="11" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="96" t="s">
+      <c r="A11" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="97"/>
-      <c r="C11" s="111"/>
-      <c r="D11" s="112"/>
-      <c r="E11" s="112"/>
-      <c r="F11" s="112"/>
-      <c r="G11" s="112"/>
-      <c r="H11" s="113"/>
-      <c r="I11" s="53" t="s">
+      <c r="B11" s="37"/>
+      <c r="C11" s="92"/>
+      <c r="D11" s="93"/>
+      <c r="E11" s="93"/>
+      <c r="F11" s="93"/>
+      <c r="G11" s="93"/>
+      <c r="H11" s="94"/>
+      <c r="I11" s="95" t="s">
         <v>7</v>
       </c>
-      <c r="J11" s="54"/>
-      <c r="K11" s="128"/>
-      <c r="L11" s="129"/>
-      <c r="M11" s="130"/>
+      <c r="J11" s="96"/>
+      <c r="K11" s="60"/>
+      <c r="L11" s="61"/>
+      <c r="M11" s="62"/>
     </row>
     <row r="12" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="96" t="s">
+      <c r="A12" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="97"/>
+      <c r="B12" s="37"/>
       <c r="C12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="114" t="s">
+      <c r="D12" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="E12" s="115"/>
-      <c r="F12" s="55" t="s">
+      <c r="E12" s="54"/>
+      <c r="F12" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="57"/>
+      <c r="G12" s="98"/>
       <c r="H12" s="1"/>
-      <c r="I12" s="55" t="s">
+      <c r="I12" s="97" t="s">
         <v>12</v>
       </c>
-      <c r="J12" s="57"/>
-      <c r="K12" s="131"/>
-      <c r="L12" s="132"/>
-      <c r="M12" s="133"/>
+      <c r="J12" s="98"/>
+      <c r="K12" s="63"/>
+      <c r="L12" s="64"/>
+      <c r="M12" s="65"/>
     </row>
     <row r="13" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="96" t="s">
+      <c r="A13" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="97"/>
-      <c r="C13" s="101"/>
-      <c r="D13" s="102"/>
-      <c r="E13" s="102"/>
-      <c r="F13" s="103"/>
-      <c r="G13" s="101" t="s">
+      <c r="B13" s="37"/>
+      <c r="C13" s="85"/>
+      <c r="D13" s="86"/>
+      <c r="E13" s="86"/>
+      <c r="F13" s="87"/>
+      <c r="G13" s="85" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="102"/>
-      <c r="I13" s="103"/>
-      <c r="J13" s="134"/>
-      <c r="K13" s="135"/>
-      <c r="L13" s="135"/>
-      <c r="M13" s="136"/>
+      <c r="H13" s="86"/>
+      <c r="I13" s="87"/>
+      <c r="J13" s="66"/>
+      <c r="K13" s="67"/>
+      <c r="L13" s="67"/>
+      <c r="M13" s="68"/>
     </row>
     <row r="14" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="104" t="s">
+      <c r="A14" s="88" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="96" t="s">
+      <c r="B14" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="107"/>
-      <c r="D14" s="97"/>
-      <c r="E14" s="122"/>
-      <c r="F14" s="123"/>
-      <c r="G14" s="123"/>
-      <c r="H14" s="123"/>
-      <c r="I14" s="123"/>
-      <c r="J14" s="123"/>
-      <c r="K14" s="123"/>
-      <c r="L14" s="123"/>
-      <c r="M14" s="124"/>
+      <c r="C14" s="51"/>
+      <c r="D14" s="37"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="58"/>
+      <c r="G14" s="58"/>
+      <c r="H14" s="58"/>
+      <c r="I14" s="58"/>
+      <c r="J14" s="58"/>
+      <c r="K14" s="58"/>
+      <c r="L14" s="58"/>
+      <c r="M14" s="59"/>
     </row>
     <row r="15" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="105"/>
-      <c r="B15" s="108" t="s">
+      <c r="A15" s="73"/>
+      <c r="B15" s="89" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="109"/>
-      <c r="D15" s="110"/>
-      <c r="E15" s="137"/>
-      <c r="F15" s="138"/>
-      <c r="G15" s="138"/>
-      <c r="H15" s="138"/>
-      <c r="I15" s="138"/>
-      <c r="J15" s="138"/>
-      <c r="K15" s="138"/>
-      <c r="L15" s="138"/>
-      <c r="M15" s="139"/>
+      <c r="C15" s="90"/>
+      <c r="D15" s="91"/>
+      <c r="E15" s="69"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="70"/>
+      <c r="K15" s="70"/>
+      <c r="L15" s="70"/>
+      <c r="M15" s="71"/>
     </row>
     <row r="16" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="105"/>
-      <c r="B16" s="96" t="s">
+      <c r="A16" s="73"/>
+      <c r="B16" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="107"/>
-      <c r="D16" s="97"/>
-      <c r="E16" s="122"/>
-      <c r="F16" s="123"/>
-      <c r="G16" s="123"/>
-      <c r="H16" s="123"/>
-      <c r="I16" s="123"/>
-      <c r="J16" s="123"/>
-      <c r="K16" s="123"/>
-      <c r="L16" s="123"/>
-      <c r="M16" s="124"/>
+      <c r="C16" s="51"/>
+      <c r="D16" s="37"/>
+      <c r="E16" s="57"/>
+      <c r="F16" s="58"/>
+      <c r="G16" s="58"/>
+      <c r="H16" s="58"/>
+      <c r="I16" s="58"/>
+      <c r="J16" s="58"/>
+      <c r="K16" s="58"/>
+      <c r="L16" s="58"/>
+      <c r="M16" s="59"/>
     </row>
     <row r="17" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="105"/>
-      <c r="B17" s="96" t="s">
+      <c r="A17" s="73"/>
+      <c r="B17" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="107"/>
-      <c r="D17" s="97"/>
-      <c r="E17" s="122"/>
-      <c r="F17" s="123"/>
-      <c r="G17" s="123"/>
-      <c r="H17" s="123"/>
-      <c r="I17" s="123"/>
-      <c r="J17" s="123"/>
-      <c r="K17" s="123"/>
-      <c r="L17" s="123"/>
-      <c r="M17" s="124"/>
+      <c r="C17" s="51"/>
+      <c r="D17" s="37"/>
+      <c r="E17" s="57"/>
+      <c r="F17" s="58"/>
+      <c r="G17" s="58"/>
+      <c r="H17" s="58"/>
+      <c r="I17" s="58"/>
+      <c r="J17" s="58"/>
+      <c r="K17" s="58"/>
+      <c r="L17" s="58"/>
+      <c r="M17" s="59"/>
     </row>
     <row r="18" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="105"/>
-      <c r="B18" s="96" t="s">
+      <c r="A18" s="73"/>
+      <c r="B18" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="107"/>
-      <c r="D18" s="97"/>
-      <c r="E18" s="122"/>
-      <c r="F18" s="123"/>
-      <c r="G18" s="123"/>
-      <c r="H18" s="123"/>
-      <c r="I18" s="123"/>
-      <c r="J18" s="123"/>
-      <c r="K18" s="123"/>
-      <c r="L18" s="123"/>
-      <c r="M18" s="124"/>
+      <c r="C18" s="51"/>
+      <c r="D18" s="37"/>
+      <c r="E18" s="57"/>
+      <c r="F18" s="58"/>
+      <c r="G18" s="58"/>
+      <c r="H18" s="58"/>
+      <c r="I18" s="58"/>
+      <c r="J18" s="58"/>
+      <c r="K18" s="58"/>
+      <c r="L18" s="58"/>
+      <c r="M18" s="59"/>
     </row>
     <row r="19" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="105"/>
-      <c r="B19" s="96" t="s">
+      <c r="A19" s="73"/>
+      <c r="B19" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="107"/>
-      <c r="D19" s="97"/>
-      <c r="E19" s="122"/>
-      <c r="F19" s="123"/>
-      <c r="G19" s="123"/>
-      <c r="H19" s="123"/>
-      <c r="I19" s="123"/>
-      <c r="J19" s="123"/>
-      <c r="K19" s="123"/>
-      <c r="L19" s="123"/>
-      <c r="M19" s="124"/>
+      <c r="C19" s="51"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="58"/>
+      <c r="G19" s="58"/>
+      <c r="H19" s="58"/>
+      <c r="I19" s="58"/>
+      <c r="J19" s="58"/>
+      <c r="K19" s="58"/>
+      <c r="L19" s="58"/>
+      <c r="M19" s="59"/>
     </row>
     <row r="20" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="105"/>
-      <c r="B20" s="96" t="s">
+      <c r="A20" s="73"/>
+      <c r="B20" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="107"/>
-      <c r="D20" s="97"/>
-      <c r="E20" s="116"/>
-      <c r="F20" s="117"/>
-      <c r="G20" s="117"/>
-      <c r="H20" s="117"/>
-      <c r="I20" s="117"/>
-      <c r="J20" s="117"/>
-      <c r="K20" s="117"/>
-      <c r="L20" s="117"/>
-      <c r="M20" s="118"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="41"/>
+      <c r="J20" s="41"/>
+      <c r="K20" s="41"/>
+      <c r="L20" s="41"/>
+      <c r="M20" s="42"/>
     </row>
     <row r="21" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="105"/>
-      <c r="B21" s="96" t="s">
+      <c r="A21" s="73"/>
+      <c r="B21" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="107"/>
-      <c r="D21" s="97"/>
-      <c r="E21" s="116"/>
-      <c r="F21" s="117"/>
-      <c r="G21" s="117"/>
-      <c r="H21" s="117"/>
-      <c r="I21" s="117"/>
-      <c r="J21" s="117"/>
-      <c r="K21" s="117"/>
-      <c r="L21" s="117"/>
-      <c r="M21" s="118"/>
+      <c r="C21" s="51"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="41"/>
+      <c r="I21" s="41"/>
+      <c r="J21" s="41"/>
+      <c r="K21" s="41"/>
+      <c r="L21" s="41"/>
+      <c r="M21" s="42"/>
     </row>
     <row r="22" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="106"/>
-      <c r="B22" s="96" t="s">
+      <c r="A22" s="74"/>
+      <c r="B22" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="107"/>
-      <c r="D22" s="97"/>
-      <c r="E22" s="116"/>
-      <c r="F22" s="117"/>
-      <c r="G22" s="117"/>
-      <c r="H22" s="117"/>
-      <c r="I22" s="117"/>
-      <c r="J22" s="117"/>
-      <c r="K22" s="117"/>
-      <c r="L22" s="117"/>
-      <c r="M22" s="118"/>
+      <c r="C22" s="51"/>
+      <c r="D22" s="37"/>
+      <c r="E22" s="40"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="41"/>
+      <c r="H22" s="41"/>
+      <c r="I22" s="41"/>
+      <c r="J22" s="41"/>
+      <c r="K22" s="41"/>
+      <c r="L22" s="41"/>
+      <c r="M22" s="42"/>
     </row>
     <row r="23" spans="1:13" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="140" t="s">
+      <c r="A23" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="96" t="s">
+      <c r="B23" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="C23" s="107"/>
-      <c r="D23" s="97"/>
-      <c r="E23" s="141" t="s">
+      <c r="C23" s="51"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="75" t="s">
         <v>27</v>
       </c>
-      <c r="F23" s="142"/>
-      <c r="G23" s="142"/>
-      <c r="H23" s="142"/>
-      <c r="I23" s="142"/>
-      <c r="J23" s="142"/>
-      <c r="K23" s="142"/>
-      <c r="L23" s="142"/>
-      <c r="M23" s="143"/>
+      <c r="F23" s="76"/>
+      <c r="G23" s="76"/>
+      <c r="H23" s="76"/>
+      <c r="I23" s="76"/>
+      <c r="J23" s="76"/>
+      <c r="K23" s="76"/>
+      <c r="L23" s="76"/>
+      <c r="M23" s="77"/>
     </row>
     <row r="24" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="105"/>
-      <c r="B24" s="96" t="s">
+      <c r="A24" s="73"/>
+      <c r="B24" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="C24" s="107"/>
-      <c r="D24" s="97"/>
-      <c r="E24" s="87"/>
-      <c r="F24" s="88"/>
-      <c r="G24" s="88"/>
-      <c r="H24" s="88"/>
-      <c r="I24" s="88"/>
-      <c r="J24" s="88"/>
-      <c r="K24" s="88"/>
-      <c r="L24" s="88"/>
-      <c r="M24" s="89"/>
+      <c r="C24" s="51"/>
+      <c r="D24" s="37"/>
+      <c r="E24" s="78"/>
+      <c r="F24" s="79"/>
+      <c r="G24" s="79"/>
+      <c r="H24" s="79"/>
+      <c r="I24" s="79"/>
+      <c r="J24" s="79"/>
+      <c r="K24" s="79"/>
+      <c r="L24" s="79"/>
+      <c r="M24" s="80"/>
     </row>
     <row r="25" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="106"/>
-      <c r="B25" s="96" t="s">
+      <c r="A25" s="74"/>
+      <c r="B25" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="C25" s="107"/>
-      <c r="D25" s="97"/>
-      <c r="E25" s="141" t="s">
+      <c r="C25" s="51"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="F25" s="142"/>
-      <c r="G25" s="142"/>
-      <c r="H25" s="142"/>
-      <c r="I25" s="142"/>
-      <c r="J25" s="142"/>
-      <c r="K25" s="142"/>
-      <c r="L25" s="142"/>
-      <c r="M25" s="143"/>
+      <c r="F25" s="76"/>
+      <c r="G25" s="76"/>
+      <c r="H25" s="76"/>
+      <c r="I25" s="76"/>
+      <c r="J25" s="76"/>
+      <c r="K25" s="76"/>
+      <c r="L25" s="76"/>
+      <c r="M25" s="77"/>
     </row>
     <row r="26" spans="1:13" ht="25.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="96" t="s">
+      <c r="B26" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C26" s="107"/>
-      <c r="D26" s="97"/>
-      <c r="E26" s="122"/>
-      <c r="F26" s="123"/>
-      <c r="G26" s="123"/>
-      <c r="H26" s="123"/>
-      <c r="I26" s="123"/>
-      <c r="J26" s="123"/>
-      <c r="K26" s="123"/>
-      <c r="L26" s="123"/>
-      <c r="M26" s="124"/>
+      <c r="C26" s="51"/>
+      <c r="D26" s="37"/>
+      <c r="E26" s="57"/>
+      <c r="F26" s="58"/>
+      <c r="G26" s="58"/>
+      <c r="H26" s="58"/>
+      <c r="I26" s="58"/>
+      <c r="J26" s="58"/>
+      <c r="K26" s="58"/>
+      <c r="L26" s="58"/>
+      <c r="M26" s="59"/>
     </row>
     <row r="27" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="96" t="s">
+      <c r="B27" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="C27" s="107"/>
-      <c r="D27" s="97"/>
-      <c r="E27" s="122"/>
-      <c r="F27" s="123"/>
-      <c r="G27" s="123"/>
-      <c r="H27" s="123"/>
-      <c r="I27" s="123"/>
-      <c r="J27" s="123"/>
-      <c r="K27" s="123"/>
-      <c r="L27" s="123"/>
-      <c r="M27" s="124"/>
+      <c r="C27" s="51"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="57"/>
+      <c r="F27" s="58"/>
+      <c r="G27" s="58"/>
+      <c r="H27" s="58"/>
+      <c r="I27" s="58"/>
+      <c r="J27" s="58"/>
+      <c r="K27" s="58"/>
+      <c r="L27" s="58"/>
+      <c r="M27" s="59"/>
     </row>
     <row r="28" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
-      <c r="B28" s="96" t="s">
+      <c r="B28" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="C28" s="107"/>
-      <c r="D28" s="97"/>
-      <c r="E28" s="122"/>
-      <c r="F28" s="123"/>
-      <c r="G28" s="123"/>
-      <c r="H28" s="123"/>
-      <c r="I28" s="123"/>
-      <c r="J28" s="123"/>
-      <c r="K28" s="123"/>
-      <c r="L28" s="123"/>
-      <c r="M28" s="124"/>
+      <c r="C28" s="51"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="57"/>
+      <c r="F28" s="58"/>
+      <c r="G28" s="58"/>
+      <c r="H28" s="58"/>
+      <c r="I28" s="58"/>
+      <c r="J28" s="58"/>
+      <c r="K28" s="58"/>
+      <c r="L28" s="58"/>
+      <c r="M28" s="59"/>
     </row>
     <row r="29" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3"/>
-      <c r="B29" s="96" t="s">
+      <c r="B29" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="C29" s="107"/>
-      <c r="D29" s="97"/>
-      <c r="E29" s="122"/>
-      <c r="F29" s="123"/>
-      <c r="G29" s="123"/>
-      <c r="H29" s="123"/>
-      <c r="I29" s="123"/>
-      <c r="J29" s="123"/>
-      <c r="K29" s="123"/>
-      <c r="L29" s="123"/>
-      <c r="M29" s="124"/>
+      <c r="C29" s="51"/>
+      <c r="D29" s="37"/>
+      <c r="E29" s="57"/>
+      <c r="F29" s="58"/>
+      <c r="G29" s="58"/>
+      <c r="H29" s="58"/>
+      <c r="I29" s="58"/>
+      <c r="J29" s="58"/>
+      <c r="K29" s="58"/>
+      <c r="L29" s="58"/>
+      <c r="M29" s="59"/>
     </row>
     <row r="30" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B30" s="96" t="s">
+      <c r="B30" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="107"/>
-      <c r="D30" s="97"/>
-      <c r="E30" s="122"/>
-      <c r="F30" s="123"/>
-      <c r="G30" s="123"/>
-      <c r="H30" s="123"/>
-      <c r="I30" s="123"/>
-      <c r="J30" s="123"/>
-      <c r="K30" s="123"/>
-      <c r="L30" s="123"/>
-      <c r="M30" s="124"/>
+      <c r="C30" s="51"/>
+      <c r="D30" s="37"/>
+      <c r="E30" s="57"/>
+      <c r="F30" s="58"/>
+      <c r="G30" s="58"/>
+      <c r="H30" s="58"/>
+      <c r="I30" s="58"/>
+      <c r="J30" s="58"/>
+      <c r="K30" s="58"/>
+      <c r="L30" s="58"/>
+      <c r="M30" s="59"/>
     </row>
     <row r="31" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6"/>
-      <c r="B31" s="96" t="s">
+      <c r="B31" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="C31" s="107"/>
-      <c r="D31" s="97"/>
-      <c r="E31" s="122"/>
-      <c r="F31" s="123"/>
-      <c r="G31" s="123"/>
-      <c r="H31" s="123"/>
-      <c r="I31" s="123"/>
-      <c r="J31" s="123"/>
-      <c r="K31" s="123"/>
-      <c r="L31" s="123"/>
-      <c r="M31" s="124"/>
+      <c r="C31" s="51"/>
+      <c r="D31" s="37"/>
+      <c r="E31" s="57"/>
+      <c r="F31" s="58"/>
+      <c r="G31" s="58"/>
+      <c r="H31" s="58"/>
+      <c r="I31" s="58"/>
+      <c r="J31" s="58"/>
+      <c r="K31" s="58"/>
+      <c r="L31" s="58"/>
+      <c r="M31" s="59"/>
     </row>
     <row r="32" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6"/>
-      <c r="B32" s="96" t="s">
+      <c r="B32" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="C32" s="107"/>
-      <c r="D32" s="97"/>
-      <c r="E32" s="116"/>
-      <c r="F32" s="117"/>
-      <c r="G32" s="117"/>
-      <c r="H32" s="117"/>
-      <c r="I32" s="117"/>
-      <c r="J32" s="117"/>
-      <c r="K32" s="117"/>
-      <c r="L32" s="117"/>
-      <c r="M32" s="118"/>
+      <c r="C32" s="51"/>
+      <c r="D32" s="37"/>
+      <c r="E32" s="40"/>
+      <c r="F32" s="41"/>
+      <c r="G32" s="41"/>
+      <c r="H32" s="41"/>
+      <c r="I32" s="41"/>
+      <c r="J32" s="41"/>
+      <c r="K32" s="41"/>
+      <c r="L32" s="41"/>
+      <c r="M32" s="42"/>
     </row>
     <row r="33" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="6"/>
-      <c r="B33" s="96" t="s">
+      <c r="B33" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="107"/>
-      <c r="D33" s="97"/>
-      <c r="E33" s="122"/>
-      <c r="F33" s="123"/>
-      <c r="G33" s="123"/>
-      <c r="H33" s="123"/>
-      <c r="I33" s="123"/>
-      <c r="J33" s="123"/>
-      <c r="K33" s="123"/>
-      <c r="L33" s="123"/>
-      <c r="M33" s="124"/>
+      <c r="C33" s="51"/>
+      <c r="D33" s="37"/>
+      <c r="E33" s="57"/>
+      <c r="F33" s="58"/>
+      <c r="G33" s="58"/>
+      <c r="H33" s="58"/>
+      <c r="I33" s="58"/>
+      <c r="J33" s="58"/>
+      <c r="K33" s="58"/>
+      <c r="L33" s="58"/>
+      <c r="M33" s="59"/>
     </row>
     <row r="34" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7"/>
-      <c r="B34" s="119" t="s">
+      <c r="B34" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="120"/>
-      <c r="D34" s="121"/>
-      <c r="E34" s="116"/>
-      <c r="F34" s="117"/>
-      <c r="G34" s="117"/>
-      <c r="H34" s="117"/>
-      <c r="I34" s="117"/>
-      <c r="J34" s="117"/>
-      <c r="K34" s="117"/>
-      <c r="L34" s="117"/>
-      <c r="M34" s="118"/>
+      <c r="C34" s="39"/>
+      <c r="D34" s="81"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="41"/>
+      <c r="G34" s="41"/>
+      <c r="H34" s="41"/>
+      <c r="I34" s="41"/>
+      <c r="J34" s="41"/>
+      <c r="K34" s="41"/>
+      <c r="L34" s="41"/>
+      <c r="M34" s="42"/>
     </row>
     <row r="35" spans="1:13" ht="25.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B35" s="164" t="s">
+      <c r="B35" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="C35" s="165"/>
-      <c r="D35" s="166"/>
-      <c r="E35" s="116"/>
-      <c r="F35" s="117"/>
-      <c r="G35" s="117"/>
-      <c r="H35" s="117"/>
-      <c r="I35" s="117"/>
-      <c r="J35" s="117"/>
-      <c r="K35" s="117"/>
-      <c r="L35" s="117"/>
-      <c r="M35" s="118"/>
+      <c r="C35" s="49"/>
+      <c r="D35" s="50"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="41"/>
+      <c r="G35" s="41"/>
+      <c r="H35" s="41"/>
+      <c r="I35" s="41"/>
+      <c r="J35" s="41"/>
+      <c r="K35" s="41"/>
+      <c r="L35" s="41"/>
+      <c r="M35" s="42"/>
     </row>
     <row r="36" spans="1:13" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B36" s="96" t="s">
+      <c r="B36" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="C36" s="107"/>
-      <c r="D36" s="97"/>
-      <c r="E36" s="116"/>
-      <c r="F36" s="117"/>
-      <c r="G36" s="117"/>
-      <c r="H36" s="117"/>
-      <c r="I36" s="117"/>
-      <c r="J36" s="117"/>
-      <c r="K36" s="117"/>
-      <c r="L36" s="117"/>
-      <c r="M36" s="118"/>
+      <c r="C36" s="51"/>
+      <c r="D36" s="37"/>
+      <c r="E36" s="40"/>
+      <c r="F36" s="41"/>
+      <c r="G36" s="41"/>
+      <c r="H36" s="41"/>
+      <c r="I36" s="41"/>
+      <c r="J36" s="41"/>
+      <c r="K36" s="41"/>
+      <c r="L36" s="41"/>
+      <c r="M36" s="42"/>
     </row>
     <row r="37" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="10"/>
-      <c r="B37" s="96" t="s">
+      <c r="B37" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="107"/>
-      <c r="D37" s="97"/>
-      <c r="E37" s="116"/>
-      <c r="F37" s="117"/>
-      <c r="G37" s="117"/>
-      <c r="H37" s="117"/>
-      <c r="I37" s="117"/>
-      <c r="J37" s="117"/>
-      <c r="K37" s="117"/>
-      <c r="L37" s="117"/>
-      <c r="M37" s="118"/>
+      <c r="C37" s="51"/>
+      <c r="D37" s="37"/>
+      <c r="E37" s="40"/>
+      <c r="F37" s="41"/>
+      <c r="G37" s="41"/>
+      <c r="H37" s="41"/>
+      <c r="I37" s="41"/>
+      <c r="J37" s="41"/>
+      <c r="K37" s="41"/>
+      <c r="L37" s="41"/>
+      <c r="M37" s="42"/>
     </row>
     <row r="38" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="144" t="s">
+      <c r="A38" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="B38" s="144"/>
-      <c r="C38" s="144"/>
-      <c r="D38" s="144"/>
-      <c r="E38" s="144"/>
-      <c r="F38" s="144"/>
-      <c r="G38" s="144"/>
-      <c r="H38" s="144"/>
-      <c r="I38" s="144"/>
-      <c r="J38" s="144"/>
-      <c r="K38" s="144"/>
-      <c r="L38" s="144"/>
-      <c r="M38" s="144"/>
+      <c r="B38" s="21"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="21"/>
+      <c r="H38" s="21"/>
+      <c r="I38" s="21"/>
+      <c r="J38" s="21"/>
+      <c r="K38" s="21"/>
+      <c r="L38" s="21"/>
+      <c r="M38" s="21"/>
     </row>
     <row r="39" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="144"/>
-      <c r="B39" s="144"/>
-      <c r="C39" s="144"/>
-      <c r="D39" s="144"/>
-      <c r="E39" s="144"/>
-      <c r="F39" s="144"/>
-      <c r="G39" s="144"/>
-      <c r="H39" s="144"/>
-      <c r="I39" s="144"/>
-      <c r="J39" s="144"/>
-      <c r="K39" s="144"/>
-      <c r="L39" s="144"/>
-      <c r="M39" s="144"/>
+      <c r="A39" s="21"/>
+      <c r="B39" s="21"/>
+      <c r="C39" s="21"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="21"/>
+      <c r="G39" s="21"/>
+      <c r="H39" s="21"/>
+      <c r="I39" s="21"/>
+      <c r="J39" s="21"/>
+      <c r="K39" s="21"/>
+      <c r="L39" s="21"/>
+      <c r="M39" s="21"/>
     </row>
     <row r="40" spans="1:13" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="144"/>
-      <c r="B40" s="144"/>
-      <c r="C40" s="144"/>
-      <c r="D40" s="144"/>
-      <c r="E40" s="144"/>
-      <c r="F40" s="144"/>
-      <c r="G40" s="144"/>
-      <c r="H40" s="144"/>
-      <c r="I40" s="144"/>
-      <c r="J40" s="144"/>
-      <c r="K40" s="144"/>
-      <c r="L40" s="144"/>
-      <c r="M40" s="144"/>
+      <c r="A40" s="21"/>
+      <c r="B40" s="21"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="21"/>
+      <c r="G40" s="21"/>
+      <c r="H40" s="21"/>
+      <c r="I40" s="21"/>
+      <c r="J40" s="21"/>
+      <c r="K40" s="21"/>
+      <c r="L40" s="21"/>
+      <c r="M40" s="21"/>
     </row>
     <row r="41" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="11"/>
-      <c r="B41" s="72" t="s">
+      <c r="B41" s="99" t="s">
         <v>73</v>
       </c>
-      <c r="C41" s="73"/>
-      <c r="D41" s="73"/>
-      <c r="E41" s="73"/>
-      <c r="F41" s="73"/>
-      <c r="G41" s="73"/>
-      <c r="H41" s="73"/>
-      <c r="I41" s="73"/>
-      <c r="J41" s="74"/>
+      <c r="C41" s="100"/>
+      <c r="D41" s="100"/>
+      <c r="E41" s="100"/>
+      <c r="F41" s="100"/>
+      <c r="G41" s="100"/>
+      <c r="H41" s="100"/>
+      <c r="I41" s="100"/>
+      <c r="J41" s="101"/>
       <c r="K41" s="11"/>
       <c r="L41" s="11"/>
       <c r="M41" s="11"/>
     </row>
     <row r="42" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="11"/>
-      <c r="B42" s="75" t="s">
+      <c r="B42" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="C42" s="152"/>
-      <c r="D42" s="153"/>
-      <c r="E42" s="154"/>
-      <c r="F42" s="155"/>
-      <c r="G42" s="75" t="s">
+      <c r="C42" s="27"/>
+      <c r="D42" s="30"/>
+      <c r="E42" s="31"/>
+      <c r="F42" s="32"/>
+      <c r="G42" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="H42" s="76"/>
-      <c r="I42" s="77"/>
-      <c r="J42" s="81"/>
+      <c r="H42" s="102"/>
+      <c r="I42" s="103"/>
+      <c r="J42" s="107"/>
       <c r="K42" s="11"/>
       <c r="L42" s="11"/>
       <c r="M42" s="11"/>
     </row>
     <row r="43" spans="1:13" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="11"/>
-      <c r="B43" s="39"/>
-      <c r="C43" s="40"/>
-      <c r="D43" s="156"/>
-      <c r="E43" s="157"/>
-      <c r="F43" s="158"/>
-      <c r="G43" s="78" t="s">
+      <c r="B43" s="28"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="33"/>
+      <c r="E43" s="34"/>
+      <c r="F43" s="35"/>
+      <c r="G43" s="104" t="s">
         <v>44</v>
       </c>
-      <c r="H43" s="79"/>
-      <c r="I43" s="80"/>
-      <c r="J43" s="82"/>
+      <c r="H43" s="105"/>
+      <c r="I43" s="106"/>
+      <c r="J43" s="108"/>
       <c r="K43" s="11"/>
       <c r="L43" s="11"/>
       <c r="M43" s="11"/>
     </row>
     <row r="44" spans="1:13" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="11"/>
-      <c r="B44" s="96" t="s">
+      <c r="B44" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="C44" s="97"/>
+      <c r="C44" s="37"/>
       <c r="D44" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="E44" s="119" t="s">
+      <c r="E44" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="F44" s="120"/>
-      <c r="G44" s="120"/>
-      <c r="H44" s="116"/>
-      <c r="I44" s="117"/>
-      <c r="J44" s="118"/>
+      <c r="F44" s="39"/>
+      <c r="G44" s="39"/>
+      <c r="H44" s="40"/>
+      <c r="I44" s="41"/>
+      <c r="J44" s="42"/>
       <c r="K44" s="11"/>
       <c r="L44" s="11"/>
       <c r="M44" s="11"/>
     </row>
     <row r="45" spans="1:13" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="11"/>
-      <c r="B45" s="83" t="s">
+      <c r="B45" s="109" t="s">
         <v>49</v>
       </c>
-      <c r="C45" s="84"/>
-      <c r="D45" s="85"/>
-      <c r="E45" s="85"/>
-      <c r="F45" s="85"/>
-      <c r="G45" s="85"/>
-      <c r="H45" s="84"/>
-      <c r="I45" s="84"/>
-      <c r="J45" s="86"/>
+      <c r="C45" s="110"/>
+      <c r="D45" s="111"/>
+      <c r="E45" s="111"/>
+      <c r="F45" s="111"/>
+      <c r="G45" s="111"/>
+      <c r="H45" s="110"/>
+      <c r="I45" s="110"/>
+      <c r="J45" s="112"/>
       <c r="K45" s="11"/>
       <c r="L45" s="11"/>
       <c r="M45" s="11"/>
     </row>
     <row r="46" spans="1:13" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="11"/>
-      <c r="B46" s="51" t="s">
+      <c r="B46" s="127" t="s">
         <v>50</v>
       </c>
-      <c r="C46" s="52"/>
-      <c r="D46" s="55" t="s">
+      <c r="C46" s="128"/>
+      <c r="D46" s="97" t="s">
         <v>51</v>
       </c>
-      <c r="E46" s="56"/>
-      <c r="F46" s="56"/>
-      <c r="G46" s="57"/>
-      <c r="H46" s="58" t="s">
+      <c r="E46" s="129"/>
+      <c r="F46" s="129"/>
+      <c r="G46" s="98"/>
+      <c r="H46" s="115" t="s">
         <v>52</v>
       </c>
-      <c r="I46" s="59"/>
-      <c r="J46" s="60"/>
+      <c r="I46" s="119"/>
+      <c r="J46" s="116"/>
       <c r="K46" s="11"/>
       <c r="L46" s="11"/>
       <c r="M46" s="11"/>
     </row>
     <row r="47" spans="1:13" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="11"/>
-      <c r="B47" s="53"/>
-      <c r="C47" s="54"/>
-      <c r="D47" s="64" t="s">
+      <c r="B47" s="95"/>
+      <c r="C47" s="96"/>
+      <c r="D47" s="130" t="s">
         <v>53</v>
       </c>
-      <c r="E47" s="65"/>
-      <c r="F47" s="64" t="s">
+      <c r="E47" s="131"/>
+      <c r="F47" s="130" t="s">
         <v>54</v>
       </c>
-      <c r="G47" s="65"/>
-      <c r="H47" s="61"/>
-      <c r="I47" s="62"/>
-      <c r="J47" s="63"/>
+      <c r="G47" s="131"/>
+      <c r="H47" s="117"/>
+      <c r="I47" s="120"/>
+      <c r="J47" s="118"/>
       <c r="K47" s="11"/>
       <c r="L47" s="11"/>
       <c r="M47" s="11"/>
     </row>
-    <row r="48" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="15"/>
-      <c r="B48" s="32" t="s">
+      <c r="B48" s="113" t="s">
         <v>55</v>
       </c>
-      <c r="C48" s="33"/>
-      <c r="D48" s="34"/>
-      <c r="E48" s="35"/>
-      <c r="F48" s="34"/>
-      <c r="G48" s="35"/>
-      <c r="H48" s="66"/>
-      <c r="I48" s="67"/>
-      <c r="J48" s="68"/>
+      <c r="C48" s="114"/>
+      <c r="D48" s="18"/>
+      <c r="E48" s="19"/>
+      <c r="F48" s="18"/>
+      <c r="G48" s="19"/>
+      <c r="H48" s="149"/>
+      <c r="I48" s="150"/>
+      <c r="J48" s="151"/>
       <c r="K48" s="15"/>
       <c r="L48" s="15"/>
       <c r="M48" s="15"/>
     </row>
-    <row r="49" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:13" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="15"/>
-      <c r="B49" s="32" t="s">
+      <c r="B49" s="113" t="s">
         <v>56</v>
       </c>
-      <c r="C49" s="33"/>
-      <c r="D49" s="34"/>
-      <c r="E49" s="35"/>
-      <c r="F49" s="34"/>
-      <c r="G49" s="35"/>
-      <c r="H49" s="41"/>
-      <c r="I49" s="42"/>
-      <c r="J49" s="43"/>
+      <c r="C49" s="114"/>
+      <c r="D49" s="18"/>
+      <c r="E49" s="19"/>
+      <c r="F49" s="18"/>
+      <c r="G49" s="19"/>
+      <c r="H49" s="149"/>
+      <c r="I49" s="150"/>
+      <c r="J49" s="151"/>
       <c r="K49" s="15"/>
       <c r="L49" s="15"/>
       <c r="M49" s="15"/>
     </row>
-    <row r="50" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="15"/>
-      <c r="B50" s="32" t="s">
+      <c r="B50" s="113" t="s">
         <v>57</v>
       </c>
-      <c r="C50" s="33"/>
-      <c r="D50" s="34"/>
-      <c r="E50" s="35"/>
-      <c r="F50" s="34"/>
-      <c r="G50" s="35"/>
-      <c r="H50" s="41"/>
-      <c r="I50" s="42"/>
-      <c r="J50" s="43"/>
+      <c r="C50" s="114"/>
+      <c r="D50" s="18"/>
+      <c r="E50" s="19"/>
+      <c r="F50" s="18"/>
+      <c r="G50" s="19"/>
+      <c r="H50" s="149"/>
+      <c r="I50" s="150"/>
+      <c r="J50" s="151"/>
       <c r="K50" s="15"/>
       <c r="L50" s="15"/>
       <c r="M50" s="15"/>
     </row>
-    <row r="51" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="15"/>
-      <c r="B51" s="39" t="s">
+      <c r="B51" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="C51" s="40"/>
-      <c r="D51" s="94"/>
-      <c r="E51" s="95"/>
-      <c r="F51" s="94"/>
-      <c r="G51" s="95"/>
-      <c r="H51" s="69"/>
-      <c r="I51" s="70"/>
-      <c r="J51" s="71"/>
+      <c r="C51" s="29"/>
+      <c r="D51" s="125"/>
+      <c r="E51" s="126"/>
+      <c r="F51" s="125"/>
+      <c r="G51" s="126"/>
+      <c r="H51" s="149"/>
+      <c r="I51" s="150"/>
+      <c r="J51" s="151"/>
       <c r="K51" s="15"/>
       <c r="L51" s="15"/>
       <c r="M51" s="15"/>
     </row>
-    <row r="52" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:13" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="15"/>
-      <c r="B52" s="32" t="s">
+      <c r="B52" s="113" t="s">
         <v>58</v>
       </c>
-      <c r="C52" s="33"/>
-      <c r="D52" s="34"/>
-      <c r="E52" s="35"/>
-      <c r="F52" s="34"/>
-      <c r="G52" s="35"/>
-      <c r="H52" s="36"/>
-      <c r="I52" s="37"/>
-      <c r="J52" s="38"/>
+      <c r="C52" s="114"/>
+      <c r="D52" s="18"/>
+      <c r="E52" s="19"/>
+      <c r="F52" s="18"/>
+      <c r="G52" s="19"/>
+      <c r="H52" s="149"/>
+      <c r="I52" s="150"/>
+      <c r="J52" s="151"/>
       <c r="K52" s="15"/>
       <c r="L52" s="15"/>
       <c r="M52" s="15"/>
     </row>
-    <row r="53" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:13" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="15"/>
-      <c r="B53" s="32" t="s">
+      <c r="B53" s="113" t="s">
         <v>59</v>
       </c>
-      <c r="C53" s="33"/>
-      <c r="D53" s="34"/>
-      <c r="E53" s="35"/>
-      <c r="F53" s="34"/>
-      <c r="G53" s="35"/>
-      <c r="H53" s="41"/>
-      <c r="I53" s="42"/>
-      <c r="J53" s="43"/>
+      <c r="C53" s="114"/>
+      <c r="D53" s="18"/>
+      <c r="E53" s="19"/>
+      <c r="F53" s="18"/>
+      <c r="G53" s="19"/>
+      <c r="H53" s="149"/>
+      <c r="I53" s="150"/>
+      <c r="J53" s="151"/>
       <c r="K53" s="15"/>
       <c r="L53" s="15"/>
       <c r="M53" s="15"/>
     </row>
-    <row r="54" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:13" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="15"/>
-      <c r="B54" s="32" t="s">
+      <c r="B54" s="113" t="s">
         <v>60</v>
       </c>
-      <c r="C54" s="33"/>
-      <c r="D54" s="34"/>
-      <c r="E54" s="35"/>
-      <c r="F54" s="34"/>
-      <c r="G54" s="35"/>
-      <c r="H54" s="41"/>
-      <c r="I54" s="42"/>
-      <c r="J54" s="43"/>
+      <c r="C54" s="114"/>
+      <c r="D54" s="18"/>
+      <c r="E54" s="19"/>
+      <c r="F54" s="18"/>
+      <c r="G54" s="19"/>
+      <c r="H54" s="149"/>
+      <c r="I54" s="150"/>
+      <c r="J54" s="151"/>
       <c r="K54" s="15"/>
       <c r="L54" s="15"/>
       <c r="M54" s="15"/>
     </row>
-    <row r="55" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="15"/>
-      <c r="B55" s="44" t="s">
+      <c r="B55" s="143" t="s">
         <v>61</v>
       </c>
-      <c r="C55" s="45"/>
-      <c r="D55" s="46"/>
-      <c r="E55" s="47"/>
-      <c r="F55" s="46"/>
-      <c r="G55" s="47"/>
-      <c r="H55" s="48"/>
-      <c r="I55" s="49"/>
-      <c r="J55" s="50"/>
+      <c r="C55" s="144"/>
+      <c r="D55" s="145"/>
+      <c r="E55" s="146"/>
+      <c r="F55" s="145"/>
+      <c r="G55" s="146"/>
+      <c r="H55" s="149"/>
+      <c r="I55" s="150"/>
+      <c r="J55" s="151"/>
       <c r="K55" s="15"/>
       <c r="L55" s="15"/>
       <c r="M55" s="15"/>
     </row>
     <row r="56" spans="1:13" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="15"/>
-      <c r="B56" s="92" t="s">
+      <c r="B56" s="123" t="s">
         <v>62</v>
       </c>
-      <c r="C56" s="85"/>
-      <c r="D56" s="85"/>
-      <c r="E56" s="85"/>
-      <c r="F56" s="85"/>
-      <c r="G56" s="85"/>
-      <c r="H56" s="85"/>
-      <c r="I56" s="85"/>
-      <c r="J56" s="93"/>
+      <c r="C56" s="111"/>
+      <c r="D56" s="111"/>
+      <c r="E56" s="111"/>
+      <c r="F56" s="111"/>
+      <c r="G56" s="111"/>
+      <c r="H56" s="111"/>
+      <c r="I56" s="111"/>
+      <c r="J56" s="124"/>
       <c r="K56" s="15"/>
       <c r="L56" s="15"/>
       <c r="M56" s="15"/>
     </row>
     <row r="57" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="15"/>
-      <c r="B57" s="58" t="s">
+      <c r="B57" s="115" t="s">
         <v>50</v>
       </c>
-      <c r="C57" s="60"/>
-      <c r="D57" s="87" t="s">
+      <c r="C57" s="116"/>
+      <c r="D57" s="78" t="s">
         <v>51</v>
       </c>
-      <c r="E57" s="88"/>
-      <c r="F57" s="88"/>
-      <c r="G57" s="89"/>
-      <c r="H57" s="58" t="s">
+      <c r="E57" s="79"/>
+      <c r="F57" s="79"/>
+      <c r="G57" s="80"/>
+      <c r="H57" s="115" t="s">
         <v>52</v>
       </c>
-      <c r="I57" s="59"/>
-      <c r="J57" s="60"/>
+      <c r="I57" s="119"/>
+      <c r="J57" s="116"/>
       <c r="K57" s="15"/>
       <c r="L57" s="15"/>
       <c r="M57" s="15"/>
     </row>
     <row r="58" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="15"/>
-      <c r="B58" s="61"/>
-      <c r="C58" s="63"/>
-      <c r="D58" s="90" t="s">
+      <c r="B58" s="117"/>
+      <c r="C58" s="118"/>
+      <c r="D58" s="121" t="s">
         <v>53</v>
       </c>
-      <c r="E58" s="91"/>
-      <c r="F58" s="90" t="s">
+      <c r="E58" s="122"/>
+      <c r="F58" s="121" t="s">
         <v>54</v>
       </c>
-      <c r="G58" s="91"/>
-      <c r="H58" s="61"/>
-      <c r="I58" s="62"/>
-      <c r="J58" s="63"/>
+      <c r="G58" s="122"/>
+      <c r="H58" s="117"/>
+      <c r="I58" s="120"/>
+      <c r="J58" s="118"/>
       <c r="K58" s="15"/>
       <c r="L58" s="15"/>
       <c r="M58" s="15"/>
     </row>
-    <row r="59" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:13" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="15"/>
-      <c r="B59" s="32" t="s">
+      <c r="B59" s="113" t="s">
         <v>63</v>
       </c>
-      <c r="C59" s="33"/>
-      <c r="D59" s="34"/>
-      <c r="E59" s="35"/>
-      <c r="F59" s="34"/>
-      <c r="G59" s="35"/>
-      <c r="H59" s="36"/>
-      <c r="I59" s="37"/>
-      <c r="J59" s="38"/>
+      <c r="C59" s="114"/>
+      <c r="D59" s="18"/>
+      <c r="E59" s="19"/>
+      <c r="F59" s="18"/>
+      <c r="G59" s="19"/>
+      <c r="H59" s="149"/>
+      <c r="I59" s="150"/>
+      <c r="J59" s="151"/>
       <c r="K59" s="15"/>
       <c r="L59" s="15"/>
       <c r="M59" s="15"/>
     </row>
-    <row r="60" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:13" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="15"/>
-      <c r="B60" s="32" t="s">
+      <c r="B60" s="113" t="s">
         <v>64</v>
       </c>
-      <c r="C60" s="33"/>
-      <c r="D60" s="34"/>
-      <c r="E60" s="35"/>
-      <c r="F60" s="34"/>
-      <c r="G60" s="35"/>
-      <c r="H60" s="36"/>
-      <c r="I60" s="37"/>
-      <c r="J60" s="38"/>
+      <c r="C60" s="114"/>
+      <c r="D60" s="18"/>
+      <c r="E60" s="19"/>
+      <c r="F60" s="18"/>
+      <c r="G60" s="19"/>
+      <c r="H60" s="149"/>
+      <c r="I60" s="150"/>
+      <c r="J60" s="151"/>
       <c r="K60" s="15"/>
       <c r="L60" s="15"/>
       <c r="M60" s="15"/>
     </row>
-    <row r="61" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:13" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="15"/>
-      <c r="B61" s="32" t="s">
+      <c r="B61" s="113" t="s">
         <v>65</v>
       </c>
-      <c r="C61" s="33"/>
-      <c r="D61" s="34"/>
-      <c r="E61" s="35"/>
-      <c r="F61" s="34"/>
-      <c r="G61" s="35"/>
-      <c r="H61" s="36"/>
-      <c r="I61" s="37"/>
-      <c r="J61" s="38"/>
+      <c r="C61" s="114"/>
+      <c r="D61" s="18"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="18"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="149"/>
+      <c r="I61" s="150"/>
+      <c r="J61" s="151"/>
       <c r="K61" s="15"/>
       <c r="L61" s="15"/>
       <c r="M61" s="15"/>
     </row>
-    <row r="62" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:13" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="15"/>
-      <c r="B62" s="32" t="s">
+      <c r="B62" s="113" t="s">
         <v>66</v>
       </c>
-      <c r="C62" s="33"/>
-      <c r="D62" s="34"/>
-      <c r="E62" s="35"/>
-      <c r="F62" s="34"/>
-      <c r="G62" s="35"/>
-      <c r="H62" s="36"/>
-      <c r="I62" s="37"/>
-      <c r="J62" s="38"/>
+      <c r="C62" s="114"/>
+      <c r="D62" s="18"/>
+      <c r="E62" s="19"/>
+      <c r="F62" s="18"/>
+      <c r="G62" s="19"/>
+      <c r="H62" s="149"/>
+      <c r="I62" s="150"/>
+      <c r="J62" s="151"/>
       <c r="K62" s="15"/>
       <c r="L62" s="15"/>
       <c r="M62" s="15"/>
     </row>
-    <row r="63" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:13" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="15"/>
-      <c r="B63" s="32" t="s">
+      <c r="B63" s="113" t="s">
         <v>67</v>
       </c>
-      <c r="C63" s="33"/>
-      <c r="D63" s="34"/>
-      <c r="E63" s="35"/>
-      <c r="F63" s="34"/>
-      <c r="G63" s="35"/>
-      <c r="H63" s="36"/>
-      <c r="I63" s="37"/>
-      <c r="J63" s="38"/>
+      <c r="C63" s="114"/>
+      <c r="D63" s="18"/>
+      <c r="E63" s="19"/>
+      <c r="F63" s="18"/>
+      <c r="G63" s="19"/>
+      <c r="H63" s="149"/>
+      <c r="I63" s="150"/>
+      <c r="J63" s="151"/>
       <c r="K63" s="15"/>
       <c r="L63" s="15"/>
       <c r="M63" s="15"/>
@@ -3001,15 +2950,15 @@
     </row>
     <row r="66" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="11"/>
-      <c r="B66" s="149"/>
-      <c r="C66" s="149"/>
-      <c r="D66" s="149"/>
-      <c r="E66" s="149"/>
-      <c r="F66" s="149"/>
-      <c r="G66" s="149"/>
-      <c r="H66" s="149"/>
-      <c r="I66" s="149"/>
-      <c r="J66" s="149"/>
+      <c r="B66" s="153"/>
+      <c r="C66" s="153"/>
+      <c r="D66" s="153"/>
+      <c r="E66" s="153"/>
+      <c r="F66" s="153"/>
+      <c r="G66" s="153"/>
+      <c r="H66" s="153"/>
+      <c r="I66" s="153"/>
+      <c r="J66" s="153"/>
       <c r="K66" s="11"/>
       <c r="L66" s="11"/>
       <c r="M66" s="11"/>
@@ -3025,15 +2974,15 @@
     </row>
     <row r="68" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="11"/>
-      <c r="B68" s="150"/>
-      <c r="C68" s="150"/>
-      <c r="D68" s="150"/>
-      <c r="E68" s="150"/>
-      <c r="F68" s="150"/>
-      <c r="G68" s="150"/>
-      <c r="H68" s="150"/>
-      <c r="I68" s="150"/>
-      <c r="J68" s="150"/>
+      <c r="B68" s="152"/>
+      <c r="C68" s="152"/>
+      <c r="D68" s="152"/>
+      <c r="E68" s="152"/>
+      <c r="F68" s="152"/>
+      <c r="G68" s="152"/>
+      <c r="H68" s="152"/>
+      <c r="I68" s="152"/>
+      <c r="J68" s="152"/>
       <c r="K68" s="11"/>
       <c r="L68" s="11"/>
       <c r="M68" s="11"/>
@@ -3049,15 +2998,15 @@
     </row>
     <row r="70" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="11"/>
-      <c r="B70" s="151"/>
-      <c r="C70" s="151"/>
-      <c r="D70" s="151"/>
-      <c r="E70" s="151"/>
-      <c r="F70" s="151"/>
-      <c r="G70" s="151"/>
-      <c r="H70" s="151"/>
-      <c r="I70" s="151"/>
-      <c r="J70" s="151"/>
+      <c r="B70" s="152"/>
+      <c r="C70" s="152"/>
+      <c r="D70" s="152"/>
+      <c r="E70" s="152"/>
+      <c r="F70" s="152"/>
+      <c r="G70" s="152"/>
+      <c r="H70" s="152"/>
+      <c r="I70" s="152"/>
+      <c r="J70" s="152"/>
       <c r="K70" s="11"/>
       <c r="L70" s="11"/>
       <c r="M70" s="11"/>
@@ -3078,96 +3027,96 @@
       <c r="M71" s="11"/>
     </row>
     <row r="72" spans="1:13" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="162"/>
-      <c r="B72" s="162"/>
-      <c r="C72" s="162"/>
-      <c r="D72" s="162"/>
-      <c r="E72" s="160"/>
-      <c r="F72" s="160"/>
-      <c r="G72" s="162"/>
-      <c r="H72" s="162"/>
-      <c r="I72" s="160"/>
-      <c r="J72" s="160"/>
-      <c r="K72" s="162"/>
-      <c r="L72" s="162"/>
-      <c r="M72" s="162"/>
+      <c r="A72" s="46"/>
+      <c r="B72" s="46"/>
+      <c r="C72" s="46"/>
+      <c r="D72" s="46"/>
+      <c r="E72" s="44"/>
+      <c r="F72" s="44"/>
+      <c r="G72" s="46"/>
+      <c r="H72" s="46"/>
+      <c r="I72" s="44"/>
+      <c r="J72" s="44"/>
+      <c r="K72" s="46"/>
+      <c r="L72" s="46"/>
+      <c r="M72" s="46"/>
     </row>
     <row r="73" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="162"/>
-      <c r="B73" s="162"/>
-      <c r="C73" s="162"/>
-      <c r="D73" s="162"/>
-      <c r="E73" s="160"/>
-      <c r="F73" s="160"/>
-      <c r="G73" s="162"/>
-      <c r="H73" s="162"/>
-      <c r="I73" s="160"/>
-      <c r="J73" s="160"/>
-      <c r="K73" s="162"/>
-      <c r="L73" s="162"/>
-      <c r="M73" s="162"/>
+      <c r="A73" s="46"/>
+      <c r="B73" s="46"/>
+      <c r="C73" s="46"/>
+      <c r="D73" s="46"/>
+      <c r="E73" s="44"/>
+      <c r="F73" s="44"/>
+      <c r="G73" s="46"/>
+      <c r="H73" s="46"/>
+      <c r="I73" s="44"/>
+      <c r="J73" s="44"/>
+      <c r="K73" s="46"/>
+      <c r="L73" s="46"/>
+      <c r="M73" s="46"/>
     </row>
     <row r="74" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="162"/>
-      <c r="B74" s="162"/>
-      <c r="C74" s="162"/>
-      <c r="D74" s="162"/>
-      <c r="E74" s="160"/>
-      <c r="F74" s="160"/>
-      <c r="G74" s="162"/>
-      <c r="H74" s="162"/>
-      <c r="I74" s="160"/>
-      <c r="J74" s="160"/>
-      <c r="K74" s="162"/>
-      <c r="L74" s="162"/>
-      <c r="M74" s="162"/>
+      <c r="A74" s="46"/>
+      <c r="B74" s="46"/>
+      <c r="C74" s="46"/>
+      <c r="D74" s="46"/>
+      <c r="E74" s="44"/>
+      <c r="F74" s="44"/>
+      <c r="G74" s="46"/>
+      <c r="H74" s="46"/>
+      <c r="I74" s="44"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="46"/>
+      <c r="L74" s="46"/>
+      <c r="M74" s="46"/>
     </row>
     <row r="75" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="162"/>
-      <c r="B75" s="162"/>
-      <c r="C75" s="162"/>
-      <c r="D75" s="162"/>
-      <c r="E75" s="160"/>
-      <c r="F75" s="160"/>
-      <c r="G75" s="162"/>
-      <c r="H75" s="162"/>
-      <c r="I75" s="160"/>
-      <c r="J75" s="160"/>
-      <c r="K75" s="162"/>
-      <c r="L75" s="162"/>
-      <c r="M75" s="162"/>
+      <c r="A75" s="46"/>
+      <c r="B75" s="46"/>
+      <c r="C75" s="46"/>
+      <c r="D75" s="46"/>
+      <c r="E75" s="44"/>
+      <c r="F75" s="44"/>
+      <c r="G75" s="46"/>
+      <c r="H75" s="46"/>
+      <c r="I75" s="44"/>
+      <c r="J75" s="44"/>
+      <c r="K75" s="46"/>
+      <c r="L75" s="46"/>
+      <c r="M75" s="46"/>
     </row>
     <row r="76" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="163"/>
-      <c r="B76" s="163"/>
-      <c r="C76" s="163"/>
-      <c r="D76" s="163"/>
-      <c r="E76" s="160"/>
-      <c r="F76" s="160"/>
-      <c r="G76" s="163"/>
-      <c r="H76" s="163"/>
-      <c r="I76" s="160"/>
-      <c r="J76" s="160"/>
-      <c r="K76" s="163"/>
-      <c r="L76" s="163"/>
-      <c r="M76" s="163"/>
+      <c r="A76" s="47"/>
+      <c r="B76" s="47"/>
+      <c r="C76" s="47"/>
+      <c r="D76" s="47"/>
+      <c r="E76" s="44"/>
+      <c r="F76" s="44"/>
+      <c r="G76" s="47"/>
+      <c r="H76" s="47"/>
+      <c r="I76" s="44"/>
+      <c r="J76" s="44"/>
+      <c r="K76" s="47"/>
+      <c r="L76" s="47"/>
+      <c r="M76" s="47"/>
     </row>
     <row r="77" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="159"/>
-      <c r="B77" s="159"/>
-      <c r="C77" s="159"/>
-      <c r="D77" s="159"/>
-      <c r="E77" s="160"/>
-      <c r="F77" s="160"/>
-      <c r="G77" s="161" t="s">
+      <c r="A77" s="43"/>
+      <c r="B77" s="43"/>
+      <c r="C77" s="43"/>
+      <c r="D77" s="43"/>
+      <c r="E77" s="44"/>
+      <c r="F77" s="44"/>
+      <c r="G77" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="H77" s="161"/>
-      <c r="I77" s="160"/>
-      <c r="J77" s="160"/>
-      <c r="K77" s="159"/>
-      <c r="L77" s="159"/>
-      <c r="M77" s="159"/>
+      <c r="H77" s="45"/>
+      <c r="I77" s="44"/>
+      <c r="J77" s="44"/>
+      <c r="K77" s="43"/>
+      <c r="L77" s="43"/>
+      <c r="M77" s="43"/>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" s="12"/>
@@ -3186,24 +3135,166 @@
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" s="13"/>
-      <c r="C79" s="145"/>
-      <c r="D79" s="145"/>
-      <c r="E79" s="145"/>
-      <c r="F79" s="145"/>
-      <c r="G79" s="145"/>
-      <c r="H79" s="145"/>
-      <c r="I79" s="145"/>
-      <c r="J79" s="145"/>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="22"/>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="F80" s="24" t="s">
+      <c r="F80" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="G80" s="24"/>
+      <c r="G80" s="20"/>
     </row>
     <row r="81" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="166">
+    <mergeCell ref="B1:K1"/>
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="B3:K3"/>
+    <mergeCell ref="B4:K4"/>
+    <mergeCell ref="B5:K5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="D63:E63"/>
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="H63:J63"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="H53:J53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="H54:J54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="H55:J55"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="D62:E62"/>
+    <mergeCell ref="F62:G62"/>
+    <mergeCell ref="H62:J62"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="H52:J52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="B46:C47"/>
+    <mergeCell ref="D46:G46"/>
+    <mergeCell ref="H46:J47"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="H48:J48"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="D61:E61"/>
+    <mergeCell ref="F61:G61"/>
+    <mergeCell ref="H61:J61"/>
+    <mergeCell ref="H51:J51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="H49:J49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B41:J41"/>
+    <mergeCell ref="G42:I42"/>
+    <mergeCell ref="G43:I43"/>
+    <mergeCell ref="J42:J43"/>
+    <mergeCell ref="B45:J45"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="H60:J60"/>
+    <mergeCell ref="B57:C58"/>
+    <mergeCell ref="D57:G57"/>
+    <mergeCell ref="H57:J58"/>
+    <mergeCell ref="D58:E58"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="D59:E59"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="H59:J59"/>
+    <mergeCell ref="B56:J56"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="H50:J50"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="A14:A22"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E20:M20"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E17:M17"/>
+    <mergeCell ref="E18:M18"/>
+    <mergeCell ref="E19:M19"/>
+    <mergeCell ref="E31:M31"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E26:M26"/>
+    <mergeCell ref="E27:M27"/>
+    <mergeCell ref="E28:M28"/>
+    <mergeCell ref="E22:M22"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="E35:M35"/>
+    <mergeCell ref="E36:M36"/>
+    <mergeCell ref="E37:M37"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="E33:M33"/>
+    <mergeCell ref="E34:M34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="C9:M9"/>
+    <mergeCell ref="A8:M8"/>
+    <mergeCell ref="E14:M14"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="J13:M13"/>
+    <mergeCell ref="E15:M15"/>
+    <mergeCell ref="E16:M16"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="E32:M32"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="E29:M29"/>
+    <mergeCell ref="E30:M30"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E23:M23"/>
+    <mergeCell ref="E24:M24"/>
+    <mergeCell ref="E25:M25"/>
+    <mergeCell ref="E21:M21"/>
     <mergeCell ref="F50:G50"/>
     <mergeCell ref="F80:G80"/>
     <mergeCell ref="A38:M40"/>
@@ -3228,180 +3319,38 @@
     <mergeCell ref="I72:J76"/>
     <mergeCell ref="K72:M76"/>
     <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="C9:M9"/>
-    <mergeCell ref="A8:M8"/>
-    <mergeCell ref="E14:M14"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="J13:M13"/>
-    <mergeCell ref="E15:M15"/>
-    <mergeCell ref="E16:M16"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="E32:M32"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="E29:M29"/>
-    <mergeCell ref="E30:M30"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E23:M23"/>
-    <mergeCell ref="E24:M24"/>
-    <mergeCell ref="E25:M25"/>
-    <mergeCell ref="E21:M21"/>
-    <mergeCell ref="E22:M22"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="E35:M35"/>
-    <mergeCell ref="E36:M36"/>
-    <mergeCell ref="E37:M37"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="E33:M33"/>
-    <mergeCell ref="E34:M34"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E17:M17"/>
-    <mergeCell ref="E18:M18"/>
-    <mergeCell ref="E19:M19"/>
-    <mergeCell ref="E31:M31"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="E26:M26"/>
-    <mergeCell ref="E27:M27"/>
-    <mergeCell ref="E28:M28"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="H50:J50"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="A14:A22"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E20:M20"/>
-    <mergeCell ref="B41:J41"/>
-    <mergeCell ref="G42:I42"/>
-    <mergeCell ref="G43:I43"/>
-    <mergeCell ref="J42:J43"/>
-    <mergeCell ref="B45:J45"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="F60:G60"/>
-    <mergeCell ref="H60:J60"/>
-    <mergeCell ref="B57:C58"/>
-    <mergeCell ref="D57:G57"/>
-    <mergeCell ref="H57:J58"/>
-    <mergeCell ref="D58:E58"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="D59:E59"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="H59:J59"/>
-    <mergeCell ref="B56:J56"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="F62:G62"/>
-    <mergeCell ref="H62:J62"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="H52:J52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="B46:C47"/>
-    <mergeCell ref="D46:G46"/>
-    <mergeCell ref="H46:J47"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="H48:J48"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="D61:E61"/>
-    <mergeCell ref="F61:G61"/>
-    <mergeCell ref="H61:J61"/>
-    <mergeCell ref="H51:J51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="H49:J49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B1:K1"/>
-    <mergeCell ref="B2:K2"/>
-    <mergeCell ref="B3:K3"/>
-    <mergeCell ref="B4:K4"/>
-    <mergeCell ref="B5:K5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="D63:E63"/>
-    <mergeCell ref="F63:G63"/>
-    <mergeCell ref="H63:J63"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="H53:J53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="H54:J54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="D55:E55"/>
-    <mergeCell ref="F55:G55"/>
-    <mergeCell ref="H55:J55"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="D62:E62"/>
   </mergeCells>
   <conditionalFormatting sqref="A77:D77">
-    <cfRule type="containsBlanks" dxfId="5" priority="4">
+    <cfRule type="containsBlanks" dxfId="11" priority="4">
       <formula>LEN(TRIM(A77))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C79">
-    <cfRule type="containsBlanks" dxfId="4" priority="5">
+    <cfRule type="containsBlanks" dxfId="10" priority="5">
       <formula>LEN(TRIM(C79))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D42:F43 J42:J43 D59:J63 B68:J68 B70:J70">
-    <cfRule type="containsBlanks" dxfId="3" priority="1">
+  <conditionalFormatting sqref="D42:F43 J42:J43 B68:J68 B70:J70 D59:J63">
+    <cfRule type="containsBlanks" dxfId="9" priority="1">
       <formula>LEN(TRIM(B42))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A77:D77 K77:M77 C79:J79 D48:J55">
-    <cfRule type="containsBlanks" dxfId="2" priority="2">
+    <cfRule type="containsBlanks" dxfId="8" priority="2">
       <formula>LEN(TRIM(A48))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I10:M10 C11:H11 K11:M11 J13:M13 E14:M22 E26:M37">
-    <cfRule type="containsBlanks" dxfId="1" priority="7">
+  <conditionalFormatting sqref="I10:M10 C11:H11 K11:M11 J13:M13 E14:M22 E26:M34">
+    <cfRule type="containsBlanks" dxfId="7" priority="7">
       <formula>LEN(TRIM(C10))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K77:M77">
-    <cfRule type="containsBlanks" dxfId="0" priority="3">
+    <cfRule type="containsBlanks" dxfId="6" priority="3">
       <formula>LEN(TRIM(K77))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="47">
+  <dataValidations count="46">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Indicar el nivel formativo en el cual se encuentra el aprendiz. Técnio o Tecnólogo" sqref="I10:M10" xr:uid="{FDFD4240-B4E4-40FA-8880-3E4E045C5084}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Registrar el nombre del programa" prompt="Registrar el nombre del programa" sqref="C11:H11" xr:uid="{34EF5BAD-650F-4FA7-AB25-B4A5694BB4C0}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Número Ficha" prompt="Registre el número de ficha en el que se encuentra matriculado según el programa de formación." sqref="K11:M11" xr:uid="{C295E52F-E427-4103-89DB-18FF195E95C6}"/>
@@ -3446,9 +3395,8 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Es comprometido con las actividades asignadas y con la empresa, demostrando puntualidad, proactividad y buena presentación personal en el desarrollo de su etapa productiva" sqref="D62:G62" xr:uid="{C5D9BB00-F014-4DE5-B59C-090440CDA5FD}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Demuestra capacidad para ordenar y disponer los elementos necesarios e información que facilite la ejecución del trabajo y el logro de los objetivos." sqref="D63:G63" xr:uid="{B8588CD4-9B9C-4123-8FA4-B0191CFB9CEA}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="OBLIGATORIO" prompt="Registrar de manera objetiva y concisa la información adicional que complemente el proceso de acompañamiento al aprendiz en su etapa productiva." sqref="B70:J70 B68:J68" xr:uid="{D7E55FAF-6FC8-4AC1-A902-F35811C9DD3B}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="DILIGENCIAR SI HAY POR MEJORAR" prompt="Si hay factores por mejorar favor escribir las observaciones o los compromisos de mejora" sqref="H48:J55" xr:uid="{70C7BBAF-F2BE-4776-BA55-57FE0807C14D}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Diligenciar si hay por mejorar" prompt="Si hay factores por mejorar favor escribir las observaciones o los compromisos de mejora" sqref="H59:J63" xr:uid="{56231F2E-9BAE-4742-84BB-A6BBFCFB029F}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Realiza acciones que fortalezcan su perfil ocupacional potenciando sus competencias en el marco de su proyecto de vida." sqref="D50:G50 F49:G49" xr:uid="{379961D4-6BD4-47A0-B009-E49C8B35A883}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="SIEMPRE DEBE HABER OBSERVACIONES" prompt="SIEMPRE DEBE HABER OBSERVACIONES, COMO FUE EL PROCESO, Si hay factores por mejorar favor escribir las observaciones o los compromisos de mejora" sqref="H48:J55 H59:J63" xr:uid="{F350E65D-086A-488F-8DDD-8C255CF214DC}"/>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="5" scale="68" fitToHeight="0" orientation="portrait" r:id="rId1"/>
@@ -3476,47 +3424,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="17" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="17" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="17" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="17" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="17" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="17" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="17" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="17" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="17" t="s">
         <v>90</v>
       </c>
     </row>
